--- a/data/proteomics/ecGEM_membrane_size_across_compartment.xlsx
+++ b/data/proteomics/ecGEM_membrane_size_across_compartment.xlsx
@@ -825,34 +825,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>341.9349002733412</v>
+        <v>341.9349002733411</v>
       </c>
       <c r="D2" t="n">
-        <v>405.1947170903244</v>
+        <v>405.1947170903243</v>
       </c>
       <c r="E2" t="n">
-        <v>363.0797480033031</v>
+        <v>363.0797480033033</v>
       </c>
       <c r="F2" t="n">
         <v>274.5615582077581</v>
       </c>
       <c r="G2" t="n">
-        <v>172.9248932250703</v>
+        <v>172.9248932250705</v>
       </c>
       <c r="H2" t="n">
-        <v>155.4409650019627</v>
+        <v>155.4409650019626</v>
       </c>
       <c r="I2" t="n">
-        <v>159.9638404648633</v>
+        <v>159.9638404648632</v>
       </c>
       <c r="J2" t="n">
         <v>211.3460219146438</v>
       </c>
       <c r="K2" t="n">
-        <v>221.5226409593046</v>
+        <v>221.5226409593047</v>
       </c>
       <c r="L2" t="n">
-        <v>187.9936846122838</v>
+        <v>187.9936846122835</v>
       </c>
       <c r="M2" t="n">
         <v>120.8896936178489</v>
@@ -861,46 +861,46 @@
         <v>125.5907455487216</v>
       </c>
       <c r="O2" t="n">
-        <v>175.6405888892381</v>
+        <v>175.6405888892379</v>
       </c>
       <c r="P2" t="n">
-        <v>174.4105961189974</v>
+        <v>174.4105961189973</v>
       </c>
       <c r="Q2" t="n">
-        <v>151.1915042685536</v>
+        <v>151.1915042685537</v>
       </c>
       <c r="R2" t="n">
-        <v>152.6438936516334</v>
+        <v>152.6438936516335</v>
       </c>
       <c r="S2" t="n">
         <v>151.0877045263773</v>
       </c>
       <c r="T2" t="n">
-        <v>151.2432138679309</v>
+        <v>151.2432138679308</v>
       </c>
       <c r="U2" t="n">
-        <v>156.8027671641794</v>
+        <v>156.8027671641793</v>
       </c>
       <c r="V2" t="n">
-        <v>228.5194626076303</v>
+        <v>228.5194626076302</v>
       </c>
       <c r="W2" t="n">
-        <v>231.7730421083305</v>
+        <v>231.7730421083303</v>
       </c>
       <c r="X2" t="n">
-        <v>214.1382574620363</v>
+        <v>214.1382574620362</v>
       </c>
       <c r="Y2" t="n">
-        <v>261.8597809286517</v>
+        <v>261.8597809286516</v>
       </c>
       <c r="Z2" t="n">
-        <v>279.0203552760472</v>
+        <v>279.0203552760471</v>
       </c>
       <c r="AA2" t="n">
         <v>278.354159069203</v>
       </c>
       <c r="AB2" t="n">
-        <v>279.1885986168287</v>
+        <v>279.1885986168289</v>
       </c>
       <c r="AC2" t="n">
         <v>321.811851960721</v>
@@ -909,16 +909,16 @@
         <v>330.9064607635642</v>
       </c>
       <c r="AE2" t="n">
-        <v>304.5224289388142</v>
+        <v>304.5224289388145</v>
       </c>
       <c r="AF2" t="n">
         <v>193.4648870452864</v>
       </c>
       <c r="AG2" t="n">
-        <v>242.2496924480211</v>
+        <v>242.249692448021</v>
       </c>
       <c r="AH2" t="n">
-        <v>130.8144880329803</v>
+        <v>130.8144880329804</v>
       </c>
       <c r="AI2" t="n">
         <v>216.8915738065944</v>
@@ -930,22 +930,22 @@
         <v>247.8031890058446</v>
       </c>
       <c r="AL2" t="n">
-        <v>306.4636294235858</v>
+        <v>306.4636294235856</v>
       </c>
       <c r="AM2" t="n">
-        <v>260.8792407341286</v>
+        <v>260.8792407341285</v>
       </c>
       <c r="AN2" t="n">
-        <v>239.2254599542547</v>
+        <v>239.2254599542548</v>
       </c>
       <c r="AO2" t="n">
-        <v>224.9267901784</v>
+        <v>224.9267901784002</v>
       </c>
       <c r="AP2" t="n">
-        <v>231.1852695671313</v>
+        <v>231.1852695671315</v>
       </c>
       <c r="AQ2" t="n">
-        <v>200.3269817688594</v>
+        <v>200.3269817688593</v>
       </c>
       <c r="AR2" t="n">
         <v>246.7508226430674</v>
@@ -954,13 +954,13 @@
         <v>230.1939020535299</v>
       </c>
       <c r="AT2" t="n">
-        <v>310.4983358499035</v>
+        <v>310.4983358499036</v>
       </c>
       <c r="AU2" t="n">
-        <v>287.872679578608</v>
+        <v>287.8726795786079</v>
       </c>
       <c r="AV2" t="n">
-        <v>290.145778309544</v>
+        <v>290.1457783095438</v>
       </c>
       <c r="AW2" t="n">
         <v>300.0662134307963</v>
@@ -972,37 +972,37 @@
         <v>259.0950691120357</v>
       </c>
       <c r="AZ2" t="n">
-        <v>349.5896466973706</v>
+        <v>349.5896466973705</v>
       </c>
       <c r="BA2" t="n">
-        <v>333.886748126864</v>
+        <v>333.8867481268639</v>
       </c>
       <c r="BB2" t="n">
-        <v>586.6577469290879</v>
+        <v>586.6577469290878</v>
       </c>
       <c r="BC2" t="n">
-        <v>329.3437840271649</v>
+        <v>329.343784027165</v>
       </c>
       <c r="BD2" t="n">
-        <v>580.1216431772932</v>
+        <v>580.1216431772926</v>
       </c>
       <c r="BE2" t="n">
         <v>259.3538107294333</v>
       </c>
       <c r="BF2" t="n">
-        <v>331.42878008261</v>
+        <v>331.4287800826103</v>
       </c>
       <c r="BG2" t="n">
-        <v>318.8434890755989</v>
+        <v>318.8434890755988</v>
       </c>
       <c r="BH2" t="n">
-        <v>355.8473788560283</v>
+        <v>355.8473788560285</v>
       </c>
       <c r="BI2" t="n">
-        <v>342.1197882023944</v>
+        <v>342.1197882023943</v>
       </c>
       <c r="BJ2" t="n">
-        <v>288.14915505727</v>
+        <v>288.1491550572701</v>
       </c>
       <c r="BK2" t="n">
         <v>161.827811073294</v>
@@ -1011,43 +1011,43 @@
         <v>153.8595194045932</v>
       </c>
       <c r="BM2" t="n">
-        <v>175.9932487326847</v>
+        <v>175.9932487326849</v>
       </c>
       <c r="BN2" t="n">
         <v>168.4520436957342</v>
       </c>
       <c r="BO2" t="n">
-        <v>242.618650735509</v>
+        <v>242.6186507355089</v>
       </c>
       <c r="BP2" t="n">
-        <v>208.6930947151088</v>
+        <v>208.6930947151087</v>
       </c>
       <c r="BQ2" t="n">
-        <v>127.1555314028006</v>
+        <v>127.1555314028005</v>
       </c>
       <c r="BR2" t="n">
-        <v>308.2392283694922</v>
+        <v>308.2392283694921</v>
       </c>
       <c r="BS2" t="n">
-        <v>326.3861040688064</v>
+        <v>326.3861040688067</v>
       </c>
       <c r="BT2" t="n">
-        <v>337.5075583366237</v>
+        <v>337.5075583366238</v>
       </c>
       <c r="BU2" t="n">
-        <v>359.4194068747437</v>
+        <v>359.4194068747439</v>
       </c>
       <c r="BV2" t="n">
         <v>257.4587570664362</v>
       </c>
       <c r="BW2" t="n">
-        <v>289.6519867845599</v>
+        <v>289.6519867845597</v>
       </c>
       <c r="BX2" t="n">
-        <v>292.4192857193289</v>
+        <v>292.4192857193287</v>
       </c>
       <c r="BY2" t="n">
-        <v>273.8028656426549</v>
+        <v>273.802865642655</v>
       </c>
       <c r="BZ2" t="n">
         <v>231.1502369602601</v>
@@ -1281,13 +1281,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0878624074492252</v>
+        <v>0.08786240744922519</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09776049402893387</v>
+        <v>0.0977604940289339</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09373030712755938</v>
+        <v>0.09373030712755939</v>
       </c>
       <c r="F4" t="n">
         <v>0.2736685339738332</v>
@@ -1302,7 +1302,7 @@
         <v>0.03539924750238321</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03827388923119541</v>
+        <v>0.03827388923119539</v>
       </c>
       <c r="K4" t="n">
         <v>0.0471922871770764</v>
@@ -1317,10 +1317,10 @@
         <v>0.03518434524936068</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06230361954245957</v>
+        <v>0.06230361954245958</v>
       </c>
       <c r="P4" t="n">
-        <v>0.05701414587723647</v>
+        <v>0.05701414587723648</v>
       </c>
       <c r="Q4" t="n">
         <v>0.04781607159520919</v>
@@ -1332,10 +1332,10 @@
         <v>0.0500861661659988</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04905490041695486</v>
+        <v>0.04905490041695487</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05238804099524868</v>
+        <v>0.05238804099524867</v>
       </c>
       <c r="V4" t="n">
         <v>0.06480364036596395</v>
@@ -1344,7 +1344,7 @@
         <v>0.06097944312664596</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05992828074712241</v>
+        <v>0.05992828074712242</v>
       </c>
       <c r="Y4" t="n">
         <v>0.06654170379663973</v>
@@ -1362,40 +1362,40 @@
         <v>0.05868799456079477</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.05117829936021531</v>
+        <v>0.05117829936021532</v>
       </c>
       <c r="AE4" t="n">
         <v>0.05084916792127157</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.03944117010382708</v>
+        <v>0.03944117010382707</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.04603451099103918</v>
+        <v>0.04603451099103919</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.03744517245583453</v>
+        <v>0.03744517245583454</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.05482466175825535</v>
+        <v>0.05482466175825534</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.05196553583678643</v>
+        <v>0.05196553583678645</v>
       </c>
       <c r="AK4" t="n">
         <v>0.05086074976993901</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.05824023616950345</v>
+        <v>0.05824023616950346</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.05817918006249572</v>
+        <v>0.05817918006249573</v>
       </c>
       <c r="AN4" t="n">
         <v>0.06282006603106814</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.05804090469146447</v>
+        <v>0.05804090469146448</v>
       </c>
       <c r="AP4" t="n">
         <v>0.05677991314208466</v>
@@ -1404,7 +1404,7 @@
         <v>0.03829961817035991</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.05178206597351048</v>
+        <v>0.05178206597351047</v>
       </c>
       <c r="AS4" t="n">
         <v>0.04163725462341571</v>
@@ -1416,16 +1416,16 @@
         <v>0.06947451676143096</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.06616247623782531</v>
+        <v>0.0661624762378253</v>
       </c>
       <c r="AW4" t="n">
         <v>0.1082664067649206</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1219220236452314</v>
+        <v>0.1219220236452313</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.1345487008519253</v>
+        <v>0.1345487008519252</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.1149655642176981</v>
@@ -1440,7 +1440,7 @@
         <v>0.4156136549686594</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.7451551373727866</v>
+        <v>0.7451551373727867</v>
       </c>
       <c r="BE4" t="n">
         <v>0.3694220892547386</v>
@@ -1470,7 +1470,7 @@
         <v>0.108546258654005</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.08975716298308481</v>
+        <v>0.0897571629830848</v>
       </c>
       <c r="BO4" t="n">
         <v>0.1018959177532607</v>
@@ -1479,7 +1479,7 @@
         <v>1.046669958361335</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.989776559774673</v>
+        <v>0.9897765597746732</v>
       </c>
       <c r="BR4" t="n">
         <v>0.1844701171588178</v>
@@ -1763,43 +1763,43 @@
         <v>104.9524906399786</v>
       </c>
       <c r="E6" t="n">
-        <v>92.36899644137914</v>
+        <v>92.3689964413791</v>
       </c>
       <c r="F6" t="n">
         <v>125.29430404497</v>
       </c>
       <c r="G6" t="n">
-        <v>67.15409264993158</v>
+        <v>67.1540926499316</v>
       </c>
       <c r="H6" t="n">
         <v>59.55086416278206</v>
       </c>
       <c r="I6" t="n">
-        <v>63.92916691663603</v>
+        <v>63.92916691663604</v>
       </c>
       <c r="J6" t="n">
         <v>77.70009605634515</v>
       </c>
       <c r="K6" t="n">
-        <v>85.76619128918185</v>
+        <v>85.76619128918182</v>
       </c>
       <c r="L6" t="n">
-        <v>68.40745177144235</v>
+        <v>68.40745177144233</v>
       </c>
       <c r="M6" t="n">
-        <v>51.76212624651814</v>
+        <v>51.76212624651816</v>
       </c>
       <c r="N6" t="n">
-        <v>53.11867279829028</v>
+        <v>53.11867279829027</v>
       </c>
       <c r="O6" t="n">
-        <v>65.66302516626351</v>
+        <v>65.66302516626348</v>
       </c>
       <c r="P6" t="n">
-        <v>72.27950266559918</v>
+        <v>72.27950266559915</v>
       </c>
       <c r="Q6" t="n">
-        <v>64.91522677922795</v>
+        <v>64.91522677922794</v>
       </c>
       <c r="R6" t="n">
         <v>62.77161794016624</v>
@@ -1808,19 +1808,19 @@
         <v>59.76283572635477</v>
       </c>
       <c r="T6" t="n">
-        <v>62.01783985095433</v>
+        <v>62.01783985095432</v>
       </c>
       <c r="U6" t="n">
-        <v>64.44286089421344</v>
+        <v>64.44286089421347</v>
       </c>
       <c r="V6" t="n">
-        <v>93.10748693845264</v>
+        <v>93.10748693845257</v>
       </c>
       <c r="W6" t="n">
-        <v>93.58365912511356</v>
+        <v>93.58365912511361</v>
       </c>
       <c r="X6" t="n">
-        <v>89.69449523885864</v>
+        <v>89.69449523885871</v>
       </c>
       <c r="Y6" t="n">
         <v>112.6333373179989</v>
@@ -1829,61 +1829,61 @@
         <v>123.3412034750496</v>
       </c>
       <c r="AA6" t="n">
-        <v>112.8590213913088</v>
+        <v>112.8590213913089</v>
       </c>
       <c r="AB6" t="n">
-        <v>99.31938159640289</v>
+        <v>99.31938159640281</v>
       </c>
       <c r="AC6" t="n">
-        <v>124.6340634093126</v>
+        <v>124.6340634093125</v>
       </c>
       <c r="AD6" t="n">
-        <v>131.5252905827195</v>
+        <v>131.5252905827194</v>
       </c>
       <c r="AE6" t="n">
-        <v>120.6445647834176</v>
+        <v>120.6445647834175</v>
       </c>
       <c r="AF6" t="n">
-        <v>64.37619875969699</v>
+        <v>64.376198759697</v>
       </c>
       <c r="AG6" t="n">
-        <v>83.01749336817684</v>
+        <v>83.01749336817693</v>
       </c>
       <c r="AH6" t="n">
-        <v>47.83625616617235</v>
+        <v>47.83625616617233</v>
       </c>
       <c r="AI6" t="n">
-        <v>81.33969256739573</v>
+        <v>81.3396925673957</v>
       </c>
       <c r="AJ6" t="n">
         <v>80.33521034376383</v>
       </c>
       <c r="AK6" t="n">
-        <v>92.55553164731654</v>
+        <v>92.55553164731658</v>
       </c>
       <c r="AL6" t="n">
         <v>118.468423573499</v>
       </c>
       <c r="AM6" t="n">
-        <v>93.44124449291282</v>
+        <v>93.44124449291283</v>
       </c>
       <c r="AN6" t="n">
-        <v>97.55582982877584</v>
+        <v>97.55582982877583</v>
       </c>
       <c r="AO6" t="n">
-        <v>84.13186667825271</v>
+        <v>84.13186667825266</v>
       </c>
       <c r="AP6" t="n">
-        <v>84.22489749825202</v>
+        <v>84.22489749825198</v>
       </c>
       <c r="AQ6" t="n">
-        <v>65.26362408802048</v>
+        <v>65.26362408802045</v>
       </c>
       <c r="AR6" t="n">
-        <v>92.05602153984361</v>
+        <v>92.05602153984357</v>
       </c>
       <c r="AS6" t="n">
-        <v>69.66559203152329</v>
+        <v>69.66559203152326</v>
       </c>
       <c r="AT6" t="n">
         <v>107.2361736484064</v>
@@ -1898,16 +1898,16 @@
         <v>124.089615540064</v>
       </c>
       <c r="AX6" t="n">
-        <v>72.5037596188545</v>
+        <v>72.50375961885449</v>
       </c>
       <c r="AY6" t="n">
-        <v>63.21708422287572</v>
+        <v>63.21708422287573</v>
       </c>
       <c r="AZ6" t="n">
-        <v>82.19488884521344</v>
+        <v>82.19488884521341</v>
       </c>
       <c r="BA6" t="n">
-        <v>72.73883230735765</v>
+        <v>72.73883230735767</v>
       </c>
       <c r="BB6" t="n">
         <v>174.6498131049931</v>
@@ -1916,22 +1916,22 @@
         <v>142.1194502172913</v>
       </c>
       <c r="BD6" t="n">
-        <v>209.1405143300435</v>
+        <v>209.1405143300437</v>
       </c>
       <c r="BE6" t="n">
         <v>122.3828946934715</v>
       </c>
       <c r="BF6" t="n">
-        <v>128.9740815973819</v>
+        <v>128.974081597382</v>
       </c>
       <c r="BG6" t="n">
         <v>127.9073701044319</v>
       </c>
       <c r="BH6" t="n">
-        <v>130.2718937998454</v>
+        <v>130.2718937998455</v>
       </c>
       <c r="BI6" t="n">
-        <v>127.3227166801647</v>
+        <v>127.3227166801646</v>
       </c>
       <c r="BJ6" t="n">
         <v>127.4098617017515</v>
@@ -1940,13 +1940,13 @@
         <v>66.92972781362373</v>
       </c>
       <c r="BL6" t="n">
-        <v>87.4710283031478</v>
+        <v>87.47102830314775</v>
       </c>
       <c r="BM6" t="n">
-        <v>71.54013841658083</v>
+        <v>71.54013841658086</v>
       </c>
       <c r="BN6" t="n">
-        <v>50.18613880570712</v>
+        <v>50.18613880570716</v>
       </c>
       <c r="BO6" t="n">
         <v>60.81165837559851</v>
@@ -1955,34 +1955,34 @@
         <v>101.0188662304882</v>
       </c>
       <c r="BQ6" t="n">
-        <v>58.21698665230519</v>
+        <v>58.2169866523052</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.90347763437538</v>
+        <v>94.90347763437536</v>
       </c>
       <c r="BS6" t="n">
-        <v>96.90866742805295</v>
+        <v>96.90866742805292</v>
       </c>
       <c r="BT6" t="n">
         <v>101.7159524418537</v>
       </c>
       <c r="BU6" t="n">
-        <v>107.958626410866</v>
+        <v>107.9586264108659</v>
       </c>
       <c r="BV6" t="n">
-        <v>77.04504175968445</v>
+        <v>77.04504175968441</v>
       </c>
       <c r="BW6" t="n">
         <v>85.38288611857176</v>
       </c>
       <c r="BX6" t="n">
-        <v>89.70391304772467</v>
+        <v>89.7039130477246</v>
       </c>
       <c r="BY6" t="n">
-        <v>92.1086147408065</v>
+        <v>92.10861474080649</v>
       </c>
       <c r="BZ6" t="n">
-        <v>85.25046617113851</v>
+        <v>85.25046617113846</v>
       </c>
     </row>
     <row r="7">
@@ -1995,19 +1995,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>393.7802898543649</v>
+        <v>393.780289854365</v>
       </c>
       <c r="D7" t="n">
-        <v>353.829723925033</v>
+        <v>353.8297239250331</v>
       </c>
       <c r="E7" t="n">
         <v>377.4425983687771</v>
       </c>
       <c r="F7" t="n">
-        <v>403.1396804407571</v>
+        <v>403.1396804407568</v>
       </c>
       <c r="G7" t="n">
-        <v>145.5494809724668</v>
+        <v>145.5494809724669</v>
       </c>
       <c r="H7" t="n">
         <v>130.9135813885022</v>
@@ -2016,7 +2016,7 @@
         <v>134.5473164723454</v>
       </c>
       <c r="J7" t="n">
-        <v>245.1879127668931</v>
+        <v>245.1879127668932</v>
       </c>
       <c r="K7" t="n">
         <v>255.5709307696925</v>
@@ -2028,7 +2028,7 @@
         <v>105.0712846207883</v>
       </c>
       <c r="N7" t="n">
-        <v>111.0730701460937</v>
+        <v>111.0730701460938</v>
       </c>
       <c r="O7" t="n">
         <v>150.4600940928404</v>
@@ -2037,13 +2037,13 @@
         <v>148.8895989905881</v>
       </c>
       <c r="Q7" t="n">
-        <v>126.3351471257818</v>
+        <v>126.3351471257817</v>
       </c>
       <c r="R7" t="n">
         <v>129.6343786139362</v>
       </c>
       <c r="S7" t="n">
-        <v>138.607306602502</v>
+        <v>138.6073066025021</v>
       </c>
       <c r="T7" t="n">
         <v>134.93107888812</v>
@@ -2052,73 +2052,73 @@
         <v>136.2893836529861</v>
       </c>
       <c r="V7" t="n">
-        <v>215.1453954863056</v>
+        <v>215.1453954863058</v>
       </c>
       <c r="W7" t="n">
-        <v>217.5674339710708</v>
+        <v>217.5674339710707</v>
       </c>
       <c r="X7" t="n">
         <v>212.1580742804857</v>
       </c>
       <c r="Y7" t="n">
-        <v>261.1162485178046</v>
+        <v>261.1162485178047</v>
       </c>
       <c r="Z7" t="n">
-        <v>269.0245211137774</v>
+        <v>269.0245211137775</v>
       </c>
       <c r="AA7" t="n">
         <v>273.4404460393056</v>
       </c>
       <c r="AB7" t="n">
-        <v>352.1539869970747</v>
+        <v>352.1539869970745</v>
       </c>
       <c r="AC7" t="n">
         <v>425.9642767366879</v>
       </c>
       <c r="AD7" t="n">
-        <v>421.9433531924815</v>
+        <v>421.9433531924816</v>
       </c>
       <c r="AE7" t="n">
-        <v>318.1126415958856</v>
+        <v>318.1126415958857</v>
       </c>
       <c r="AF7" t="n">
         <v>173.0338740538957</v>
       </c>
       <c r="AG7" t="n">
-        <v>208.3222249664171</v>
+        <v>208.3222249664169</v>
       </c>
       <c r="AH7" t="n">
         <v>100.5966687668571</v>
       </c>
       <c r="AI7" t="n">
-        <v>174.9488408442105</v>
+        <v>174.9488408442104</v>
       </c>
       <c r="AJ7" t="n">
-        <v>175.9573605728365</v>
+        <v>175.9573605728364</v>
       </c>
       <c r="AK7" t="n">
-        <v>222.1492721867725</v>
+        <v>222.1492721867724</v>
       </c>
       <c r="AL7" t="n">
         <v>278.1109674714263</v>
       </c>
       <c r="AM7" t="n">
-        <v>231.7967840619462</v>
+        <v>231.7967840619459</v>
       </c>
       <c r="AN7" t="n">
-        <v>199.6478493085536</v>
+        <v>199.6478493085534</v>
       </c>
       <c r="AO7" t="n">
-        <v>177.4639340983668</v>
+        <v>177.4639340983667</v>
       </c>
       <c r="AP7" t="n">
         <v>190.3193770583186</v>
       </c>
       <c r="AQ7" t="n">
-        <v>187.7926486450444</v>
+        <v>187.7926486450443</v>
       </c>
       <c r="AR7" t="n">
-        <v>262.2362083886538</v>
+        <v>262.2362083886539</v>
       </c>
       <c r="AS7" t="n">
         <v>202.9162520935215</v>
@@ -2130,28 +2130,28 @@
         <v>234.5226054291994</v>
       </c>
       <c r="AV7" t="n">
-        <v>233.9243151753155</v>
+        <v>233.9243151753151</v>
       </c>
       <c r="AW7" t="n">
-        <v>278.3197735502645</v>
+        <v>278.3197735502646</v>
       </c>
       <c r="AX7" t="n">
-        <v>360.3273069585053</v>
+        <v>360.3273069585054</v>
       </c>
       <c r="AY7" t="n">
-        <v>279.1185715185017</v>
+        <v>279.1185715185015</v>
       </c>
       <c r="AZ7" t="n">
-        <v>475.3744339991776</v>
+        <v>475.3744339991771</v>
       </c>
       <c r="BA7" t="n">
         <v>401.446391350001</v>
       </c>
       <c r="BB7" t="n">
-        <v>500.2951941358536</v>
+        <v>500.2951941358538</v>
       </c>
       <c r="BC7" t="n">
-        <v>343.1854401311078</v>
+        <v>343.1854401311076</v>
       </c>
       <c r="BD7" t="n">
         <v>520.5667864658333</v>
@@ -2163,61 +2163,61 @@
         <v>338.5581515773115</v>
       </c>
       <c r="BG7" t="n">
-        <v>333.3311871562325</v>
+        <v>333.3311871562322</v>
       </c>
       <c r="BH7" t="n">
         <v>344.7328947216702</v>
       </c>
       <c r="BI7" t="n">
-        <v>342.1356160600154</v>
+        <v>342.1356160600157</v>
       </c>
       <c r="BJ7" t="n">
-        <v>336.0826507628213</v>
+        <v>336.0826507628212</v>
       </c>
       <c r="BK7" t="n">
-        <v>152.5296398490326</v>
+        <v>152.5296398490327</v>
       </c>
       <c r="BL7" t="n">
-        <v>186.648118822323</v>
+        <v>186.6481188223231</v>
       </c>
       <c r="BM7" t="n">
-        <v>214.453658321959</v>
+        <v>214.4536583219589</v>
       </c>
       <c r="BN7" t="n">
         <v>154.9903349183698</v>
       </c>
       <c r="BO7" t="n">
-        <v>196.7357390609295</v>
+        <v>196.7357390609293</v>
       </c>
       <c r="BP7" t="n">
-        <v>240.9612828350307</v>
+        <v>240.9612828350309</v>
       </c>
       <c r="BQ7" t="n">
-        <v>145.6101709004397</v>
+        <v>145.6101709004396</v>
       </c>
       <c r="BR7" t="n">
-        <v>244.764218014687</v>
+        <v>244.7642180146869</v>
       </c>
       <c r="BS7" t="n">
-        <v>251.622493181497</v>
+        <v>251.6224931814971</v>
       </c>
       <c r="BT7" t="n">
         <v>263.9874116962216</v>
       </c>
       <c r="BU7" t="n">
-        <v>282.9906179885493</v>
+        <v>282.9906179885498</v>
       </c>
       <c r="BV7" t="n">
         <v>200.7959133700631</v>
       </c>
       <c r="BW7" t="n">
-        <v>227.2885759691806</v>
+        <v>227.2885759691805</v>
       </c>
       <c r="BX7" t="n">
         <v>235.1767751557642</v>
       </c>
       <c r="BY7" t="n">
-        <v>235.7546889003885</v>
+        <v>235.7546889003884</v>
       </c>
       <c r="BZ7" t="n">
         <v>215.9940827949831</v>
@@ -2236,64 +2236,64 @@
         <v>259.6384019303881</v>
       </c>
       <c r="D8" t="n">
-        <v>237.9917917902833</v>
+        <v>237.9917917902832</v>
       </c>
       <c r="E8" t="n">
         <v>193.9100589434975</v>
       </c>
       <c r="F8" t="n">
-        <v>203.8738416486982</v>
+        <v>203.8738416486983</v>
       </c>
       <c r="G8" t="n">
-        <v>91.20085027116291</v>
+        <v>91.20085027116295</v>
       </c>
       <c r="H8" t="n">
-        <v>77.70618739212732</v>
+        <v>77.70618739212735</v>
       </c>
       <c r="I8" t="n">
-        <v>79.54076642419913</v>
+        <v>79.54076642419908</v>
       </c>
       <c r="J8" t="n">
-        <v>100.1165331364528</v>
+        <v>100.1165331364527</v>
       </c>
       <c r="K8" t="n">
         <v>105.9574565642989</v>
       </c>
       <c r="L8" t="n">
-        <v>87.52066194164338</v>
+        <v>87.52066194164335</v>
       </c>
       <c r="M8" t="n">
-        <v>63.75362914924166</v>
+        <v>63.75362914924165</v>
       </c>
       <c r="N8" t="n">
-        <v>64.45377183366456</v>
+        <v>64.45377183366458</v>
       </c>
       <c r="O8" t="n">
         <v>103.4165822371214</v>
       </c>
       <c r="P8" t="n">
-        <v>95.86266647732128</v>
+        <v>95.86266647732133</v>
       </c>
       <c r="Q8" t="n">
-        <v>83.78943718957099</v>
+        <v>83.789437189571</v>
       </c>
       <c r="R8" t="n">
-        <v>80.9108485696936</v>
+        <v>80.91084856969363</v>
       </c>
       <c r="S8" t="n">
-        <v>74.14040837319688</v>
+        <v>74.14040837319683</v>
       </c>
       <c r="T8" t="n">
         <v>77.67187524887824</v>
       </c>
       <c r="U8" t="n">
-        <v>78.75396366684288</v>
+        <v>78.75396366684286</v>
       </c>
       <c r="V8" t="n">
         <v>125.7142997109812</v>
       </c>
       <c r="W8" t="n">
-        <v>126.514953232624</v>
+        <v>126.5149532326239</v>
       </c>
       <c r="X8" t="n">
         <v>121.2089115923363</v>
@@ -2305,22 +2305,22 @@
         <v>178.4559386647898</v>
       </c>
       <c r="AA8" t="n">
-        <v>165.7624110590196</v>
+        <v>165.7624110590197</v>
       </c>
       <c r="AB8" t="n">
         <v>128.1453128204851</v>
       </c>
       <c r="AC8" t="n">
-        <v>141.8083848124056</v>
+        <v>141.8083848124055</v>
       </c>
       <c r="AD8" t="n">
-        <v>156.5801394098187</v>
+        <v>156.5801394098188</v>
       </c>
       <c r="AE8" t="n">
-        <v>134.5592569463714</v>
+        <v>134.5592569463715</v>
       </c>
       <c r="AF8" t="n">
-        <v>97.54611162049459</v>
+        <v>97.54611162049457</v>
       </c>
       <c r="AG8" t="n">
         <v>125.4757951859946</v>
@@ -2335,7 +2335,7 @@
         <v>101.8026575009742</v>
       </c>
       <c r="AK8" t="n">
-        <v>99.27375227063072</v>
+        <v>99.27375227063077</v>
       </c>
       <c r="AL8" t="n">
         <v>120.9639896748585</v>
@@ -2350,10 +2350,10 @@
         <v>110.9991004188127</v>
       </c>
       <c r="AP8" t="n">
-        <v>109.6283722821635</v>
+        <v>109.6283722821634</v>
       </c>
       <c r="AQ8" t="n">
-        <v>91.09309068424339</v>
+        <v>91.09309068424334</v>
       </c>
       <c r="AR8" t="n">
         <v>105.1023021247009</v>
@@ -2362,10 +2362,10 @@
         <v>119.6925250784803</v>
       </c>
       <c r="AT8" t="n">
-        <v>178.0275097213575</v>
+        <v>178.0275097213576</v>
       </c>
       <c r="AU8" t="n">
-        <v>155.8614180825735</v>
+        <v>155.8614180825734</v>
       </c>
       <c r="AV8" t="n">
         <v>166.33906914185</v>
@@ -2380,25 +2380,25 @@
         <v>129.4759795993962</v>
       </c>
       <c r="AZ8" t="n">
-        <v>176.8000758371951</v>
+        <v>176.800075837195</v>
       </c>
       <c r="BA8" t="n">
         <v>170.1827258067195</v>
       </c>
       <c r="BB8" t="n">
-        <v>319.544428015453</v>
+        <v>319.5444280154531</v>
       </c>
       <c r="BC8" t="n">
         <v>219.9931359457752</v>
       </c>
       <c r="BD8" t="n">
-        <v>340.7134403738793</v>
+        <v>340.7134403738796</v>
       </c>
       <c r="BE8" t="n">
-        <v>182.7700552597774</v>
+        <v>182.7700552597775</v>
       </c>
       <c r="BF8" t="n">
-        <v>192.5629880154602</v>
+        <v>192.5629880154603</v>
       </c>
       <c r="BG8" t="n">
         <v>187.9652658728042</v>
@@ -2407,49 +2407,49 @@
         <v>201.3818848546065</v>
       </c>
       <c r="BI8" t="n">
-        <v>196.3180611559311</v>
+        <v>196.318061155931</v>
       </c>
       <c r="BJ8" t="n">
-        <v>209.2574803477562</v>
+        <v>209.2574803477563</v>
       </c>
       <c r="BK8" t="n">
-        <v>103.8255306017528</v>
+        <v>103.8255306017529</v>
       </c>
       <c r="BL8" t="n">
         <v>121.4117717896248</v>
       </c>
       <c r="BM8" t="n">
-        <v>128.581255117506</v>
+        <v>128.5812551175059</v>
       </c>
       <c r="BN8" t="n">
-        <v>92.84927936279972</v>
+        <v>92.84927936279969</v>
       </c>
       <c r="BO8" t="n">
-        <v>133.5407599901006</v>
+        <v>133.5407599901005</v>
       </c>
       <c r="BP8" t="n">
-        <v>164.5631685377225</v>
+        <v>164.5631685377226</v>
       </c>
       <c r="BQ8" t="n">
         <v>93.34187316634784</v>
       </c>
       <c r="BR8" t="n">
-        <v>177.2062987793514</v>
+        <v>177.2062987793513</v>
       </c>
       <c r="BS8" t="n">
-        <v>186.9444492472608</v>
+        <v>186.9444492472607</v>
       </c>
       <c r="BT8" t="n">
         <v>181.0451568225294</v>
       </c>
       <c r="BU8" t="n">
-        <v>184.81445632761</v>
+        <v>184.8144563276101</v>
       </c>
       <c r="BV8" t="n">
         <v>121.523655542962</v>
       </c>
       <c r="BW8" t="n">
-        <v>130.9066879099618</v>
+        <v>130.9066879099619</v>
       </c>
       <c r="BX8" t="n">
         <v>139.2274317582826</v>
@@ -2798,7 +2798,7 @@
         <v>109.1123406764097</v>
       </c>
       <c r="D11" t="n">
-        <v>71.57890644773207</v>
+        <v>71.57890644773205</v>
       </c>
       <c r="E11" t="n">
         <v>36.10737895848247</v>
@@ -2885,7 +2885,7 @@
         <v>26.71956385605761</v>
       </c>
       <c r="AG11" t="n">
-        <v>32.49180909022746</v>
+        <v>32.49180909022745</v>
       </c>
       <c r="AH11" t="n">
         <v>22.3063530075021</v>
@@ -2924,7 +2924,7 @@
         <v>33.11906976771949</v>
       </c>
       <c r="AT11" t="n">
-        <v>60.76674036159645</v>
+        <v>60.76674036159646</v>
       </c>
       <c r="AU11" t="n">
         <v>45.41915066391886</v>
@@ -2945,7 +2945,7 @@
         <v>9.845059625413011</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.994558773253488</v>
+        <v>8.994558773253489</v>
       </c>
       <c r="BB11" t="n">
         <v>55.27516274225574</v>
@@ -2975,7 +2975,7 @@
         <v>23.54872650596934</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.657703299153504</v>
+        <v>6.657703299153503</v>
       </c>
       <c r="BL11" t="n">
         <v>27.40215148090775</v>
@@ -3033,43 +3033,43 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.119726172884628</v>
+        <v>7.119726172884627</v>
       </c>
       <c r="D12" t="n">
-        <v>7.562475616987798</v>
+        <v>7.562475616987794</v>
       </c>
       <c r="E12" t="n">
-        <v>8.265532563734286</v>
+        <v>8.265532563734284</v>
       </c>
       <c r="F12" t="n">
-        <v>16.00799889328673</v>
+        <v>16.00799889328672</v>
       </c>
       <c r="G12" t="n">
-        <v>6.300152634979606</v>
+        <v>6.300152634979604</v>
       </c>
       <c r="H12" t="n">
-        <v>5.630198045120319</v>
+        <v>5.630198045120316</v>
       </c>
       <c r="I12" t="n">
         <v>5.887144393701476</v>
       </c>
       <c r="J12" t="n">
-        <v>7.450227006249113</v>
+        <v>7.450227006249111</v>
       </c>
       <c r="K12" t="n">
-        <v>8.055520527258805</v>
+        <v>8.055520527258803</v>
       </c>
       <c r="L12" t="n">
-        <v>6.713320876612444</v>
+        <v>6.713320876612446</v>
       </c>
       <c r="M12" t="n">
-        <v>4.892222607041882</v>
+        <v>4.892222607041884</v>
       </c>
       <c r="N12" t="n">
         <v>5.534472728367807</v>
       </c>
       <c r="O12" t="n">
-        <v>5.889875997420881</v>
+        <v>5.88987599742088</v>
       </c>
       <c r="P12" t="n">
         <v>8.461873195224177</v>
@@ -3081,25 +3081,25 @@
         <v>7.331866254835993</v>
       </c>
       <c r="S12" t="n">
-        <v>8.111145844434256</v>
+        <v>8.111145844434258</v>
       </c>
       <c r="T12" t="n">
-        <v>7.433987622870987</v>
+        <v>7.43398762287099</v>
       </c>
       <c r="U12" t="n">
-        <v>8.063799081079624</v>
+        <v>8.063799081079626</v>
       </c>
       <c r="V12" t="n">
-        <v>9.850610726158134</v>
+        <v>9.850610726158132</v>
       </c>
       <c r="W12" t="n">
         <v>10.16200164303329</v>
       </c>
       <c r="X12" t="n">
-        <v>10.03941519897694</v>
+        <v>10.03941519897695</v>
       </c>
       <c r="Y12" t="n">
-        <v>10.47011006102953</v>
+        <v>10.47011006102952</v>
       </c>
       <c r="Z12" t="n">
         <v>10.85441070434241</v>
@@ -3117,28 +3117,28 @@
         <v>10.90954260419334</v>
       </c>
       <c r="AE12" t="n">
-        <v>9.127666371125878</v>
+        <v>9.12766637112588</v>
       </c>
       <c r="AF12" t="n">
-        <v>5.601882372158089</v>
+        <v>5.601882372158085</v>
       </c>
       <c r="AG12" t="n">
-        <v>6.627505054501245</v>
+        <v>6.627505054501247</v>
       </c>
       <c r="AH12" t="n">
-        <v>5.867923417894615</v>
+        <v>5.867923417894614</v>
       </c>
       <c r="AI12" t="n">
-        <v>9.60172183201662</v>
+        <v>9.601721832016622</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9.636553016470375</v>
+        <v>9.636553016470373</v>
       </c>
       <c r="AK12" t="n">
-        <v>8.514192491464643</v>
+        <v>8.514192491464645</v>
       </c>
       <c r="AL12" t="n">
-        <v>8.982038243924656</v>
+        <v>8.982038243924654</v>
       </c>
       <c r="AM12" t="n">
         <v>7.828985586025186</v>
@@ -3153,19 +3153,19 @@
         <v>10.98133855129794</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.918029814335</v>
+        <v>5.918029814334999</v>
       </c>
       <c r="AR12" t="n">
         <v>8.642043816150816</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.427689113020834</v>
+        <v>6.427689113020836</v>
       </c>
       <c r="AT12" t="n">
         <v>10.47670249691913</v>
       </c>
       <c r="AU12" t="n">
-        <v>9.918212580541821</v>
+        <v>9.918212580541823</v>
       </c>
       <c r="AV12" t="n">
         <v>10.46723928242286</v>
@@ -3192,7 +3192,7 @@
         <v>18.80404921272088</v>
       </c>
       <c r="BD12" t="n">
-        <v>29.46518008114434</v>
+        <v>29.46518008114433</v>
       </c>
       <c r="BE12" t="n">
         <v>15.2728823420362</v>
@@ -3201,40 +3201,40 @@
         <v>10.44441464777265</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.93469884940505</v>
+        <v>9.934698849405052</v>
       </c>
       <c r="BH12" t="n">
         <v>11.82642877078547</v>
       </c>
       <c r="BI12" t="n">
-        <v>13.05479532010817</v>
+        <v>13.05479532010818</v>
       </c>
       <c r="BJ12" t="n">
-        <v>25.28616009490267</v>
+        <v>25.28616009490269</v>
       </c>
       <c r="BK12" t="n">
-        <v>22.36894723670346</v>
+        <v>22.36894723670345</v>
       </c>
       <c r="BL12" t="n">
-        <v>7.418176421548393</v>
+        <v>7.418176421548394</v>
       </c>
       <c r="BM12" t="n">
-        <v>10.6012025719302</v>
+        <v>10.60120257193019</v>
       </c>
       <c r="BN12" t="n">
-        <v>7.305559463920193</v>
+        <v>7.305559463920196</v>
       </c>
       <c r="BO12" t="n">
-        <v>9.001960857255499</v>
+        <v>9.001960857255506</v>
       </c>
       <c r="BP12" t="n">
-        <v>18.91021731681724</v>
+        <v>18.91021731681725</v>
       </c>
       <c r="BQ12" t="n">
-        <v>13.93135630752182</v>
+        <v>13.93135630752183</v>
       </c>
       <c r="BR12" t="n">
-        <v>9.074348346552325</v>
+        <v>9.074348346552322</v>
       </c>
       <c r="BS12" t="n">
         <v>11.10736995302925</v>
@@ -3252,13 +3252,13 @@
         <v>10.95104807049834</v>
       </c>
       <c r="BX12" t="n">
-        <v>9.463919591777465</v>
+        <v>9.463919591777469</v>
       </c>
       <c r="BY12" t="n">
         <v>8.750879621111334</v>
       </c>
       <c r="BZ12" t="n">
-        <v>7.559758207517535</v>
+        <v>7.559758207517533</v>
       </c>
     </row>
     <row r="13">
@@ -3482,13 +3482,13 @@
         <v>2.73724876836601</v>
       </c>
       <c r="D14" t="n">
-        <v>3.704221155906144</v>
+        <v>3.704221155906143</v>
       </c>
       <c r="E14" t="n">
-        <v>5.733964050634745</v>
+        <v>5.733964050634744</v>
       </c>
       <c r="F14" t="n">
-        <v>2.974289202623176</v>
+        <v>2.974289202623177</v>
       </c>
       <c r="G14" t="n">
         <v>2.884630251876803</v>
@@ -3497,13 +3497,13 @@
         <v>2.648520191739398</v>
       </c>
       <c r="I14" t="n">
-        <v>2.693229997986613</v>
+        <v>2.693229997986612</v>
       </c>
       <c r="J14" t="n">
         <v>4.564044002773525</v>
       </c>
       <c r="K14" t="n">
-        <v>4.589636633851855</v>
+        <v>4.589636633851856</v>
       </c>
       <c r="L14" t="n">
         <v>3.925821250462723</v>
@@ -3524,13 +3524,13 @@
         <v>2.565268812341075</v>
       </c>
       <c r="R14" t="n">
-        <v>2.681845966729322</v>
+        <v>2.681845966729323</v>
       </c>
       <c r="S14" t="n">
-        <v>2.882727258011035</v>
+        <v>2.882727258011036</v>
       </c>
       <c r="T14" t="n">
-        <v>2.844422465955987</v>
+        <v>2.844422465955986</v>
       </c>
       <c r="U14" t="n">
         <v>2.872952807615336</v>
@@ -3539,10 +3539,10 @@
         <v>3.687174620158458</v>
       </c>
       <c r="W14" t="n">
-        <v>3.783061953693559</v>
+        <v>3.78306195369356</v>
       </c>
       <c r="X14" t="n">
-        <v>3.242149192442683</v>
+        <v>3.242149192442682</v>
       </c>
       <c r="Y14" t="n">
         <v>3.709337859762214</v>
@@ -3560,37 +3560,37 @@
         <v>6.005097987926042</v>
       </c>
       <c r="AD14" t="n">
-        <v>5.725753559603687</v>
+        <v>5.725753559603689</v>
       </c>
       <c r="AE14" t="n">
-        <v>4.964500339772382</v>
+        <v>4.964500339772381</v>
       </c>
       <c r="AF14" t="n">
         <v>3.109585448738489</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.68837081736818</v>
+        <v>3.688370817368179</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.210687422774047</v>
+        <v>2.210687422774046</v>
       </c>
       <c r="AI14" t="n">
-        <v>3.751449962316108</v>
+        <v>3.751449962316109</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.656342181344685</v>
+        <v>3.656342181344686</v>
       </c>
       <c r="AK14" t="n">
-        <v>5.835227707618187</v>
+        <v>5.835227707618188</v>
       </c>
       <c r="AL14" t="n">
-        <v>6.470751522744525</v>
+        <v>6.470751522744527</v>
       </c>
       <c r="AM14" t="n">
-        <v>5.852555910684663</v>
+        <v>5.852555910684661</v>
       </c>
       <c r="AN14" t="n">
-        <v>4.216924019479624</v>
+        <v>4.216924019479625</v>
       </c>
       <c r="AO14" t="n">
         <v>3.926920303068532</v>
@@ -3599,37 +3599,37 @@
         <v>3.880133397930334</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.278521063401073</v>
+        <v>3.278521063401074</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.274742080522753</v>
+        <v>4.274742080522755</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.529821224588816</v>
+        <v>3.529821224588815</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.558051863919309</v>
+        <v>4.55805186391931</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.13816341990676</v>
+        <v>4.138163419906759</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.784626429883469</v>
+        <v>3.784626429883467</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.585258363964559</v>
+        <v>9.585258363964558</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.03088023266143</v>
+        <v>4.030880232661431</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.809455031417992</v>
+        <v>4.809455031417994</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.291095192098194</v>
+        <v>4.291095192098195</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.52973792662524</v>
+        <v>4.529737926625241</v>
       </c>
       <c r="BB14" t="n">
         <v>16.09809485407839</v>
@@ -3644,10 +3644,10 @@
         <v>8.205433146633949</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.068399123847305</v>
+        <v>7.068399123847304</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.855215211366761</v>
+        <v>6.855215211366762</v>
       </c>
       <c r="BH14" t="n">
         <v>7.97063963125983</v>
@@ -3656,7 +3656,7 @@
         <v>7.86255733759717</v>
       </c>
       <c r="BJ14" t="n">
-        <v>6.247833745439516</v>
+        <v>6.247833745439517</v>
       </c>
       <c r="BK14" t="n">
         <v>4.407094868010319</v>
@@ -3671,10 +3671,10 @@
         <v>4.669798646290508</v>
       </c>
       <c r="BO14" t="n">
-        <v>6.451691336322647</v>
+        <v>6.451691336322648</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.715240122410268</v>
+        <v>4.715240122410269</v>
       </c>
       <c r="BQ14" t="n">
         <v>3.633698415573896</v>
@@ -3683,7 +3683,7 @@
         <v>8.505614995591266</v>
       </c>
       <c r="BS14" t="n">
-        <v>9.435425174693316</v>
+        <v>9.435425174693318</v>
       </c>
       <c r="BT14" t="n">
         <v>11.59156058932542</v>
@@ -3692,7 +3692,7 @@
         <v>12.40539659886712</v>
       </c>
       <c r="BV14" t="n">
-        <v>8.770307620867035</v>
+        <v>8.770307620867031</v>
       </c>
       <c r="BW14" t="n">
         <v>9.046576423086764</v>
@@ -3704,7 +3704,7 @@
         <v>6.371166486169979</v>
       </c>
       <c r="BZ14" t="n">
-        <v>5.180768893884784</v>
+        <v>5.180768893884783</v>
       </c>
     </row>
     <row r="15">
@@ -3720,7 +3720,7 @@
         <v>0.2141355587050488</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4762577253376878</v>
+        <v>0.4762577253376879</v>
       </c>
       <c r="E15" t="n">
         <v>0.8457692128378944</v>
@@ -3735,10 +3735,10 @@
         <v>0.3609343114119035</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3524040953363319</v>
+        <v>0.352404095336332</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6391550807181735</v>
+        <v>0.6391550807181736</v>
       </c>
       <c r="K15" t="n">
         <v>0.6338891872736576</v>
@@ -3768,7 +3768,7 @@
         <v>0.3353850574343637</v>
       </c>
       <c r="T15" t="n">
-        <v>0.323477598168387</v>
+        <v>0.3234775981683869</v>
       </c>
       <c r="U15" t="n">
         <v>0.3515393695103547</v>
@@ -3789,7 +3789,7 @@
         <v>0.2838597681689801</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.3264662012740701</v>
+        <v>0.3264662012740702</v>
       </c>
       <c r="AB15" t="n">
         <v>0.7523043379194488</v>
@@ -3801,7 +3801,7 @@
         <v>0.7814367727596728</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.6188649343870437</v>
+        <v>0.6188649343870438</v>
       </c>
       <c r="AF15" t="n">
         <v>0.3988540266766732</v>
@@ -3813,7 +3813,7 @@
         <v>0.3172475349773055</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.5267908516430569</v>
+        <v>0.5267908516430568</v>
       </c>
       <c r="AJ15" t="n">
         <v>0.5115309294385684</v>
@@ -3828,16 +3828,16 @@
         <v>1.010560486986219</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.583481579597531</v>
+        <v>0.5834815795975311</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.5604060994399281</v>
+        <v>0.560406099439928</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.5903630456534886</v>
+        <v>0.5903630456534887</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.4121821277562304</v>
+        <v>0.4121821277562303</v>
       </c>
       <c r="AR15" t="n">
         <v>0.5529271091679383</v>
@@ -3849,10 +3849,10 @@
         <v>0.6048447636980984</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.5659736283533133</v>
+        <v>0.5659736283533134</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.528114873340789</v>
+        <v>0.5281148733407889</v>
       </c>
       <c r="AW15" t="n">
         <v>5.134574309742404</v>
@@ -3900,7 +3900,7 @@
         <v>0.3059166807251252</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.6474337372942078</v>
+        <v>0.6474337372942079</v>
       </c>
       <c r="BM15" t="n">
         <v>0.7532684054466222</v>
@@ -3958,22 +3958,22 @@
         <v>2.764788758207688</v>
       </c>
       <c r="D16" t="n">
-        <v>2.723315416834915</v>
+        <v>2.723315416834916</v>
       </c>
       <c r="E16" t="n">
         <v>2.43346234594654</v>
       </c>
       <c r="F16" t="n">
-        <v>4.26062684986552</v>
+        <v>4.260626849865521</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8124514881825599</v>
+        <v>0.8124514881825597</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7154757840337829</v>
+        <v>0.7154757840337828</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7139322407803499</v>
+        <v>0.7139322407803498</v>
       </c>
       <c r="J16" t="n">
         <v>1.009737764865348</v>
@@ -3982,7 +3982,7 @@
         <v>1.012074915584269</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9766898359896262</v>
+        <v>0.9766898359896261</v>
       </c>
       <c r="M16" t="n">
         <v>0.7372624115443583</v>
@@ -3997,7 +3997,7 @@
         <v>1.155136176515937</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9995277457088557</v>
+        <v>0.9995277457088556</v>
       </c>
       <c r="R16" t="n">
         <v>1.017886090537425</v>
@@ -4012,7 +4012,7 @@
         <v>1.209360961959842</v>
       </c>
       <c r="V16" t="n">
-        <v>1.655683458871786</v>
+        <v>1.655683458871785</v>
       </c>
       <c r="W16" t="n">
         <v>1.586713660356731</v>
@@ -4036,7 +4036,7 @@
         <v>1.448141701905931</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.629813329593891</v>
+        <v>1.629813329593892</v>
       </c>
       <c r="AE16" t="n">
         <v>1.916818198883434</v>
@@ -4048,13 +4048,13 @@
         <v>1.433603652264322</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.7119813805904935</v>
+        <v>0.7119813805904937</v>
       </c>
       <c r="AI16" t="n">
         <v>1.232726099951339</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.251918500717989</v>
+        <v>1.251918500717988</v>
       </c>
       <c r="AK16" t="n">
         <v>1.166014605838879</v>
@@ -4066,7 +4066,7 @@
         <v>1.264165274572487</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.449179112906696</v>
+        <v>1.449179112906695</v>
       </c>
       <c r="AO16" t="n">
         <v>1.27747482265898</v>
@@ -4084,7 +4084,7 @@
         <v>1.493492289087764</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.219925780238131</v>
+        <v>1.219925780238132</v>
       </c>
       <c r="AU16" t="n">
         <v>1.331219911601964</v>
@@ -4099,7 +4099,7 @@
         <v>5.355222210901932</v>
       </c>
       <c r="AY16" t="n">
-        <v>5.914124439593171</v>
+        <v>5.91412443959317</v>
       </c>
       <c r="AZ16" t="n">
         <v>3.606876721446517</v>
@@ -4117,7 +4117,7 @@
         <v>5.381838255159439</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.206186584302378</v>
+        <v>3.206186584302377</v>
       </c>
       <c r="BF16" t="n">
         <v>2.799894862469773</v>
@@ -4138,7 +4138,7 @@
         <v>1.366914610038924</v>
       </c>
       <c r="BL16" t="n">
-        <v>2.097597127301286</v>
+        <v>2.097597127301287</v>
       </c>
       <c r="BM16" t="n">
         <v>2.713805059357085</v>
@@ -4159,7 +4159,7 @@
         <v>2.205886061300476</v>
       </c>
       <c r="BS16" t="n">
-        <v>2.332814489349351</v>
+        <v>2.332814489349352</v>
       </c>
       <c r="BT16" t="n">
         <v>2.887490339374105</v>
@@ -4177,7 +4177,7 @@
         <v>2.573908180514377</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.915193052091158</v>
+        <v>2.915193052091159</v>
       </c>
       <c r="BZ16" t="n">
         <v>2.713505396286902</v>
@@ -4217,10 +4217,10 @@
         <v>0.5791992035854638</v>
       </c>
       <c r="K17" t="n">
-        <v>0.668553208504458</v>
+        <v>0.6685532085044581</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4697057072433492</v>
+        <v>0.4697057072433491</v>
       </c>
       <c r="M17" t="n">
         <v>1.344165002528123</v>
@@ -4265,16 +4265,16 @@
         <v>1.61976681551037</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.066300982460668</v>
+        <v>2.066300982460669</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8517357928110729</v>
+        <v>0.8517357928110728</v>
       </c>
       <c r="AC17" t="n">
         <v>1.056416984442829</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.9712850494304834</v>
+        <v>0.9712850494304833</v>
       </c>
       <c r="AE17" t="n">
         <v>0.739308089192848</v>
@@ -4292,16 +4292,16 @@
         <v>2.569738971781009</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.623080545222472</v>
+        <v>2.623080545222473</v>
       </c>
       <c r="AK17" t="n">
         <v>0.6811707184867224</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.6958605867676407</v>
+        <v>0.6958605867676406</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.6292882534720073</v>
+        <v>0.6292882534720072</v>
       </c>
       <c r="AN17" t="n">
         <v>3.0545092456606</v>
@@ -4313,7 +4313,7 @@
         <v>3.07269880998091</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.5845843812738989</v>
+        <v>0.5845843812738988</v>
       </c>
       <c r="AR17" t="n">
         <v>0.9229575246364823</v>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.773590170198471</v>
+        <v>0.7735901701984709</v>
       </c>
       <c r="D19" t="n">
         <v>0.4653190711638118</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6354157249715495</v>
+        <v>0.6354157249715496</v>
       </c>
       <c r="F19" t="n">
         <v>0.9927081126518774</v>
@@ -4682,7 +4682,7 @@
         <v>0.3418049884001831</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2907420031991489</v>
+        <v>0.2907420031991488</v>
       </c>
       <c r="I19" t="n">
         <v>0.3191355292054479</v>
@@ -4691,7 +4691,7 @@
         <v>0.4748873159214426</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5098564734812682</v>
+        <v>0.5098564734812681</v>
       </c>
       <c r="L19" t="n">
         <v>0.4667664620544784</v>
@@ -4706,7 +4706,7 @@
         <v>0.2896215011103337</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4806015289204242</v>
+        <v>0.4806015289204243</v>
       </c>
       <c r="Q19" t="n">
         <v>0.4415567328317749</v>
@@ -4718,7 +4718,7 @@
         <v>0.5189221747614976</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4932316467151615</v>
+        <v>0.4932316467151616</v>
       </c>
       <c r="U19" t="n">
         <v>0.5279835392326815</v>
@@ -4727,13 +4727,13 @@
         <v>0.6250566525898158</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6248527813230847</v>
+        <v>0.6248527813230849</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7050414552900591</v>
+        <v>0.7050414552900592</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.7671810839113076</v>
+        <v>0.7671810839113075</v>
       </c>
       <c r="Z19" t="n">
         <v>0.7960540655631346</v>
@@ -4745,7 +4745,7 @@
         <v>0.7258113855923976</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.8558752339417144</v>
+        <v>0.8558752339417145</v>
       </c>
       <c r="AD19" t="n">
         <v>0.9544875256437206</v>
@@ -4757,19 +4757,19 @@
         <v>0.3974905251816701</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.4394168787648108</v>
+        <v>0.4394168787648107</v>
       </c>
       <c r="AH19" t="n">
         <v>0.2606173880878815</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.469336230738601</v>
+        <v>0.4693362307386009</v>
       </c>
       <c r="AJ19" t="n">
         <v>0.52162152759967</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.5330655620993264</v>
+        <v>0.5330655620993263</v>
       </c>
       <c r="AL19" t="n">
         <v>0.6500112485566993</v>
@@ -4784,13 +4784,13 @@
         <v>0.5176817344896936</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.5955892894687894</v>
+        <v>0.5955892894687896</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.4172483852531025</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.6289307361912628</v>
+        <v>0.6289307361912629</v>
       </c>
       <c r="AS19" t="n">
         <v>0.3974562568167097</v>
@@ -4802,7 +4802,7 @@
         <v>0.6119155553896698</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.5921032006758042</v>
+        <v>0.5921032006758041</v>
       </c>
       <c r="AW19" t="n">
         <v>0.2659834321575075</v>
@@ -4811,7 +4811,7 @@
         <v>0.7630743723782317</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.9918745085507769</v>
+        <v>0.9918745085507767</v>
       </c>
       <c r="AZ19" t="n">
         <v>0.6108120080821583</v>
@@ -4862,7 +4862,7 @@
         <v>0.1554565297458091</v>
       </c>
       <c r="BP19" t="n">
-        <v>1.614962049962966</v>
+        <v>1.614962049962967</v>
       </c>
       <c r="BQ19" t="n">
         <v>1.320641510840016</v>
@@ -5465,25 +5465,25 @@
         <v>74.46818141774904</v>
       </c>
       <c r="E23" t="n">
-        <v>39.34584203933981</v>
+        <v>39.3458420393398</v>
       </c>
       <c r="F23" t="n">
-        <v>41.95366035123352</v>
+        <v>41.95366035123351</v>
       </c>
       <c r="G23" t="n">
         <v>26.87321717524441</v>
       </c>
       <c r="H23" t="n">
-        <v>21.41389844644234</v>
+        <v>21.41389844644233</v>
       </c>
       <c r="I23" t="n">
         <v>18.47414650033026</v>
       </c>
       <c r="J23" t="n">
-        <v>21.439802838708</v>
+        <v>21.43980283870801</v>
       </c>
       <c r="K23" t="n">
-        <v>20.578819817554</v>
+        <v>20.57881981755401</v>
       </c>
       <c r="L23" t="n">
         <v>19.68671415745135</v>
@@ -5495,61 +5495,61 @@
         <v>14.27715689184966</v>
       </c>
       <c r="O23" t="n">
-        <v>38.19854184731547</v>
+        <v>38.19854184731548</v>
       </c>
       <c r="P23" t="n">
-        <v>29.09293322891898</v>
+        <v>29.09293322891899</v>
       </c>
       <c r="Q23" t="n">
         <v>24.42270259705824</v>
       </c>
       <c r="R23" t="n">
-        <v>23.00401462267707</v>
+        <v>23.00401462267708</v>
       </c>
       <c r="S23" t="n">
         <v>19.72058261024681</v>
       </c>
       <c r="T23" t="n">
-        <v>21.99508738517611</v>
+        <v>21.99508738517612</v>
       </c>
       <c r="U23" t="n">
-        <v>19.35975687148133</v>
+        <v>19.35975687148134</v>
       </c>
       <c r="V23" t="n">
-        <v>36.73156940755081</v>
+        <v>36.73156940755083</v>
       </c>
       <c r="W23" t="n">
-        <v>38.13961512036102</v>
+        <v>38.13961512036101</v>
       </c>
       <c r="X23" t="n">
         <v>36.01378592008253</v>
       </c>
       <c r="Y23" t="n">
-        <v>47.954071090569</v>
+        <v>47.95407109056902</v>
       </c>
       <c r="Z23" t="n">
-        <v>62.47586000875876</v>
+        <v>62.47586000875877</v>
       </c>
       <c r="AA23" t="n">
-        <v>51.40054702504175</v>
+        <v>51.40054702504174</v>
       </c>
       <c r="AB23" t="n">
         <v>18.69342771522822</v>
       </c>
       <c r="AC23" t="n">
-        <v>24.89015482015798</v>
+        <v>24.89015482015797</v>
       </c>
       <c r="AD23" t="n">
         <v>29.7944279067285</v>
       </c>
       <c r="AE23" t="n">
-        <v>32.02601838215919</v>
+        <v>32.02601838215921</v>
       </c>
       <c r="AF23" t="n">
         <v>28.80526633110571</v>
       </c>
       <c r="AG23" t="n">
-        <v>34.5478620878866</v>
+        <v>34.54786208788661</v>
       </c>
       <c r="AH23" t="n">
         <v>24.74845956415302</v>
@@ -5558,34 +5558,34 @@
         <v>37.25685060014577</v>
       </c>
       <c r="AJ23" t="n">
-        <v>30.39395369418603</v>
+        <v>30.39395369418602</v>
       </c>
       <c r="AK23" t="n">
         <v>23.04313486797042</v>
       </c>
       <c r="AL23" t="n">
-        <v>24.46194013129456</v>
+        <v>24.46194013129455</v>
       </c>
       <c r="AM23" t="n">
         <v>22.95735330478274</v>
       </c>
       <c r="AN23" t="n">
-        <v>32.69313227740231</v>
+        <v>32.6931322774023</v>
       </c>
       <c r="AO23" t="n">
         <v>33.83385132245898</v>
       </c>
       <c r="AP23" t="n">
-        <v>34.76916181143744</v>
+        <v>34.76916181143743</v>
       </c>
       <c r="AQ23" t="n">
-        <v>23.02030589020388</v>
+        <v>23.02030589020389</v>
       </c>
       <c r="AR23" t="n">
-        <v>26.22333568261249</v>
+        <v>26.22333568261248</v>
       </c>
       <c r="AS23" t="n">
-        <v>35.83072811848899</v>
+        <v>35.83072811848898</v>
       </c>
       <c r="AT23" t="n">
         <v>64.84761631768939</v>
@@ -5594,37 +5594,37 @@
         <v>48.8737101695546</v>
       </c>
       <c r="AV23" t="n">
-        <v>55.39613793815888</v>
+        <v>55.39613793815887</v>
       </c>
       <c r="AW23" t="n">
-        <v>59.21691419238611</v>
+        <v>59.21691419238613</v>
       </c>
       <c r="AX23" t="n">
-        <v>8.228715909647899</v>
+        <v>8.228715909647898</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.73846347937414</v>
+        <v>9.738463479374142</v>
       </c>
       <c r="AZ23" t="n">
         <v>15.42660757304842</v>
       </c>
       <c r="BA23" t="n">
-        <v>15.72785877373015</v>
+        <v>15.72785877373014</v>
       </c>
       <c r="BB23" t="n">
-        <v>69.84836341056908</v>
+        <v>69.84836341056911</v>
       </c>
       <c r="BC23" t="n">
-        <v>50.77743693856382</v>
+        <v>50.77743693856383</v>
       </c>
       <c r="BD23" t="n">
         <v>81.0366459704161</v>
       </c>
       <c r="BE23" t="n">
-        <v>40.71822344716204</v>
+        <v>40.71822344716205</v>
       </c>
       <c r="BF23" t="n">
-        <v>36.6300878243273</v>
+        <v>36.63008782432729</v>
       </c>
       <c r="BG23" t="n">
         <v>35.41292779387459</v>
@@ -5633,7 +5633,7 @@
         <v>39.14844808806887</v>
       </c>
       <c r="BI23" t="n">
-        <v>38.48171489413817</v>
+        <v>38.48171489413816</v>
       </c>
       <c r="BJ23" t="n">
         <v>36.25140306054632</v>
@@ -5648,22 +5648,22 @@
         <v>13.54686600387851</v>
       </c>
       <c r="BN23" t="n">
-        <v>9.777613208107233</v>
+        <v>9.777613208107235</v>
       </c>
       <c r="BO23" t="n">
         <v>14.73438081215211</v>
       </c>
       <c r="BP23" t="n">
-        <v>34.35521399945724</v>
+        <v>34.35521399945725</v>
       </c>
       <c r="BQ23" t="n">
-        <v>21.4022580181175</v>
+        <v>21.40225801811749</v>
       </c>
       <c r="BR23" t="n">
-        <v>40.19329232127687</v>
+        <v>40.19329232127688</v>
       </c>
       <c r="BS23" t="n">
-        <v>42.68753407174446</v>
+        <v>42.68753407174445</v>
       </c>
       <c r="BT23" t="n">
         <v>39.24046385676996</v>
@@ -5678,13 +5678,13 @@
         <v>21.6589355290675</v>
       </c>
       <c r="BX23" t="n">
-        <v>21.99078510037637</v>
+        <v>21.99078510037636</v>
       </c>
       <c r="BY23" t="n">
         <v>22.52213602124543</v>
       </c>
       <c r="BZ23" t="n">
-        <v>20.38133544839189</v>
+        <v>20.3813354483919</v>
       </c>
     </row>
     <row r="24">
@@ -5968,7 +5968,7 @@
         <v>0.0397353698936833</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0.07996147621114072</v>
+        <v>0.07996147621114071</v>
       </c>
       <c r="BK25" t="n">
         <v>0.004029802339128698</v>
@@ -5989,7 +5989,7 @@
         <v>0.2047134901343432</v>
       </c>
       <c r="BQ25" t="n">
-        <v>0.08454957718153258</v>
+        <v>0.0845495771815326</v>
       </c>
       <c r="BR25" t="n">
         <v>0.2705023812849059</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02496779118561095</v>
+        <v>0.02496779118561094</v>
       </c>
       <c r="D28" t="n">
         <v>0.03279589746970663</v>
@@ -6524,10 +6524,10 @@
         <v>0.01674693836741102</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02041948418743295</v>
+        <v>0.02041948418743296</v>
       </c>
       <c r="K28" t="n">
-        <v>0.02383187591862816</v>
+        <v>0.02383187591862817</v>
       </c>
       <c r="L28" t="n">
         <v>0.01817993980764078</v>
@@ -6584,16 +6584,16 @@
         <v>0.03909412180269181</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.03866445418033426</v>
+        <v>0.03866445418033427</v>
       </c>
       <c r="AE28" t="n">
         <v>0.03101485914238943</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.01567166527401465</v>
+        <v>0.01567166527401466</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.01911110067942386</v>
+        <v>0.01911110067942385</v>
       </c>
       <c r="AH28" t="n">
         <v>0.01120018774125572</v>
@@ -6608,7 +6608,7 @@
         <v>0.02292177750433327</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.02479658318457519</v>
+        <v>0.02479658318457518</v>
       </c>
       <c r="AM28" t="n">
         <v>0.02026089217713677</v>
@@ -6680,10 +6680,10 @@
         <v>0.01777739244926321</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0.2261266849359631</v>
+        <v>0.226126684935963</v>
       </c>
       <c r="BK28" t="n">
-        <v>0.08151875088265327</v>
+        <v>0.08151875088265326</v>
       </c>
       <c r="BL28" t="n">
         <v>0.06092741148896894</v>
@@ -6738,58 +6738,58 @@
         <v>30.87886282575769</v>
       </c>
       <c r="F29" t="n">
-        <v>8.325835261231596</v>
+        <v>8.325835261231592</v>
       </c>
       <c r="G29" t="n">
-        <v>7.376694375621586</v>
+        <v>7.376694375621585</v>
       </c>
       <c r="H29" t="n">
-        <v>7.052943728629351</v>
+        <v>7.052943728629352</v>
       </c>
       <c r="I29" t="n">
-        <v>6.873757950931458</v>
+        <v>6.873757950931459</v>
       </c>
       <c r="J29" t="n">
         <v>6.04708063078375</v>
       </c>
       <c r="K29" t="n">
-        <v>6.150257176760142</v>
+        <v>6.15025717676014</v>
       </c>
       <c r="L29" t="n">
-        <v>5.672490200199409</v>
+        <v>5.67249020019941</v>
       </c>
       <c r="M29" t="n">
-        <v>6.377406071975503</v>
+        <v>6.377406071975502</v>
       </c>
       <c r="N29" t="n">
-        <v>7.535407480987432</v>
+        <v>7.535407480987431</v>
       </c>
       <c r="O29" t="n">
-        <v>5.382090518941816</v>
+        <v>5.382090518941815</v>
       </c>
       <c r="P29" t="n">
-        <v>7.117313832367343</v>
+        <v>7.117313832367344</v>
       </c>
       <c r="Q29" t="n">
         <v>6.273954458848543</v>
       </c>
       <c r="R29" t="n">
-        <v>7.289656842156029</v>
+        <v>7.28965684215603</v>
       </c>
       <c r="S29" t="n">
-        <v>7.635971385794095</v>
+        <v>7.635971385794096</v>
       </c>
       <c r="T29" t="n">
         <v>7.188252160831983</v>
       </c>
       <c r="U29" t="n">
-        <v>7.629187385918094</v>
+        <v>7.629187385918093</v>
       </c>
       <c r="V29" t="n">
-        <v>9.796761601627823</v>
+        <v>9.796761601627827</v>
       </c>
       <c r="W29" t="n">
-        <v>10.10014008697769</v>
+        <v>10.1001400869777</v>
       </c>
       <c r="X29" t="n">
         <v>10.02052308521086</v>
@@ -6798,7 +6798,7 @@
         <v>10.75954557297328</v>
       </c>
       <c r="Z29" t="n">
-        <v>9.078892014128511</v>
+        <v>9.078892014128515</v>
       </c>
       <c r="AA29" t="n">
         <v>11.31577428483735</v>
@@ -6816,10 +6816,10 @@
         <v>6.67549139471893</v>
       </c>
       <c r="AF29" t="n">
-        <v>3.984893458974789</v>
+        <v>3.984893458974788</v>
       </c>
       <c r="AG29" t="n">
-        <v>4.585712940422376</v>
+        <v>4.585712940422375</v>
       </c>
       <c r="AH29" t="n">
         <v>3.65765646351508</v>
@@ -6831,22 +6831,22 @@
         <v>7.181181049163306</v>
       </c>
       <c r="AK29" t="n">
-        <v>7.835168699620397</v>
+        <v>7.835168699620398</v>
       </c>
       <c r="AL29" t="n">
         <v>9.065252650103218</v>
       </c>
       <c r="AM29" t="n">
-        <v>8.608972756430436</v>
+        <v>8.608972756430434</v>
       </c>
       <c r="AN29" t="n">
-        <v>9.964896279546753</v>
+        <v>9.96489627954675</v>
       </c>
       <c r="AO29" t="n">
-        <v>8.941477713491278</v>
+        <v>8.941477713491276</v>
       </c>
       <c r="AP29" t="n">
-        <v>9.22277351404489</v>
+        <v>9.222773514044897</v>
       </c>
       <c r="AQ29" t="n">
         <v>4.485246139310101</v>
@@ -6855,25 +6855,25 @@
         <v>6.119578602800318</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.210639945215737</v>
+        <v>4.210639945215738</v>
       </c>
       <c r="AT29" t="n">
-        <v>7.816067522293454</v>
+        <v>7.816067522293453</v>
       </c>
       <c r="AU29" t="n">
         <v>9.842537146621359</v>
       </c>
       <c r="AV29" t="n">
-        <v>9.671444603464762</v>
+        <v>9.671444603464764</v>
       </c>
       <c r="AW29" t="n">
         <v>8.025790058533612</v>
       </c>
       <c r="AX29" t="n">
-        <v>8.704266239912199</v>
+        <v>8.704266239912197</v>
       </c>
       <c r="AY29" t="n">
-        <v>8.469150264784105</v>
+        <v>8.469150264784103</v>
       </c>
       <c r="AZ29" t="n">
         <v>10.39551234444018</v>
@@ -6885,13 +6885,13 @@
         <v>10.3775485876845</v>
       </c>
       <c r="BC29" t="n">
-        <v>6.248727779797544</v>
+        <v>6.248727779797543</v>
       </c>
       <c r="BD29" t="n">
         <v>11.33463064424723</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.073161151188094</v>
+        <v>5.073161151188097</v>
       </c>
       <c r="BF29" t="n">
         <v>10.35438068201418</v>
@@ -6900,22 +6900,22 @@
         <v>9.223294252680843</v>
       </c>
       <c r="BH29" t="n">
-        <v>10.03404578998274</v>
+        <v>10.03404578998275</v>
       </c>
       <c r="BI29" t="n">
         <v>11.77198090801089</v>
       </c>
       <c r="BJ29" t="n">
-        <v>13.16254681169556</v>
+        <v>13.16254681169557</v>
       </c>
       <c r="BK29" t="n">
-        <v>4.644438582975664</v>
+        <v>4.644438582975665</v>
       </c>
       <c r="BL29" t="n">
-        <v>5.465601750023422</v>
+        <v>5.465601750023418</v>
       </c>
       <c r="BM29" t="n">
-        <v>3.050223389716581</v>
+        <v>3.050223389716582</v>
       </c>
       <c r="BN29" t="n">
         <v>2.493341680164959</v>
@@ -6927,31 +6927,31 @@
         <v>12.23926758331609</v>
       </c>
       <c r="BQ29" t="n">
-        <v>8.553671156333399</v>
+        <v>8.553671156333396</v>
       </c>
       <c r="BR29" t="n">
-        <v>4.63760934656404</v>
+        <v>4.637609346564038</v>
       </c>
       <c r="BS29" t="n">
         <v>4.728767456709005</v>
       </c>
       <c r="BT29" t="n">
-        <v>5.47826062580514</v>
+        <v>5.478260625805139</v>
       </c>
       <c r="BU29" t="n">
         <v>6.149724558856949</v>
       </c>
       <c r="BV29" t="n">
-        <v>4.76393654281641</v>
+        <v>4.763936542816409</v>
       </c>
       <c r="BW29" t="n">
         <v>5.453232129809765</v>
       </c>
       <c r="BX29" t="n">
-        <v>5.657043774645457</v>
+        <v>5.657043774645458</v>
       </c>
       <c r="BY29" t="n">
-        <v>5.542175727669366</v>
+        <v>5.542175727669365</v>
       </c>
       <c r="BZ29" t="n">
         <v>5.087747021317211</v>
@@ -7145,19 +7145,19 @@
         <v>17.42233156021145</v>
       </c>
       <c r="E32" t="n">
-        <v>14.32049854292889</v>
+        <v>14.3204985429289</v>
       </c>
       <c r="F32" t="n">
-        <v>23.63133560734494</v>
+        <v>23.63133560734495</v>
       </c>
       <c r="G32" t="n">
-        <v>8.468343413740573</v>
+        <v>8.468343413740572</v>
       </c>
       <c r="H32" t="n">
         <v>7.778266700311579</v>
       </c>
       <c r="I32" t="n">
-        <v>9.015659182562825</v>
+        <v>9.015659182562823</v>
       </c>
       <c r="J32" t="n">
         <v>14.86539938074984</v>
@@ -7172,10 +7172,10 @@
         <v>7.491877414826924</v>
       </c>
       <c r="N32" t="n">
-        <v>8.338512298542019</v>
+        <v>8.338512298542017</v>
       </c>
       <c r="O32" t="n">
-        <v>9.780281058583844</v>
+        <v>9.780281058583842</v>
       </c>
       <c r="P32" t="n">
         <v>10.16893999904383</v>
@@ -7184,10 +7184,10 @@
         <v>8.761073891162685</v>
       </c>
       <c r="R32" t="n">
-        <v>8.853203063371746</v>
+        <v>8.853203063371748</v>
       </c>
       <c r="S32" t="n">
-        <v>9.815987296287965</v>
+        <v>9.815987296287968</v>
       </c>
       <c r="T32" t="n">
         <v>10.08502083889389</v>
@@ -7205,34 +7205,34 @@
         <v>15.70415447255984</v>
       </c>
       <c r="Y32" t="n">
-        <v>19.54203183642952</v>
+        <v>19.54203183642951</v>
       </c>
       <c r="Z32" t="n">
         <v>22.35185919439449</v>
       </c>
       <c r="AA32" t="n">
-        <v>20.04563192463347</v>
+        <v>20.04563192463346</v>
       </c>
       <c r="AB32" t="n">
-        <v>30.5381236207475</v>
+        <v>30.53812362074749</v>
       </c>
       <c r="AC32" t="n">
-        <v>36.6361025539093</v>
+        <v>36.63610255390932</v>
       </c>
       <c r="AD32" t="n">
-        <v>39.52941046999604</v>
+        <v>39.52941046999605</v>
       </c>
       <c r="AE32" t="n">
-        <v>23.59368008502963</v>
+        <v>23.59368008502962</v>
       </c>
       <c r="AF32" t="n">
         <v>10.78000777276084</v>
       </c>
       <c r="AG32" t="n">
-        <v>13.6593858566314</v>
+        <v>13.65938585663139</v>
       </c>
       <c r="AH32" t="n">
-        <v>7.37918364208887</v>
+        <v>7.379183642088871</v>
       </c>
       <c r="AI32" t="n">
         <v>13.23397876323568</v>
@@ -7247,7 +7247,7 @@
         <v>21.49719265766768</v>
       </c>
       <c r="AM32" t="n">
-        <v>16.6214386656781</v>
+        <v>16.62143866567809</v>
       </c>
       <c r="AN32" t="n">
         <v>17.17541846560081</v>
@@ -7268,10 +7268,10 @@
         <v>11.1323187459061</v>
       </c>
       <c r="AT32" t="n">
-        <v>17.94911619783908</v>
+        <v>17.94911619783907</v>
       </c>
       <c r="AU32" t="n">
-        <v>17.0316023680758</v>
+        <v>17.03160236807579</v>
       </c>
       <c r="AV32" t="n">
         <v>16.18446120001957</v>
@@ -7310,7 +7310,7 @@
         <v>32.09204807803057</v>
       </c>
       <c r="BH32" t="n">
-        <v>34.12382462167718</v>
+        <v>34.12382462167717</v>
       </c>
       <c r="BI32" t="n">
         <v>33.51396658970302</v>
@@ -7337,10 +7337,10 @@
         <v>13.85098914626856</v>
       </c>
       <c r="BQ32" t="n">
-        <v>10.93948151061719</v>
+        <v>10.93948151061718</v>
       </c>
       <c r="BR32" t="n">
-        <v>13.38224545073877</v>
+        <v>13.38224545073876</v>
       </c>
       <c r="BS32" t="n">
         <v>14.53882443966239</v>
@@ -7349,16 +7349,16 @@
         <v>18.73231596986327</v>
       </c>
       <c r="BU32" t="n">
-        <v>23.23785805428639</v>
+        <v>23.23785805428638</v>
       </c>
       <c r="BV32" t="n">
         <v>19.52532492154688</v>
       </c>
       <c r="BW32" t="n">
-        <v>24.21825101774529</v>
+        <v>24.21825101774528</v>
       </c>
       <c r="BX32" t="n">
-        <v>26.4385531973555</v>
+        <v>26.43855319735551</v>
       </c>
       <c r="BY32" t="n">
         <v>27.40609509648244</v>
@@ -7401,7 +7401,7 @@
         <v>27.81541999240339</v>
       </c>
       <c r="K33" t="n">
-        <v>32.40427873225659</v>
+        <v>32.40427873225658</v>
       </c>
       <c r="L33" t="n">
         <v>20.78049940610539</v>
@@ -7425,7 +7425,7 @@
         <v>18.84790844797517</v>
       </c>
       <c r="S33" t="n">
-        <v>16.04833633530009</v>
+        <v>16.0483363353001</v>
       </c>
       <c r="T33" t="n">
         <v>16.96927614894433</v>
@@ -7434,10 +7434,10 @@
         <v>20.30827904260996</v>
       </c>
       <c r="V33" t="n">
-        <v>26.61806908782124</v>
+        <v>26.61806908782123</v>
       </c>
       <c r="W33" t="n">
-        <v>27.54012582156906</v>
+        <v>27.54012582156907</v>
       </c>
       <c r="X33" t="n">
         <v>23.66599454387799</v>
@@ -7452,10 +7452,10 @@
         <v>26.96252760163028</v>
       </c>
       <c r="AB33" t="n">
-        <v>47.08102830840534</v>
+        <v>47.08102830840533</v>
       </c>
       <c r="AC33" t="n">
-        <v>54.20790264344375</v>
+        <v>54.20790264344377</v>
       </c>
       <c r="AD33" t="n">
         <v>56.26689771271553</v>
@@ -7527,7 +7527,7 @@
         <v>32.23437670272448</v>
       </c>
       <c r="BA33" t="n">
-        <v>31.93431115043353</v>
+        <v>31.93431115043354</v>
       </c>
       <c r="BB33" t="n">
         <v>37.94093105896926</v>
@@ -7536,7 +7536,7 @@
         <v>24.73851131124484</v>
       </c>
       <c r="BD33" t="n">
-        <v>39.19409304135492</v>
+        <v>39.19409304135491</v>
       </c>
       <c r="BE33" t="n">
         <v>20.43734217357522</v>
@@ -7554,7 +7554,7 @@
         <v>21.23324450615404</v>
       </c>
       <c r="BJ33" t="n">
-        <v>15.98166079660193</v>
+        <v>15.98166079660192</v>
       </c>
       <c r="BK33" t="n">
         <v>12.11192239030468</v>
@@ -7563,7 +7563,7 @@
         <v>12.85279650904235</v>
       </c>
       <c r="BM33" t="n">
-        <v>17.23979083478964</v>
+        <v>17.23979083478965</v>
       </c>
       <c r="BN33" t="n">
         <v>13.12365616336768</v>
@@ -7572,10 +7572,10 @@
         <v>18.01319755809689</v>
       </c>
       <c r="BP33" t="n">
-        <v>8.896299854870035</v>
+        <v>8.89629985487003</v>
       </c>
       <c r="BQ33" t="n">
-        <v>5.453850994072487</v>
+        <v>5.453850994072488</v>
       </c>
       <c r="BR33" t="n">
         <v>22.88183991063863</v>
@@ -7986,7 +7986,7 @@
         <v>0.03339947361909435</v>
       </c>
       <c r="H36" t="n">
-        <v>0.02804357781065376</v>
+        <v>0.02804357781065375</v>
       </c>
       <c r="I36" t="n">
         <v>0.03716788393750816</v>
@@ -8004,7 +8004,7 @@
         <v>0.03215153528514963</v>
       </c>
       <c r="N36" t="n">
-        <v>0.03123826328716183</v>
+        <v>0.03123826328716182</v>
       </c>
       <c r="O36" t="n">
         <v>0.03592466725668749</v>
@@ -8022,7 +8022,7 @@
         <v>0.04915050472922203</v>
       </c>
       <c r="T36" t="n">
-        <v>0.04595159671944587</v>
+        <v>0.04595159671944588</v>
       </c>
       <c r="U36" t="n">
         <v>0.04890567960926719</v>
@@ -8061,7 +8061,7 @@
         <v>0.04330160187968778</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.05168449570205725</v>
+        <v>0.05168449570205724</v>
       </c>
       <c r="AH36" t="n">
         <v>0.02928898384114541</v>
@@ -8070,7 +8070,7 @@
         <v>0.05190389708626374</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.05337706377518266</v>
+        <v>0.05337706377518265</v>
       </c>
       <c r="AK36" t="n">
         <v>0.06814183647397896</v>
@@ -8097,7 +8097,7 @@
         <v>0.0727067486427742</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.0452780484959503</v>
+        <v>0.04527804849595029</v>
       </c>
       <c r="AT36" t="n">
         <v>0.06057783247956579</v>
@@ -8118,10 +8118,10 @@
         <v>0.4352366953376335</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.4701650753921288</v>
+        <v>0.4701650753921289</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.4649226306047456</v>
+        <v>0.4649226306047457</v>
       </c>
       <c r="BB36" t="n">
         <v>0.4590133129941308</v>
@@ -8148,10 +8148,10 @@
         <v>0.7422902816484519</v>
       </c>
       <c r="BJ36" t="n">
-        <v>1.374957604231431</v>
+        <v>1.37495760423143</v>
       </c>
       <c r="BK36" t="n">
-        <v>1.267201947986529</v>
+        <v>1.267201947986528</v>
       </c>
       <c r="BL36" t="n">
         <v>0.3068915044294452</v>
@@ -8209,7 +8209,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>9.236681106254377</v>
+        <v>9.236681106254375</v>
       </c>
       <c r="D37" t="n">
         <v>13.83001405596348</v>
@@ -8221,13 +8221,13 @@
         <v>8.21440487226819</v>
       </c>
       <c r="G37" t="n">
-        <v>6.591021022239652</v>
+        <v>6.591021022239651</v>
       </c>
       <c r="H37" t="n">
-        <v>5.377812061686633</v>
+        <v>5.377812061686631</v>
       </c>
       <c r="I37" t="n">
-        <v>5.950797327499081</v>
+        <v>5.950797327499082</v>
       </c>
       <c r="J37" t="n">
         <v>10.70012231332664</v>
@@ -8236,13 +8236,13 @@
         <v>12.13466082506201</v>
       </c>
       <c r="L37" t="n">
-        <v>9.57373282863786</v>
+        <v>9.573732828637862</v>
       </c>
       <c r="M37" t="n">
-        <v>4.860692542322351</v>
+        <v>4.860692542322349</v>
       </c>
       <c r="N37" t="n">
-        <v>5.122287941395715</v>
+        <v>5.122287941395714</v>
       </c>
       <c r="O37" t="n">
         <v>8.12181827840932</v>
@@ -8254,10 +8254,10 @@
         <v>7.71339026570854</v>
       </c>
       <c r="R37" t="n">
-        <v>7.88252915230203</v>
+        <v>7.882529152302029</v>
       </c>
       <c r="S37" t="n">
-        <v>8.248548079753881</v>
+        <v>8.248548079753883</v>
       </c>
       <c r="T37" t="n">
         <v>7.946950246613521</v>
@@ -8272,19 +8272,19 @@
         <v>10.60331267863964</v>
       </c>
       <c r="X37" t="n">
-        <v>9.107126111388553</v>
+        <v>9.107126111388556</v>
       </c>
       <c r="Y37" t="n">
-        <v>10.58159554193469</v>
+        <v>10.58159554193468</v>
       </c>
       <c r="Z37" t="n">
-        <v>9.545759445174131</v>
+        <v>9.545759445174127</v>
       </c>
       <c r="AA37" t="n">
         <v>11.24438007331585</v>
       </c>
       <c r="AB37" t="n">
-        <v>13.11095260149592</v>
+        <v>13.11095260149591</v>
       </c>
       <c r="AC37" t="n">
         <v>19.13545942245881</v>
@@ -8296,13 +8296,13 @@
         <v>12.86261943016644</v>
       </c>
       <c r="AF37" t="n">
-        <v>7.021138259949991</v>
+        <v>7.021138259949989</v>
       </c>
       <c r="AG37" t="n">
-        <v>8.518893433083628</v>
+        <v>8.518893433083626</v>
       </c>
       <c r="AH37" t="n">
-        <v>6.565116527656257</v>
+        <v>6.565116527656256</v>
       </c>
       <c r="AI37" t="n">
         <v>10.29140937174527</v>
@@ -8323,7 +8323,7 @@
         <v>11.49839087840912</v>
       </c>
       <c r="AO37" t="n">
-        <v>10.39825978783188</v>
+        <v>10.39825978783189</v>
       </c>
       <c r="AP37" t="n">
         <v>10.98580411046728</v>
@@ -8338,7 +8338,7 @@
         <v>7.692426983027878</v>
       </c>
       <c r="AT37" t="n">
-        <v>14.75866260976138</v>
+        <v>14.75866260976139</v>
       </c>
       <c r="AU37" t="n">
         <v>12.75053818130237</v>
@@ -8359,7 +8359,7 @@
         <v>11.05715001145059</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.072633397442193</v>
+        <v>5.072633397442192</v>
       </c>
       <c r="BB37" t="n">
         <v>29.999571473569</v>
@@ -8368,7 +8368,7 @@
         <v>21.08120387121793</v>
       </c>
       <c r="BD37" t="n">
-        <v>28.74514666374757</v>
+        <v>28.74514666374756</v>
       </c>
       <c r="BE37" t="n">
         <v>14.75498998085789</v>
@@ -8380,7 +8380,7 @@
         <v>26.44482684098206</v>
       </c>
       <c r="BH37" t="n">
-        <v>31.94023847564582</v>
+        <v>31.94023847564583</v>
       </c>
       <c r="BI37" t="n">
         <v>29.72681043325486</v>
@@ -8389,10 +8389,10 @@
         <v>13.19566903535406</v>
       </c>
       <c r="BK37" t="n">
-        <v>6.804508044016802</v>
+        <v>6.8045080440168</v>
       </c>
       <c r="BL37" t="n">
-        <v>5.288796939907735</v>
+        <v>5.288796939907737</v>
       </c>
       <c r="BM37" t="n">
         <v>9.089603919206453</v>
@@ -8428,13 +8428,13 @@
         <v>25.36193491932729</v>
       </c>
       <c r="BX37" t="n">
-        <v>29.01926061069557</v>
+        <v>29.01926061069558</v>
       </c>
       <c r="BY37" t="n">
         <v>28.42097757845574</v>
       </c>
       <c r="BZ37" t="n">
-        <v>21.95760191428739</v>
+        <v>21.95760191428738</v>
       </c>
     </row>
     <row r="38">
@@ -8950,7 +8950,7 @@
         <v>0.08775110047001004</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0820711168507407</v>
+        <v>0.08207111685074069</v>
       </c>
       <c r="I43" t="n">
         <v>0.08415929333605361</v>
@@ -8980,7 +8980,7 @@
         <v>0.09584056828964703</v>
       </c>
       <c r="R43" t="n">
-        <v>0.1070846964101655</v>
+        <v>0.1070846964101654</v>
       </c>
       <c r="S43" t="n">
         <v>0.107201241042783</v>
@@ -9031,7 +9031,7 @@
         <v>0.06769110948257599</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.1225463994838212</v>
+        <v>0.1225463994838213</v>
       </c>
       <c r="AJ43" t="n">
         <v>0.131767594036505</v>
@@ -9091,7 +9091,7 @@
         <v>0.5911216186729322</v>
       </c>
       <c r="BC43" t="n">
-        <v>0.4388652259986645</v>
+        <v>0.4388652259986646</v>
       </c>
       <c r="BD43" t="n">
         <v>0.6882475573203</v>
@@ -9100,7 +9100,7 @@
         <v>0.3704434303883064</v>
       </c>
       <c r="BF43" t="n">
-        <v>0.2948365740511933</v>
+        <v>0.2948365740511934</v>
       </c>
       <c r="BG43" t="n">
         <v>0.2856403457134515</v>
@@ -9127,7 +9127,7 @@
         <v>0.1191629456747389</v>
       </c>
       <c r="BO43" t="n">
-        <v>0.1680502126435008</v>
+        <v>0.1680502126435007</v>
       </c>
       <c r="BP43" t="n">
         <v>0.538504536515739</v>
@@ -9182,22 +9182,22 @@
         <v>0.2250182242963864</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7624504149167779</v>
+        <v>0.7624504149167778</v>
       </c>
       <c r="G44" t="n">
         <v>0.08774566591444311</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0803618465008354</v>
+        <v>0.08036184650083542</v>
       </c>
       <c r="I44" t="n">
-        <v>0.07724716661173289</v>
+        <v>0.07724716661173285</v>
       </c>
       <c r="J44" t="n">
         <v>0.1101830025614886</v>
       </c>
       <c r="K44" t="n">
-        <v>0.125729068246952</v>
+        <v>0.1257290682469519</v>
       </c>
       <c r="L44" t="n">
         <v>0.1086358999211316</v>
@@ -9206,10 +9206,10 @@
         <v>0.07135168263099231</v>
       </c>
       <c r="N44" t="n">
-        <v>0.07417687049754312</v>
+        <v>0.0741768704975431</v>
       </c>
       <c r="O44" t="n">
-        <v>0.07473601943878362</v>
+        <v>0.07473601943878361</v>
       </c>
       <c r="P44" t="n">
         <v>0.1072962036072478</v>
@@ -9218,7 +9218,7 @@
         <v>0.0925458294467181</v>
       </c>
       <c r="R44" t="n">
-        <v>0.09698951305406626</v>
+        <v>0.09698951305406624</v>
       </c>
       <c r="S44" t="n">
         <v>0.1143782596740054</v>
@@ -9230,19 +9230,19 @@
         <v>0.1100274223193427</v>
       </c>
       <c r="V44" t="n">
-        <v>0.1568286092115538</v>
+        <v>0.1568286092115539</v>
       </c>
       <c r="W44" t="n">
         <v>0.1641985893442817</v>
       </c>
       <c r="X44" t="n">
-        <v>0.165833018204835</v>
+        <v>0.1658330182048349</v>
       </c>
       <c r="Y44" t="n">
         <v>0.1882168586785155</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.1900076316229403</v>
+        <v>0.1900076316229404</v>
       </c>
       <c r="AA44" t="n">
         <v>0.20103108285719</v>
@@ -9257,16 +9257,16 @@
         <v>0.2381503223367589</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.1803611259188314</v>
+        <v>0.1803611259188315</v>
       </c>
       <c r="AF44" t="n">
         <v>0.1016195009878331</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.1126710562381136</v>
+        <v>0.1126710562381137</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.06816232161193235</v>
+        <v>0.06816232161193234</v>
       </c>
       <c r="AI44" t="n">
         <v>0.1242758326989801</v>
@@ -9284,10 +9284,10 @@
         <v>0.1538796089615282</v>
       </c>
       <c r="AN44" t="n">
-        <v>0.1461600582490316</v>
+        <v>0.1461600582490317</v>
       </c>
       <c r="AO44" t="n">
-        <v>0.1342420152461748</v>
+        <v>0.1342420152461747</v>
       </c>
       <c r="AP44" t="n">
         <v>0.149148276343805</v>
@@ -9308,22 +9308,22 @@
         <v>0.1624638001787902</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.1457321702671549</v>
+        <v>0.145732170267155</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.08816303235530484</v>
+        <v>0.08816303235530486</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.3770277623326745</v>
+        <v>0.3770277623326744</v>
       </c>
       <c r="AY44" t="n">
         <v>0.4270783408076336</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.4184677809772497</v>
+        <v>0.4184677809772496</v>
       </c>
       <c r="BA44" t="n">
-        <v>0.4812785878329097</v>
+        <v>0.4812785878329095</v>
       </c>
       <c r="BB44" t="n">
         <v>0.2961664459131726</v>
@@ -9341,7 +9341,7 @@
         <v>0.2018199098890827</v>
       </c>
       <c r="BG44" t="n">
-        <v>0.2473039424391169</v>
+        <v>0.247303942439117</v>
       </c>
       <c r="BH44" t="n">
         <v>0.2223577015221347</v>
@@ -9356,7 +9356,7 @@
         <v>1.442058302672685</v>
       </c>
       <c r="BL44" t="n">
-        <v>0.4451414169398532</v>
+        <v>0.4451414169398531</v>
       </c>
       <c r="BM44" t="n">
         <v>0.3736439846066777</v>
@@ -9365,7 +9365,7 @@
         <v>0.2085130323800725</v>
       </c>
       <c r="BO44" t="n">
-        <v>0.2193492146756423</v>
+        <v>0.2193492146756422</v>
       </c>
       <c r="BP44" t="n">
         <v>1.45697222835643</v>
@@ -9380,7 +9380,7 @@
         <v>0.1681807413135669</v>
       </c>
       <c r="BT44" t="n">
-        <v>0.2304163157598368</v>
+        <v>0.2304163157598367</v>
       </c>
       <c r="BU44" t="n">
         <v>0.2718560607871712</v>
@@ -9398,7 +9398,7 @@
         <v>0.2067117906321942</v>
       </c>
       <c r="BZ44" t="n">
-        <v>0.1965945769088316</v>
+        <v>0.1965945769088317</v>
       </c>
     </row>
     <row r="45">
@@ -9822,10 +9822,10 @@
         <v>1.065429315869947</v>
       </c>
       <c r="L48" t="n">
-        <v>0.9657065733674695</v>
+        <v>0.9657065733674696</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1115771841482973</v>
+        <v>0.1115771841482974</v>
       </c>
       <c r="N48" t="n">
         <v>0.113233317520678</v>
@@ -9870,13 +9870,13 @@
         <v>0.1493784155364853</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.9651593666854726</v>
+        <v>0.9651593666854725</v>
       </c>
       <c r="AC48" t="n">
         <v>1.058895750861178</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.9830918431165465</v>
+        <v>0.9830918431165466</v>
       </c>
       <c r="AE48" t="n">
         <v>0.3645636672803193</v>
@@ -9918,7 +9918,7 @@
         <v>0.2613420016626071</v>
       </c>
       <c r="AR48" t="n">
-        <v>0.4487727701532032</v>
+        <v>0.4487727701532031</v>
       </c>
       <c r="AS48" t="n">
         <v>0.2946395421476545</v>
@@ -9933,7 +9933,7 @@
         <v>0.1882880450394185</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.5399310015245959</v>
+        <v>0.5399310015245957</v>
       </c>
       <c r="AX48" t="n">
         <v>0.2862403753286038</v>
@@ -9972,7 +9972,7 @@
         <v>0.07802828188665753</v>
       </c>
       <c r="BJ48" t="n">
-        <v>0.7161754643546514</v>
+        <v>0.7161754643546515</v>
       </c>
       <c r="BK48" t="n">
         <v>0.2709212753061964</v>
@@ -9984,16 +9984,16 @@
         <v>0.07028969068156074</v>
       </c>
       <c r="BN48" t="n">
-        <v>0.03544348862915853</v>
+        <v>0.03544348862915854</v>
       </c>
       <c r="BO48" t="n">
         <v>0.06900117258326856</v>
       </c>
       <c r="BP48" t="n">
-        <v>0.7542639896671278</v>
+        <v>0.7542639896671279</v>
       </c>
       <c r="BQ48" t="n">
-        <v>0.5140796070046957</v>
+        <v>0.5140796070046958</v>
       </c>
       <c r="BR48" t="n">
         <v>1.473188121664948</v>
@@ -10591,7 +10591,7 @@
         <v>60.01895002236657</v>
       </c>
       <c r="G54" t="n">
-        <v>18.97454872322375</v>
+        <v>18.97454872322374</v>
       </c>
       <c r="H54" t="n">
         <v>17.29429587879103</v>
@@ -10621,7 +10621,7 @@
         <v>14.50701904753331</v>
       </c>
       <c r="Q54" t="n">
-        <v>11.86403410542123</v>
+        <v>11.86403410542124</v>
       </c>
       <c r="R54" t="n">
         <v>11.8813956859162</v>
@@ -10630,13 +10630,13 @@
         <v>11.31709676877051</v>
       </c>
       <c r="T54" t="n">
-        <v>11.37453156708499</v>
+        <v>11.374531567085</v>
       </c>
       <c r="U54" t="n">
         <v>11.72879361200085</v>
       </c>
       <c r="V54" t="n">
-        <v>23.04075247815099</v>
+        <v>23.040752478151</v>
       </c>
       <c r="W54" t="n">
         <v>22.19398020957372</v>
@@ -10645,10 +10645,10 @@
         <v>22.75726670999927</v>
       </c>
       <c r="Y54" t="n">
-        <v>33.38838513578097</v>
+        <v>33.38838513578098</v>
       </c>
       <c r="Z54" t="n">
-        <v>34.76155936016644</v>
+        <v>34.76155936016645</v>
       </c>
       <c r="AA54" t="n">
         <v>34.4595697349563</v>
@@ -10657,7 +10657,7 @@
         <v>40.79073190754479</v>
       </c>
       <c r="AC54" t="n">
-        <v>38.38609938031141</v>
+        <v>38.38609938031143</v>
       </c>
       <c r="AD54" t="n">
         <v>36.56103446528616</v>
@@ -10669,7 +10669,7 @@
         <v>23.45644036162583</v>
       </c>
       <c r="AG54" t="n">
-        <v>31.11451135005028</v>
+        <v>31.11451135005029</v>
       </c>
       <c r="AH54" t="n">
         <v>9.670676931053688</v>
@@ -10678,7 +10678,7 @@
         <v>15.87100855164787</v>
       </c>
       <c r="AJ54" t="n">
-        <v>15.58412659767418</v>
+        <v>15.58412659767417</v>
       </c>
       <c r="AK54" t="n">
         <v>13.47911074905618</v>
@@ -10687,7 +10687,7 @@
         <v>16.08860138826397</v>
       </c>
       <c r="AM54" t="n">
-        <v>14.5814151091429</v>
+        <v>14.58141510914291</v>
       </c>
       <c r="AN54" t="n">
         <v>18.12929739263931</v>
@@ -10708,13 +10708,13 @@
         <v>31.62383856508101</v>
       </c>
       <c r="AT54" t="n">
-        <v>31.57490583874332</v>
+        <v>31.57490583874331</v>
       </c>
       <c r="AU54" t="n">
         <v>28.31761791242483</v>
       </c>
       <c r="AV54" t="n">
-        <v>29.66359768486501</v>
+        <v>29.663597684865</v>
       </c>
       <c r="AW54" t="n">
         <v>11.68645986129938</v>
@@ -10723,10 +10723,10 @@
         <v>33.84488959349316</v>
       </c>
       <c r="AY54" t="n">
-        <v>32.86393958111786</v>
+        <v>32.86393958111787</v>
       </c>
       <c r="AZ54" t="n">
-        <v>44.88501923554021</v>
+        <v>44.88501923554018</v>
       </c>
       <c r="BA54" t="n">
         <v>43.34507620709159</v>
@@ -10735,28 +10735,28 @@
         <v>64.77923411740964</v>
       </c>
       <c r="BC54" t="n">
-        <v>47.32190548940222</v>
+        <v>47.32190548940223</v>
       </c>
       <c r="BD54" t="n">
         <v>68.27244462360916</v>
       </c>
       <c r="BE54" t="n">
-        <v>37.50862219599894</v>
+        <v>37.50862219599895</v>
       </c>
       <c r="BF54" t="n">
-        <v>37.27760518836686</v>
+        <v>37.27760518836685</v>
       </c>
       <c r="BG54" t="n">
-        <v>37.07979525293704</v>
+        <v>37.07979525293703</v>
       </c>
       <c r="BH54" t="n">
-        <v>36.37676097937887</v>
+        <v>36.37676097937889</v>
       </c>
       <c r="BI54" t="n">
         <v>36.94491590486591</v>
       </c>
       <c r="BJ54" t="n">
-        <v>40.66718207039254</v>
+        <v>40.66718207039255</v>
       </c>
       <c r="BK54" t="n">
         <v>13.14370625450515</v>
@@ -10765,28 +10765,28 @@
         <v>21.30413768889261</v>
       </c>
       <c r="BM54" t="n">
-        <v>21.70957628659495</v>
+        <v>21.70957628659496</v>
       </c>
       <c r="BN54" t="n">
-        <v>10.81201343552675</v>
+        <v>10.81201343552676</v>
       </c>
       <c r="BO54" t="n">
         <v>18.01149224696858</v>
       </c>
       <c r="BP54" t="n">
-        <v>38.50305565891976</v>
+        <v>38.50305565891975</v>
       </c>
       <c r="BQ54" t="n">
-        <v>19.54586638970029</v>
+        <v>19.54586638970028</v>
       </c>
       <c r="BR54" t="n">
-        <v>34.95026189119394</v>
+        <v>34.95026189119393</v>
       </c>
       <c r="BS54" t="n">
         <v>35.99223042727514</v>
       </c>
       <c r="BT54" t="n">
-        <v>30.41983632253149</v>
+        <v>30.41983632253148</v>
       </c>
       <c r="BU54" t="n">
         <v>28.13338076878737</v>
@@ -10801,7 +10801,7 @@
         <v>17.44268804643087</v>
       </c>
       <c r="BY54" t="n">
-        <v>19.24150662009027</v>
+        <v>19.24150662009026</v>
       </c>
       <c r="BZ54" t="n">
         <v>18.9395036590646</v>
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2.104464880241209</v>
+        <v>2.10446488024121</v>
       </c>
       <c r="D55" t="n">
         <v>2.322935742790195</v>
       </c>
       <c r="E55" t="n">
-        <v>2.748244523003455</v>
+        <v>2.748244523003454</v>
       </c>
       <c r="F55" t="n">
         <v>3.02764839475289</v>
@@ -10835,16 +10835,16 @@
         <v>1.012572890093322</v>
       </c>
       <c r="I55" t="n">
-        <v>0.9841193680699022</v>
+        <v>0.9841193680699023</v>
       </c>
       <c r="J55" t="n">
         <v>1.541114418535989</v>
       </c>
       <c r="K55" t="n">
-        <v>1.623878656285506</v>
+        <v>1.623878656285505</v>
       </c>
       <c r="L55" t="n">
-        <v>1.440937134627115</v>
+        <v>1.440937134627114</v>
       </c>
       <c r="M55" t="n">
         <v>1.044583524355786</v>
@@ -10874,7 +10874,7 @@
         <v>1.301894949442884</v>
       </c>
       <c r="V55" t="n">
-        <v>1.590394643038575</v>
+        <v>1.590394643038574</v>
       </c>
       <c r="W55" t="n">
         <v>1.561154124035071</v>
@@ -10889,7 +10889,7 @@
         <v>1.893344529930008</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.910109510761732</v>
+        <v>1.910109510761733</v>
       </c>
       <c r="AB55" t="n">
         <v>1.861925132942413</v>
@@ -10955,13 +10955,13 @@
         <v>2.131071540410258</v>
       </c>
       <c r="AW55" t="n">
-        <v>3.972766732941386</v>
+        <v>3.972766732941387</v>
       </c>
       <c r="AX55" t="n">
         <v>3.759793588119867</v>
       </c>
       <c r="AY55" t="n">
-        <v>4.57630962715318</v>
+        <v>4.576309627153179</v>
       </c>
       <c r="AZ55" t="n">
         <v>3.663727660542295</v>
@@ -10973,13 +10973,13 @@
         <v>4.723031932511542</v>
       </c>
       <c r="BC55" t="n">
-        <v>4.434997326486062</v>
+        <v>4.434997326486063</v>
       </c>
       <c r="BD55" t="n">
-        <v>5.502689590070485</v>
+        <v>5.502689590070486</v>
       </c>
       <c r="BE55" t="n">
-        <v>3.780429206197707</v>
+        <v>3.780429206197706</v>
       </c>
       <c r="BF55" t="n">
         <v>2.866798353183867</v>
@@ -10994,19 +10994,19 @@
         <v>3.784601633110199</v>
       </c>
       <c r="BJ55" t="n">
-        <v>7.819995638000587</v>
+        <v>7.819995638000586</v>
       </c>
       <c r="BK55" t="n">
-        <v>4.237511392000476</v>
+        <v>4.237511392000477</v>
       </c>
       <c r="BL55" t="n">
         <v>2.009007713833513</v>
       </c>
       <c r="BM55" t="n">
-        <v>2.515133654917197</v>
+        <v>2.515133654917196</v>
       </c>
       <c r="BN55" t="n">
-        <v>2.637102409636825</v>
+        <v>2.637102409636824</v>
       </c>
       <c r="BO55" t="n">
         <v>3.060305849390816</v>
@@ -11015,16 +11015,16 @@
         <v>4.425915192831257</v>
       </c>
       <c r="BQ55" t="n">
-        <v>3.594382167600897</v>
+        <v>3.594382167600898</v>
       </c>
       <c r="BR55" t="n">
         <v>4.897913517669521</v>
       </c>
       <c r="BS55" t="n">
-        <v>5.165891083251556</v>
+        <v>5.165891083251555</v>
       </c>
       <c r="BT55" t="n">
-        <v>4.716103535293788</v>
+        <v>4.716103535293787</v>
       </c>
       <c r="BU55" t="n">
         <v>4.55789676818944</v>
@@ -11033,16 +11033,16 @@
         <v>3.117661154966156</v>
       </c>
       <c r="BW55" t="n">
-        <v>3.222936405445295</v>
+        <v>3.222936405445294</v>
       </c>
       <c r="BX55" t="n">
         <v>3.540361117230148</v>
       </c>
       <c r="BY55" t="n">
-        <v>3.290154649610393</v>
+        <v>3.290154649610394</v>
       </c>
       <c r="BZ55" t="n">
-        <v>2.797480123343002</v>
+        <v>2.797480123343003</v>
       </c>
     </row>
     <row r="56">
@@ -11055,10 +11055,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>8.879000449094031</v>
+        <v>8.879000449094033</v>
       </c>
       <c r="D56" t="n">
-        <v>16.67632669855202</v>
+        <v>16.67632669855201</v>
       </c>
       <c r="E56" t="n">
         <v>24.8469393031319</v>
@@ -11070,10 +11070,10 @@
         <v>11.14428981943255</v>
       </c>
       <c r="H56" t="n">
-        <v>9.87148692202069</v>
+        <v>9.871486922020692</v>
       </c>
       <c r="I56" t="n">
-        <v>10.31798840219445</v>
+        <v>10.31798840219446</v>
       </c>
       <c r="J56" t="n">
         <v>15.70931832437396</v>
@@ -11082,7 +11082,7 @@
         <v>15.67593561120263</v>
       </c>
       <c r="L56" t="n">
-        <v>15.54307638735306</v>
+        <v>15.54307638735305</v>
       </c>
       <c r="M56" t="n">
         <v>10.82487382185755</v>
@@ -11097,16 +11097,16 @@
         <v>17.51215349007097</v>
       </c>
       <c r="Q56" t="n">
-        <v>14.8139313398327</v>
+        <v>14.81393133983271</v>
       </c>
       <c r="R56" t="n">
-        <v>15.88234552166686</v>
+        <v>15.88234552166685</v>
       </c>
       <c r="S56" t="n">
-        <v>17.72249587580758</v>
+        <v>17.72249587580757</v>
       </c>
       <c r="T56" t="n">
-        <v>16.94237959412323</v>
+        <v>16.94237959412322</v>
       </c>
       <c r="U56" t="n">
         <v>18.19059222171002</v>
@@ -11118,10 +11118,10 @@
         <v>22.4048163222778</v>
       </c>
       <c r="X56" t="n">
-        <v>20.1417672521101</v>
+        <v>20.14176725211009</v>
       </c>
       <c r="Y56" t="n">
-        <v>21.08948437655291</v>
+        <v>21.08948437655292</v>
       </c>
       <c r="Z56" t="n">
         <v>23.94610342829396</v>
@@ -11130,13 +11130,13 @@
         <v>26.08438318489998</v>
       </c>
       <c r="AB56" t="n">
-        <v>23.6408789976852</v>
+        <v>23.64087899768518</v>
       </c>
       <c r="AC56" t="n">
-        <v>26.34453627059336</v>
+        <v>26.34453627059335</v>
       </c>
       <c r="AD56" t="n">
-        <v>27.38236752196275</v>
+        <v>27.38236752196276</v>
       </c>
       <c r="AE56" t="n">
         <v>27.59552356706648</v>
@@ -11178,19 +11178,19 @@
         <v>18.91977316428192</v>
       </c>
       <c r="AR56" t="n">
-        <v>22.91544567916657</v>
+        <v>22.91544567916656</v>
       </c>
       <c r="AS56" t="n">
-        <v>16.31491634802739</v>
+        <v>16.31491634802738</v>
       </c>
       <c r="AT56" t="n">
         <v>23.39557921547557</v>
       </c>
       <c r="AU56" t="n">
-        <v>25.96428754222719</v>
+        <v>25.96428754222718</v>
       </c>
       <c r="AV56" t="n">
-        <v>23.16174859097402</v>
+        <v>23.16174859097403</v>
       </c>
       <c r="AW56" t="n">
         <v>6.657757709754605</v>
@@ -11229,10 +11229,10 @@
         <v>2.346229562976341</v>
       </c>
       <c r="BI56" t="n">
-        <v>1.732131645594522</v>
+        <v>1.732131645594523</v>
       </c>
       <c r="BJ56" t="n">
-        <v>2.604827632131043</v>
+        <v>2.604827632131044</v>
       </c>
       <c r="BK56" t="n">
         <v>1.12329918889286</v>
@@ -11244,43 +11244,43 @@
         <v>1.961622231577266</v>
       </c>
       <c r="BN56" t="n">
-        <v>3.63409862864337</v>
+        <v>3.634098628643369</v>
       </c>
       <c r="BO56" t="n">
-        <v>4.219319186682511</v>
+        <v>4.21931918668251</v>
       </c>
       <c r="BP56" t="n">
-        <v>2.383784758376182</v>
+        <v>2.383784758376181</v>
       </c>
       <c r="BQ56" t="n">
         <v>1.736955733759818</v>
       </c>
       <c r="BR56" t="n">
-        <v>3.52877680695419</v>
+        <v>3.528776806954189</v>
       </c>
       <c r="BS56" t="n">
         <v>4.540565058249707</v>
       </c>
       <c r="BT56" t="n">
-        <v>6.459092403238425</v>
+        <v>6.459092403238426</v>
       </c>
       <c r="BU56" t="n">
-        <v>7.447208336314007</v>
+        <v>7.447208336314008</v>
       </c>
       <c r="BV56" t="n">
         <v>5.81281229699224</v>
       </c>
       <c r="BW56" t="n">
-        <v>6.722167702843914</v>
+        <v>6.722167702843915</v>
       </c>
       <c r="BX56" t="n">
-        <v>7.386269850184359</v>
+        <v>7.386269850184358</v>
       </c>
       <c r="BY56" t="n">
         <v>6.663676250112323</v>
       </c>
       <c r="BZ56" t="n">
-        <v>5.617653995683448</v>
+        <v>5.617653995683447</v>
       </c>
     </row>
     <row r="57">
@@ -11723,7 +11723,7 @@
         <v>12.88019145559012</v>
       </c>
       <c r="G60" t="n">
-        <v>5.069772271738576</v>
+        <v>5.069772271738575</v>
       </c>
       <c r="H60" t="n">
         <v>4.376163401460544</v>
@@ -11744,7 +11744,7 @@
         <v>5.22375253078978</v>
       </c>
       <c r="N60" t="n">
-        <v>5.009741279030786</v>
+        <v>5.009741279030785</v>
       </c>
       <c r="O60" t="n">
         <v>6.558930512959892</v>
@@ -11753,10 +11753,10 @@
         <v>8.360776556891929</v>
       </c>
       <c r="Q60" t="n">
-        <v>7.376157410853416</v>
+        <v>7.376157410853418</v>
       </c>
       <c r="R60" t="n">
-        <v>7.362273830986726</v>
+        <v>7.362273830986727</v>
       </c>
       <c r="S60" t="n">
         <v>7.59696390046717</v>
@@ -11795,13 +11795,13 @@
         <v>9.350575145133947</v>
       </c>
       <c r="AE60" t="n">
-        <v>9.018982177082522</v>
+        <v>9.018982177082526</v>
       </c>
       <c r="AF60" t="n">
         <v>5.730530428679295</v>
       </c>
       <c r="AG60" t="n">
-        <v>6.417887733144272</v>
+        <v>6.417887733144274</v>
       </c>
       <c r="AH60" t="n">
         <v>5.199258660763308</v>
@@ -11819,10 +11819,10 @@
         <v>5.989451600693563</v>
       </c>
       <c r="AM60" t="n">
-        <v>5.507770983046384</v>
+        <v>5.507770983046383</v>
       </c>
       <c r="AN60" t="n">
-        <v>9.22288310847523</v>
+        <v>9.222883108475232</v>
       </c>
       <c r="AO60" t="n">
         <v>8.28944804434564</v>
@@ -11837,7 +11837,7 @@
         <v>7.059336453621986</v>
       </c>
       <c r="AS60" t="n">
-        <v>6.693544568435809</v>
+        <v>6.693544568435808</v>
       </c>
       <c r="AT60" t="n">
         <v>11.08560544832138</v>
@@ -11852,7 +11852,7 @@
         <v>4.193357514419293</v>
       </c>
       <c r="AX60" t="n">
-        <v>6.847158056909885</v>
+        <v>6.847158056909884</v>
       </c>
       <c r="AY60" t="n">
         <v>6.661168252559383</v>
@@ -11867,7 +11867,7 @@
         <v>3.553114160968207</v>
       </c>
       <c r="BC60" t="n">
-        <v>4.860161075893558</v>
+        <v>4.860161075893559</v>
       </c>
       <c r="BD60" t="n">
         <v>5.886321509940138</v>
@@ -11885,7 +11885,7 @@
         <v>3.179101876306361</v>
       </c>
       <c r="BI60" t="n">
-        <v>3.191869297200144</v>
+        <v>3.191869297200143</v>
       </c>
       <c r="BJ60" t="n">
         <v>27.84021114365188</v>
@@ -11897,7 +11897,7 @@
         <v>5.918676742838743</v>
       </c>
       <c r="BM60" t="n">
-        <v>4.128081617489363</v>
+        <v>4.128081617489364</v>
       </c>
       <c r="BN60" t="n">
         <v>2.581538718304228</v>
@@ -11909,10 +11909,10 @@
         <v>6.85678837608662</v>
       </c>
       <c r="BQ60" t="n">
-        <v>3.696800246266608</v>
+        <v>3.696800246266607</v>
       </c>
       <c r="BR60" t="n">
-        <v>5.550791624562272</v>
+        <v>5.550791624562271</v>
       </c>
       <c r="BS60" t="n">
         <v>6.666068768512382</v>
@@ -11924,19 +11924,19 @@
         <v>8.600230537188205</v>
       </c>
       <c r="BV60" t="n">
-        <v>5.674267068285773</v>
+        <v>5.674267068285771</v>
       </c>
       <c r="BW60" t="n">
-        <v>5.921963430366099</v>
+        <v>5.921963430366101</v>
       </c>
       <c r="BX60" t="n">
-        <v>6.660480537241253</v>
+        <v>6.660480537241252</v>
       </c>
       <c r="BY60" t="n">
         <v>8.243324276720969</v>
       </c>
       <c r="BZ60" t="n">
-        <v>7.811798335466431</v>
+        <v>7.811798335466432</v>
       </c>
     </row>
     <row r="61">
@@ -12278,7 +12278,7 @@
         <v>7.470328686616686</v>
       </c>
       <c r="F63" t="n">
-        <v>3.230229764220923</v>
+        <v>3.230229764220924</v>
       </c>
       <c r="G63" t="n">
         <v>4.475332217689176</v>
@@ -12299,7 +12299,7 @@
         <v>1.876829976907474</v>
       </c>
       <c r="M63" t="n">
-        <v>3.555555813284482</v>
+        <v>3.555555813284483</v>
       </c>
       <c r="N63" t="n">
         <v>4.314127092758112</v>
@@ -12347,7 +12347,7 @@
         <v>2.790128806359558</v>
       </c>
       <c r="AC63" t="n">
-        <v>3.6906136477077</v>
+        <v>3.690613647707701</v>
       </c>
       <c r="AD63" t="n">
         <v>3.765981401910957</v>
@@ -12359,13 +12359,13 @@
         <v>4.254420751103686</v>
       </c>
       <c r="AG63" t="n">
-        <v>5.943506769653192</v>
+        <v>5.943506769653193</v>
       </c>
       <c r="AH63" t="n">
-        <v>3.935020703838507</v>
+        <v>3.935020703838506</v>
       </c>
       <c r="AI63" t="n">
-        <v>6.878479241372823</v>
+        <v>6.878479241372824</v>
       </c>
       <c r="AJ63" t="n">
         <v>7.344900256802199</v>
@@ -12380,7 +12380,7 @@
         <v>13.25169011333408</v>
       </c>
       <c r="AN63" t="n">
-        <v>8.439971110004914</v>
+        <v>8.439971110004912</v>
       </c>
       <c r="AO63" t="n">
         <v>6.967759259414469</v>
@@ -12389,16 +12389,16 @@
         <v>5.962659898238021</v>
       </c>
       <c r="AQ63" t="n">
-        <v>4.564040765283086</v>
+        <v>4.564040765283085</v>
       </c>
       <c r="AR63" t="n">
-        <v>7.856242291902201</v>
+        <v>7.856242291902202</v>
       </c>
       <c r="AS63" t="n">
         <v>2.630387961497413</v>
       </c>
       <c r="AT63" t="n">
-        <v>6.832911627415469</v>
+        <v>6.83291162741547</v>
       </c>
       <c r="AU63" t="n">
         <v>7.231530084839688</v>
@@ -12416,13 +12416,13 @@
         <v>1.865497038091917</v>
       </c>
       <c r="AZ63" t="n">
-        <v>3.269237313582722</v>
+        <v>3.269237313582723</v>
       </c>
       <c r="BA63" t="n">
         <v>2.291369265057297</v>
       </c>
       <c r="BB63" t="n">
-        <v>2.666096188445255</v>
+        <v>2.666096188445256</v>
       </c>
       <c r="BC63" t="n">
         <v>3.437748932961805</v>
@@ -12437,7 +12437,7 @@
         <v>1.736801380602102</v>
       </c>
       <c r="BG63" t="n">
-        <v>1.712268948605501</v>
+        <v>1.7122689486055</v>
       </c>
       <c r="BH63" t="n">
         <v>1.816047531303412</v>
@@ -12446,19 +12446,19 @@
         <v>1.686071747697091</v>
       </c>
       <c r="BJ63" t="n">
-        <v>5.346409142291316</v>
+        <v>5.346409142291315</v>
       </c>
       <c r="BK63" t="n">
         <v>5.554425239233173</v>
       </c>
       <c r="BL63" t="n">
-        <v>0.6592710097238206</v>
+        <v>0.6592710097238205</v>
       </c>
       <c r="BM63" t="n">
         <v>1.024311770859487</v>
       </c>
       <c r="BN63" t="n">
-        <v>0.913757470742192</v>
+        <v>0.9137574707421922</v>
       </c>
       <c r="BO63" t="n">
         <v>2.10552615856498</v>
@@ -12479,7 +12479,7 @@
         <v>1.720416432271348</v>
       </c>
       <c r="BU63" t="n">
-        <v>2.094268851226596</v>
+        <v>2.094268851226595</v>
       </c>
       <c r="BV63" t="n">
         <v>1.673556616252669</v>
@@ -12717,7 +12717,7 @@
         <v>16.42498548726356</v>
       </c>
       <c r="E65" t="n">
-        <v>33.24811853724506</v>
+        <v>33.24811853724505</v>
       </c>
       <c r="F65" t="n">
         <v>15.74623534675436</v>
@@ -12744,7 +12744,7 @@
         <v>7.126870113289404</v>
       </c>
       <c r="N65" t="n">
-        <v>7.761856330566277</v>
+        <v>7.761856330566276</v>
       </c>
       <c r="O65" t="n">
         <v>12.25137494843027</v>
@@ -12753,13 +12753,13 @@
         <v>10.90932992734961</v>
       </c>
       <c r="Q65" t="n">
-        <v>9.407506513510434</v>
+        <v>9.407506513510436</v>
       </c>
       <c r="R65" t="n">
-        <v>9.906998316432436</v>
+        <v>9.906998316432437</v>
       </c>
       <c r="S65" t="n">
-        <v>10.77025783340515</v>
+        <v>10.77025783340516</v>
       </c>
       <c r="T65" t="n">
         <v>10.22798048229222</v>
@@ -12777,10 +12777,10 @@
         <v>12.46640276955226</v>
       </c>
       <c r="Y65" t="n">
-        <v>15.06376639168587</v>
+        <v>15.06376639168586</v>
       </c>
       <c r="Z65" t="n">
-        <v>13.62806684929937</v>
+        <v>13.62806684929938</v>
       </c>
       <c r="AA65" t="n">
         <v>15.52134896413366</v>
@@ -12816,7 +12816,7 @@
         <v>37.96654535202737</v>
       </c>
       <c r="AL65" t="n">
-        <v>47.03640480753074</v>
+        <v>47.03640480753075</v>
       </c>
       <c r="AM65" t="n">
         <v>40.46877384043077</v>
@@ -12828,10 +12828,10 @@
         <v>20.58315939947718</v>
       </c>
       <c r="AP65" t="n">
-        <v>20.67227238832455</v>
+        <v>20.67227238832454</v>
       </c>
       <c r="AQ65" t="n">
-        <v>21.92514054121093</v>
+        <v>21.92514054121094</v>
       </c>
       <c r="AR65" t="n">
         <v>28.04451099155321</v>
@@ -12849,7 +12849,7 @@
         <v>20.9292249993142</v>
       </c>
       <c r="AW65" t="n">
-        <v>50.62993113228757</v>
+        <v>50.62993113228756</v>
       </c>
       <c r="AX65" t="n">
         <v>16.98280122066726</v>
@@ -12867,7 +12867,7 @@
         <v>119.8002698580501</v>
       </c>
       <c r="BC65" t="n">
-        <v>37.44458601377006</v>
+        <v>37.44458601377007</v>
       </c>
       <c r="BD65" t="n">
         <v>108.6770826107377</v>
@@ -12882,25 +12882,25 @@
         <v>43.68080411303128</v>
       </c>
       <c r="BH65" t="n">
-        <v>53.64444630655388</v>
+        <v>53.64444630655385</v>
       </c>
       <c r="BI65" t="n">
-        <v>48.78719727270537</v>
+        <v>48.78719727270538</v>
       </c>
       <c r="BJ65" t="n">
         <v>20.61195033790997</v>
       </c>
       <c r="BK65" t="n">
-        <v>21.46347051368456</v>
+        <v>21.46347051368455</v>
       </c>
       <c r="BL65" t="n">
-        <v>7.192323016905241</v>
+        <v>7.192323016905239</v>
       </c>
       <c r="BM65" t="n">
         <v>13.86407509000137</v>
       </c>
       <c r="BN65" t="n">
-        <v>22.00150208953173</v>
+        <v>22.00150208953174</v>
       </c>
       <c r="BO65" t="n">
         <v>42.36421446028131</v>
@@ -12909,10 +12909,10 @@
         <v>13.84789079187592</v>
       </c>
       <c r="BQ65" t="n">
-        <v>6.480403998485293</v>
+        <v>6.480403998485294</v>
       </c>
       <c r="BR65" t="n">
-        <v>51.25479446067622</v>
+        <v>51.25479446067623</v>
       </c>
       <c r="BS65" t="n">
         <v>54.17977204347731</v>
@@ -12921,7 +12921,7 @@
         <v>62.20335410112788</v>
       </c>
       <c r="BU65" t="n">
-        <v>68.14268615438361</v>
+        <v>68.14268615438363</v>
       </c>
       <c r="BV65" t="n">
         <v>52.71957356756503</v>
@@ -12930,7 +12930,7 @@
         <v>60.84473982549751</v>
       </c>
       <c r="BX65" t="n">
-        <v>51.63637233794017</v>
+        <v>51.63637233794018</v>
       </c>
       <c r="BY65" t="n">
         <v>42.04694426947935</v>
@@ -12949,7 +12949,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.06828691511183722</v>
+        <v>0.06828691511183721</v>
       </c>
       <c r="D66" t="n">
         <v>0.08401540177963163</v>
@@ -12964,7 +12964,7 @@
         <v>0.03762328195947</v>
       </c>
       <c r="H66" t="n">
-        <v>0.03453803096187316</v>
+        <v>0.03453803096187315</v>
       </c>
       <c r="I66" t="n">
         <v>0.03410328048149232</v>
@@ -12976,7 +12976,7 @@
         <v>0.05371471408386701</v>
       </c>
       <c r="L66" t="n">
-        <v>0.04631725901858844</v>
+        <v>0.04631725901858845</v>
       </c>
       <c r="M66" t="n">
         <v>0.02725612508546633</v>
@@ -12988,7 +12988,7 @@
         <v>0.0206822074948958</v>
       </c>
       <c r="P66" t="n">
-        <v>0.0364105177724891</v>
+        <v>0.03641051777248909</v>
       </c>
       <c r="Q66" t="n">
         <v>0.03004351138686379</v>
@@ -13000,13 +13000,13 @@
         <v>0.03518941056491196</v>
       </c>
       <c r="T66" t="n">
-        <v>0.03588787949570679</v>
+        <v>0.0358878794957068</v>
       </c>
       <c r="U66" t="n">
         <v>0.03571513401534392</v>
       </c>
       <c r="V66" t="n">
-        <v>0.04419008089399123</v>
+        <v>0.04419008089399122</v>
       </c>
       <c r="W66" t="n">
         <v>0.04574800990057245</v>
@@ -13048,43 +13048,43 @@
         <v>0.04170158324502871</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0.04305516923079244</v>
+        <v>0.04305516923079245</v>
       </c>
       <c r="AK66" t="n">
-        <v>0.04375162598701704</v>
+        <v>0.04375162598701705</v>
       </c>
       <c r="AL66" t="n">
-        <v>0.05320357180351023</v>
+        <v>0.05320357180351024</v>
       </c>
       <c r="AM66" t="n">
-        <v>0.04303010740970131</v>
+        <v>0.04303010740970132</v>
       </c>
       <c r="AN66" t="n">
-        <v>0.05248462079232706</v>
+        <v>0.05248462079232705</v>
       </c>
       <c r="AO66" t="n">
-        <v>0.04858791120577845</v>
+        <v>0.04858791120577843</v>
       </c>
       <c r="AP66" t="n">
-        <v>0.04741481553032648</v>
+        <v>0.04741481553032647</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.04309042992899656</v>
+        <v>0.04309042992899655</v>
       </c>
       <c r="AR66" t="n">
         <v>0.06465177510543077</v>
       </c>
       <c r="AS66" t="n">
-        <v>0.04237647928315786</v>
+        <v>0.04237647928315787</v>
       </c>
       <c r="AT66" t="n">
         <v>0.05326429879185376</v>
       </c>
       <c r="AU66" t="n">
-        <v>0.05531885675715519</v>
+        <v>0.0553188567571552</v>
       </c>
       <c r="AV66" t="n">
-        <v>0.05794698938143878</v>
+        <v>0.05794698938143877</v>
       </c>
       <c r="AW66" t="n">
         <v>0.01797761314368966</v>
@@ -13135,13 +13135,13 @@
         <v>0.1502649149038093</v>
       </c>
       <c r="BM66" t="n">
-        <v>0.09135347429735025</v>
+        <v>0.09135347429735026</v>
       </c>
       <c r="BN66" t="n">
         <v>0.07923736806566008</v>
       </c>
       <c r="BO66" t="n">
-        <v>0.1036588856659291</v>
+        <v>0.103658885665929</v>
       </c>
       <c r="BP66" t="n">
         <v>0.3555023765126392</v>
@@ -13776,7 +13776,7 @@
         <v>9.321589626905046</v>
       </c>
       <c r="AB71" t="n">
-        <v>4.126002763160187</v>
+        <v>4.126002763160188</v>
       </c>
       <c r="AC71" t="n">
         <v>5.478003033254477</v>
@@ -13809,7 +13809,7 @@
         <v>4.444622683581693</v>
       </c>
       <c r="AM71" t="n">
-        <v>4.205862014467842</v>
+        <v>4.205862014467843</v>
       </c>
       <c r="AN71" t="n">
         <v>7.37661391410605</v>
@@ -13944,13 +13944,13 @@
         <v>2.16251417569332</v>
       </c>
       <c r="J72" t="n">
-        <v>3.696545577161218</v>
+        <v>3.696545577161217</v>
       </c>
       <c r="K72" t="n">
         <v>3.723678963865669</v>
       </c>
       <c r="L72" t="n">
-        <v>3.376236524914879</v>
+        <v>3.376236524914878</v>
       </c>
       <c r="M72" t="n">
         <v>1.824694485232099</v>
@@ -13977,10 +13977,10 @@
         <v>2.494216693973865</v>
       </c>
       <c r="U72" t="n">
-        <v>2.469482476289567</v>
+        <v>2.469482476289568</v>
       </c>
       <c r="V72" t="n">
-        <v>4.502241046758978</v>
+        <v>4.502241046758979</v>
       </c>
       <c r="W72" t="n">
         <v>4.699178493069114</v>
@@ -13998,19 +13998,19 @@
         <v>5.703350163585783</v>
       </c>
       <c r="AB72" t="n">
-        <v>5.260023923165286</v>
+        <v>5.260023923165285</v>
       </c>
       <c r="AC72" t="n">
-        <v>6.435725873210993</v>
+        <v>6.435725873210994</v>
       </c>
       <c r="AD72" t="n">
-        <v>5.796831160735116</v>
+        <v>5.796831160735115</v>
       </c>
       <c r="AE72" t="n">
         <v>4.68456746099486</v>
       </c>
       <c r="AF72" t="n">
-        <v>2.711026486293925</v>
+        <v>2.711026486293924</v>
       </c>
       <c r="AG72" t="n">
         <v>3.067425498640364</v>
@@ -14022,7 +14022,7 @@
         <v>3.400235439589585</v>
       </c>
       <c r="AJ72" t="n">
-        <v>3.481823544341124</v>
+        <v>3.481823544341123</v>
       </c>
       <c r="AK72" t="n">
         <v>7.221576171288306</v>
@@ -14031,7 +14031,7 @@
         <v>8.349184623310784</v>
       </c>
       <c r="AM72" t="n">
-        <v>7.849176400410665</v>
+        <v>7.849176400410666</v>
       </c>
       <c r="AN72" t="n">
         <v>3.585172859688571</v>
@@ -14055,7 +14055,7 @@
         <v>3.885330261839941</v>
       </c>
       <c r="AU72" t="n">
-        <v>4.17482092964078</v>
+        <v>4.174820929640779</v>
       </c>
       <c r="AV72" t="n">
         <v>3.516388555293658</v>
@@ -14073,7 +14073,7 @@
         <v>4.964921553099321</v>
       </c>
       <c r="BA72" t="n">
-        <v>6.369045869594876</v>
+        <v>6.369045869594877</v>
       </c>
       <c r="BB72" t="n">
         <v>5.980367212418304</v>
@@ -14091,13 +14091,13 @@
         <v>6.783585499297509</v>
       </c>
       <c r="BG72" t="n">
-        <v>6.622460966157581</v>
+        <v>6.62246096615758</v>
       </c>
       <c r="BH72" t="n">
-        <v>7.233715446633335</v>
+        <v>7.233715446633333</v>
       </c>
       <c r="BI72" t="n">
-        <v>7.174542695164828</v>
+        <v>7.174542695164829</v>
       </c>
       <c r="BJ72" t="n">
         <v>6.129596863548791</v>
@@ -14109,19 +14109,19 @@
         <v>3.011095429887524</v>
       </c>
       <c r="BM72" t="n">
-        <v>2.723729141919338</v>
+        <v>2.723729141919337</v>
       </c>
       <c r="BN72" t="n">
-        <v>6.530158205965198</v>
+        <v>6.530158205965199</v>
       </c>
       <c r="BO72" t="n">
-        <v>5.543258711310428</v>
+        <v>5.54325871131043</v>
       </c>
       <c r="BP72" t="n">
         <v>4.563277354348036</v>
       </c>
       <c r="BQ72" t="n">
-        <v>3.544396043475586</v>
+        <v>3.544396043475585</v>
       </c>
       <c r="BR72" t="n">
         <v>3.281308475141461</v>
@@ -14139,13 +14139,13 @@
         <v>5.515505292294513</v>
       </c>
       <c r="BW72" t="n">
-        <v>6.874943329720742</v>
+        <v>6.874943329720743</v>
       </c>
       <c r="BX72" t="n">
         <v>7.805514014212128</v>
       </c>
       <c r="BY72" t="n">
-        <v>7.751782016396871</v>
+        <v>7.751782016396872</v>
       </c>
       <c r="BZ72" t="n">
         <v>6.246396510833319</v>
@@ -14164,19 +14164,19 @@
         <v>2.112760581353596</v>
       </c>
       <c r="D73" t="n">
-        <v>6.596226105065423</v>
+        <v>6.596226105065424</v>
       </c>
       <c r="E73" t="n">
         <v>15.5146489806167</v>
       </c>
       <c r="F73" t="n">
-        <v>1.820169612964184</v>
+        <v>1.820169612964183</v>
       </c>
       <c r="G73" t="n">
         <v>1.028490795999998</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9493904499797006</v>
+        <v>0.9493904499797007</v>
       </c>
       <c r="I73" t="n">
         <v>0.9487346819976641</v>
@@ -14206,7 +14206,7 @@
         <v>1.048955214928992</v>
       </c>
       <c r="R73" t="n">
-        <v>1.14911235922017</v>
+        <v>1.149112359220171</v>
       </c>
       <c r="S73" t="n">
         <v>1.257513236501088</v>
@@ -14236,7 +14236,7 @@
         <v>1.648195628188313</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.502078829205144</v>
+        <v>1.502078829205143</v>
       </c>
       <c r="AC73" t="n">
         <v>1.861598259642847</v>
@@ -14245,7 +14245,7 @@
         <v>1.966615622851112</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.795221408375514</v>
+        <v>1.795221408375513</v>
       </c>
       <c r="AF73" t="n">
         <v>1.227641499388399</v>
@@ -14269,7 +14269,7 @@
         <v>2.807749347004808</v>
       </c>
       <c r="AM73" t="n">
-        <v>2.659811106229988</v>
+        <v>2.659811106229989</v>
       </c>
       <c r="AN73" t="n">
         <v>1.745697379308983</v>
@@ -14290,22 +14290,22 @@
         <v>1.463906373367991</v>
       </c>
       <c r="AT73" t="n">
-        <v>2.295443370046028</v>
+        <v>2.295443370046029</v>
       </c>
       <c r="AU73" t="n">
         <v>1.908305928406145</v>
       </c>
       <c r="AV73" t="n">
-        <v>1.955651419874639</v>
+        <v>1.95565141987464</v>
       </c>
       <c r="AW73" t="n">
-        <v>12.07663263325048</v>
+        <v>12.07663263325047</v>
       </c>
       <c r="AX73" t="n">
         <v>3.177982204474137</v>
       </c>
       <c r="AY73" t="n">
-        <v>3.381460116391876</v>
+        <v>3.381460116391875</v>
       </c>
       <c r="AZ73" t="n">
         <v>3.036298674380602</v>
@@ -14320,13 +14320,13 @@
         <v>5.872990642625203</v>
       </c>
       <c r="BD73" t="n">
-        <v>10.86933707554018</v>
+        <v>10.86933707554019</v>
       </c>
       <c r="BE73" t="n">
-        <v>4.637054203267975</v>
+        <v>4.637054203267976</v>
       </c>
       <c r="BF73" t="n">
-        <v>4.570989971262402</v>
+        <v>4.570989971262401</v>
       </c>
       <c r="BG73" t="n">
         <v>4.385094804811652</v>
@@ -14335,7 +14335,7 @@
         <v>5.126668671270251</v>
       </c>
       <c r="BI73" t="n">
-        <v>4.747363221458895</v>
+        <v>4.747363221458894</v>
       </c>
       <c r="BJ73" t="n">
         <v>2.708342057066829</v>
@@ -14347,19 +14347,19 @@
         <v>2.421855639381421</v>
       </c>
       <c r="BM73" t="n">
-        <v>2.335674122696745</v>
+        <v>2.335674122696744</v>
       </c>
       <c r="BN73" t="n">
-        <v>2.559154677979146</v>
+        <v>2.559154677979145</v>
       </c>
       <c r="BO73" t="n">
         <v>8.043749703183584</v>
       </c>
       <c r="BP73" t="n">
-        <v>3.082443734005835</v>
+        <v>3.082443734005836</v>
       </c>
       <c r="BQ73" t="n">
-        <v>2.229213597810609</v>
+        <v>2.22921359781061</v>
       </c>
       <c r="BR73" t="n">
         <v>7.895809724770188</v>
@@ -14368,25 +14368,25 @@
         <v>8.186106646799896</v>
       </c>
       <c r="BT73" t="n">
-        <v>7.899780427942615</v>
+        <v>7.899780427942614</v>
       </c>
       <c r="BU73" t="n">
-        <v>7.858886627952235</v>
+        <v>7.858886627952236</v>
       </c>
       <c r="BV73" t="n">
-        <v>5.469799948955498</v>
+        <v>5.469799948955499</v>
       </c>
       <c r="BW73" t="n">
         <v>5.668449225217168</v>
       </c>
       <c r="BX73" t="n">
-        <v>5.382796217445995</v>
+        <v>5.382796217445994</v>
       </c>
       <c r="BY73" t="n">
         <v>3.890382327953748</v>
       </c>
       <c r="BZ73" t="n">
-        <v>2.837411505347576</v>
+        <v>2.837411505347575</v>
       </c>
     </row>
     <row r="74">
@@ -14405,7 +14405,7 @@
         <v>0.6200917579748507</v>
       </c>
       <c r="E74" t="n">
-        <v>0.6366800106273984</v>
+        <v>0.6366800106273985</v>
       </c>
       <c r="F74" t="n">
         <v>0.3640652003090395</v>
@@ -14501,7 +14501,7 @@
         <v>0.2706264854165202</v>
       </c>
       <c r="AK74" t="n">
-        <v>0.3600787651038706</v>
+        <v>0.3600787651038707</v>
       </c>
       <c r="AL74" t="n">
         <v>0.3747685100697778</v>
@@ -14510,13 +14510,13 @@
         <v>0.397060448327709</v>
       </c>
       <c r="AN74" t="n">
-        <v>0.3232928862631577</v>
+        <v>0.3232928862631578</v>
       </c>
       <c r="AO74" t="n">
         <v>0.287523056599517</v>
       </c>
       <c r="AP74" t="n">
-        <v>0.3174969969322278</v>
+        <v>0.3174969969322279</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.2444197551329816</v>
@@ -14528,7 +14528,7 @@
         <v>0.2799500228643972</v>
       </c>
       <c r="AT74" t="n">
-        <v>0.3510307047023836</v>
+        <v>0.3510307047023835</v>
       </c>
       <c r="AU74" t="n">
         <v>0.3540692955967938</v>
@@ -14921,7 +14921,7 @@
         <v>0.4954334773867137</v>
       </c>
       <c r="BQ76" t="n">
-        <v>0.4212700349100551</v>
+        <v>0.4212700349100552</v>
       </c>
       <c r="BR76" t="n">
         <v>0.198947780622982</v>
@@ -15658,19 +15658,19 @@
         <v>2.876260366036696</v>
       </c>
       <c r="F83" t="n">
-        <v>4.212694508202081</v>
+        <v>4.21269450820208</v>
       </c>
       <c r="G83" t="n">
-        <v>1.853032700079785</v>
+        <v>1.853032700079784</v>
       </c>
       <c r="H83" t="n">
-        <v>1.689037137221684</v>
+        <v>1.689037137221685</v>
       </c>
       <c r="I83" t="n">
-        <v>1.678543119192665</v>
+        <v>1.678543119192666</v>
       </c>
       <c r="J83" t="n">
-        <v>1.829842863678064</v>
+        <v>1.829842863678065</v>
       </c>
       <c r="K83" t="n">
         <v>2.17608127755277</v>
@@ -15706,10 +15706,10 @@
         <v>3.14215686504065</v>
       </c>
       <c r="V83" t="n">
-        <v>5.200489072612821</v>
+        <v>5.200489072612822</v>
       </c>
       <c r="W83" t="n">
-        <v>5.56351079166192</v>
+        <v>5.563510791661921</v>
       </c>
       <c r="X83" t="n">
         <v>4.749164277747942</v>
@@ -15787,7 +15787,7 @@
         <v>4.178666678548105</v>
       </c>
       <c r="AW83" t="n">
-        <v>5.597879441888275</v>
+        <v>5.597879441888274</v>
       </c>
       <c r="AX83" t="n">
         <v>5.025588049105167</v>
@@ -15796,16 +15796,16 @@
         <v>5.038937233802324</v>
       </c>
       <c r="AZ83" t="n">
-        <v>7.802645733807811</v>
+        <v>7.802645733807812</v>
       </c>
       <c r="BA83" t="n">
-        <v>8.0643749657727</v>
+        <v>8.064374965772698</v>
       </c>
       <c r="BB83" t="n">
-        <v>7.619175188219163</v>
+        <v>7.619175188219162</v>
       </c>
       <c r="BC83" t="n">
-        <v>9.34185091680018</v>
+        <v>9.341850916800182</v>
       </c>
       <c r="BD83" t="n">
         <v>11.13132543339599</v>
@@ -15814,34 +15814,34 @@
         <v>8.281263014930225</v>
       </c>
       <c r="BF83" t="n">
-        <v>6.867701433205148</v>
+        <v>6.867701433205149</v>
       </c>
       <c r="BG83" t="n">
-        <v>6.885711274535897</v>
+        <v>6.885711274535898</v>
       </c>
       <c r="BH83" t="n">
         <v>6.663061076369354</v>
       </c>
       <c r="BI83" t="n">
-        <v>6.83661864331992</v>
+        <v>6.836618643319919</v>
       </c>
       <c r="BJ83" t="n">
         <v>10.59384681221351</v>
       </c>
       <c r="BK83" t="n">
-        <v>9.753942406687768</v>
+        <v>9.75394240668777</v>
       </c>
       <c r="BL83" t="n">
-        <v>6.093971219116222</v>
+        <v>6.093971219116221</v>
       </c>
       <c r="BM83" t="n">
-        <v>6.174218420735309</v>
+        <v>6.17421842073531</v>
       </c>
       <c r="BN83" t="n">
         <v>4.044737082403086</v>
       </c>
       <c r="BO83" t="n">
-        <v>4.353968230626615</v>
+        <v>4.353968230626616</v>
       </c>
       <c r="BP83" t="n">
         <v>5.093105766481382</v>
@@ -15862,10 +15862,10 @@
         <v>5.106325163568669</v>
       </c>
       <c r="BV83" t="n">
-        <v>3.959930523306013</v>
+        <v>3.959930523306012</v>
       </c>
       <c r="BW83" t="n">
-        <v>4.557394467283236</v>
+        <v>4.557394467283237</v>
       </c>
       <c r="BX83" t="n">
         <v>4.547162423759946</v>
@@ -15874,7 +15874,7 @@
         <v>5.295652822652454</v>
       </c>
       <c r="BZ83" t="n">
-        <v>5.079524485052683</v>
+        <v>5.079524485052684</v>
       </c>
     </row>
     <row r="84">
@@ -15914,13 +15914,13 @@
         <v>0.5281159754846262</v>
       </c>
       <c r="L84" t="n">
-        <v>0.3347298202711428</v>
+        <v>0.3347298202711429</v>
       </c>
       <c r="M84" t="n">
         <v>0.2894938583441362</v>
       </c>
       <c r="N84" t="n">
-        <v>0.3122862156562228</v>
+        <v>0.3122862156562227</v>
       </c>
       <c r="O84" t="n">
         <v>0.5285166532310034</v>
@@ -15929,10 +15929,10 @@
         <v>0.5472088160063479</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.4955660905181578</v>
+        <v>0.4955660905181579</v>
       </c>
       <c r="R84" t="n">
-        <v>0.4632022778723618</v>
+        <v>0.4632022778723619</v>
       </c>
       <c r="S84" t="n">
         <v>0.5529760348488425</v>
@@ -15950,7 +15950,7 @@
         <v>1.012794952260917</v>
       </c>
       <c r="X84" t="n">
-        <v>0.8893890996536259</v>
+        <v>0.8893890996536258</v>
       </c>
       <c r="Y84" t="n">
         <v>1.069626165626541</v>
@@ -15971,7 +15971,7 @@
         <v>0.6347507605601701</v>
       </c>
       <c r="AE84" t="n">
-        <v>0.5156335680652688</v>
+        <v>0.5156335680652689</v>
       </c>
       <c r="AF84" t="n">
         <v>0.3245911069487588</v>
@@ -15995,7 +15995,7 @@
         <v>0.6091610825465367</v>
       </c>
       <c r="AM84" t="n">
-        <v>0.5142984173989417</v>
+        <v>0.5142984173989418</v>
       </c>
       <c r="AN84" t="n">
         <v>0.7547549066144904</v>
@@ -16004,16 +16004,16 @@
         <v>0.6307372728134093</v>
       </c>
       <c r="AP84" t="n">
-        <v>0.5769293648321137</v>
+        <v>0.5769293648321135</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.3142005654353192</v>
+        <v>0.3142005654353191</v>
       </c>
       <c r="AR84" t="n">
         <v>0.4910319049975715</v>
       </c>
       <c r="AS84" t="n">
-        <v>0.4025937841676208</v>
+        <v>0.4025937841676209</v>
       </c>
       <c r="AT84" t="n">
         <v>0.8215457704046119</v>
@@ -16022,7 +16022,7 @@
         <v>0.7226371687391281</v>
       </c>
       <c r="AV84" t="n">
-        <v>0.6522650802928905</v>
+        <v>0.6522650802928907</v>
       </c>
       <c r="AW84" t="n">
         <v>2.016113643332917</v>
@@ -16085,7 +16085,7 @@
         <v>1.079486591520434</v>
       </c>
       <c r="BQ84" t="n">
-        <v>0.9119414321488795</v>
+        <v>0.9119414321488793</v>
       </c>
       <c r="BR84" t="n">
         <v>0.9265148345070381</v>
@@ -16272,7 +16272,7 @@
         <v>3.484933315759847</v>
       </c>
       <c r="AZ85" t="n">
-        <v>0.7000798493063446</v>
+        <v>0.7000798493063447</v>
       </c>
       <c r="BA85" t="n">
         <v>1.491699902482934</v>
@@ -16292,7 +16292,7 @@
       <c r="BH85" t="inlineStr"/>
       <c r="BI85" t="inlineStr"/>
       <c r="BJ85" t="n">
-        <v>4.216839144542303</v>
+        <v>4.216839144542304</v>
       </c>
       <c r="BK85" t="n">
         <v>7.09997588920676</v>
@@ -16776,10 +16776,10 @@
         <v>0.080196226509938</v>
       </c>
       <c r="AZ89" t="n">
-        <v>0.08995309152763363</v>
+        <v>0.08995309152763364</v>
       </c>
       <c r="BA89" t="n">
-        <v>0.08495213748584293</v>
+        <v>0.08495213748584292</v>
       </c>
       <c r="BB89" t="inlineStr"/>
       <c r="BC89" t="inlineStr"/>
@@ -16934,10 +16934,10 @@
         <v>0.005128169598211417</v>
       </c>
       <c r="H91" t="n">
-        <v>0.004934281538811342</v>
+        <v>0.004934281538811341</v>
       </c>
       <c r="I91" t="n">
-        <v>0.004615980839953356</v>
+        <v>0.004615980839953355</v>
       </c>
       <c r="J91" t="n">
         <v>0.01109048634528731</v>
@@ -16949,7 +16949,7 @@
         <v>0.01126820629511671</v>
       </c>
       <c r="M91" t="n">
-        <v>0.003906739311408112</v>
+        <v>0.003906739311408113</v>
       </c>
       <c r="N91" t="n">
         <v>0.004864564605790016</v>
@@ -16961,10 +16961,10 @@
         <v>0.005104429648843259</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.004896702041713662</v>
+        <v>0.004896702041713663</v>
       </c>
       <c r="R91" t="n">
-        <v>0.004768375472542638</v>
+        <v>0.004768375472542639</v>
       </c>
       <c r="S91" t="n">
         <v>0.005908791673296735</v>
@@ -16973,7 +16973,7 @@
         <v>0.005519313224901472</v>
       </c>
       <c r="U91" t="n">
-        <v>0.006851309254681135</v>
+        <v>0.006851309254681137</v>
       </c>
       <c r="V91" t="n">
         <v>0.007206040986604118</v>
@@ -17006,7 +17006,7 @@
         <v>0.01246406530884596</v>
       </c>
       <c r="AF91" t="n">
-        <v>0.006014331563092281</v>
+        <v>0.00601433156309228</v>
       </c>
       <c r="AG91" t="n">
         <v>0.007042742835416198</v>
@@ -17018,7 +17018,7 @@
         <v>0.005607381837918363</v>
       </c>
       <c r="AJ91" t="n">
-        <v>0.00803235397348874</v>
+        <v>0.008032353973488738</v>
       </c>
       <c r="AK91" t="n">
         <v>0.01081533219513197</v>
@@ -17030,7 +17030,7 @@
         <v>0.01199015835028661</v>
       </c>
       <c r="AN91" t="n">
-        <v>0.007872694791481137</v>
+        <v>0.007872694791481139</v>
       </c>
       <c r="AO91" t="n">
         <v>0.00667227226010189</v>
@@ -17054,7 +17054,7 @@
         <v>0.008216830248491184</v>
       </c>
       <c r="AV91" t="n">
-        <v>0.004977381452137084</v>
+        <v>0.004977381452137083</v>
       </c>
       <c r="AW91" t="n">
         <v>0.004512193878169039</v>
@@ -17094,7 +17094,7 @@
         <v>0.002841010898929838</v>
       </c>
       <c r="BJ91" t="n">
-        <v>0.04542470413985878</v>
+        <v>0.04542470413985877</v>
       </c>
       <c r="BK91" t="n">
         <v>0.03067681324272945</v>
@@ -17729,13 +17729,13 @@
         <v>0.8895983021433984</v>
       </c>
       <c r="M95" t="n">
-        <v>0.4709756111027242</v>
+        <v>0.4709756111027243</v>
       </c>
       <c r="N95" t="n">
         <v>0.5237196468145875</v>
       </c>
       <c r="O95" t="n">
-        <v>0.634624373553365</v>
+        <v>0.6346243735533651</v>
       </c>
       <c r="P95" t="n">
         <v>0.6525376073775273</v>
@@ -17789,7 +17789,7 @@
         <v>0.6508834817073622</v>
       </c>
       <c r="AG95" t="n">
-        <v>0.8698486323271668</v>
+        <v>0.8698486323271666</v>
       </c>
       <c r="AH95" t="n">
         <v>0.646725714632963</v>
@@ -17819,7 +17819,7 @@
         <v>0.9691201029765193</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.6929628585263677</v>
+        <v>0.6929628585263676</v>
       </c>
       <c r="AR95" t="n">
         <v>0.8860935253256026</v>
@@ -17831,28 +17831,28 @@
         <v>1.16229019781048</v>
       </c>
       <c r="AU95" t="n">
-        <v>0.9888115691206726</v>
+        <v>0.9888115691206724</v>
       </c>
       <c r="AV95" t="n">
         <v>0.9478997630041396</v>
       </c>
       <c r="AW95" t="n">
-        <v>7.117545047036209</v>
+        <v>7.11754504703621</v>
       </c>
       <c r="AX95" t="n">
-        <v>1.063159875858529</v>
+        <v>1.063159875858528</v>
       </c>
       <c r="AY95" t="n">
         <v>1.412663303859853</v>
       </c>
       <c r="AZ95" t="n">
-        <v>0.70602500300139</v>
+        <v>0.7060250030013899</v>
       </c>
       <c r="BA95" t="n">
-        <v>0.7349419205000074</v>
+        <v>0.7349419205000072</v>
       </c>
       <c r="BB95" t="n">
-        <v>7.088246251706573</v>
+        <v>7.088246251706575</v>
       </c>
       <c r="BC95" t="n">
         <v>1.479178885354202</v>
@@ -17861,7 +17861,7 @@
         <v>4.056268984615319</v>
       </c>
       <c r="BE95" t="n">
-        <v>1.120268314867162</v>
+        <v>1.120268314867163</v>
       </c>
       <c r="BF95" t="n">
         <v>1.076446894096677</v>
@@ -17894,7 +17894,7 @@
         <v>4.319589039343176</v>
       </c>
       <c r="BP95" t="n">
-        <v>0.8337878450540919</v>
+        <v>0.8337878450540918</v>
       </c>
       <c r="BQ95" t="n">
         <v>0.6758106367871616</v>
@@ -17903,13 +17903,13 @@
         <v>4.608146826834149</v>
       </c>
       <c r="BS95" t="n">
-        <v>4.670304156912013</v>
+        <v>4.670304156912012</v>
       </c>
       <c r="BT95" t="n">
         <v>4.336233295896637</v>
       </c>
       <c r="BU95" t="n">
-        <v>4.279072152430221</v>
+        <v>4.279072152430222</v>
       </c>
       <c r="BV95" t="n">
         <v>3.229753915157485</v>
@@ -17921,7 +17921,7 @@
         <v>3.144868686394676</v>
       </c>
       <c r="BY95" t="n">
-        <v>1.80968483896427</v>
+        <v>1.809684838964271</v>
       </c>
       <c r="BZ95" t="n">
         <v>1.120261138227176</v>
@@ -18424,7 +18424,7 @@
         <v>0.008040442071039091</v>
       </c>
       <c r="H98" t="n">
-        <v>0.007508040187517181</v>
+        <v>0.007508040187517182</v>
       </c>
       <c r="I98" t="n">
         <v>0.007706368896515962</v>
@@ -18451,7 +18451,7 @@
         <v>0.008430220062481262</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.007121579146699981</v>
+        <v>0.00712157914669998</v>
       </c>
       <c r="R98" t="n">
         <v>0.007588133898597932</v>
@@ -18496,7 +18496,7 @@
         <v>0.01963366299781679</v>
       </c>
       <c r="AF98" t="n">
-        <v>0.009111422455150252</v>
+        <v>0.00911142245515025</v>
       </c>
       <c r="AG98" t="n">
         <v>0.01150970233835866</v>
@@ -18523,7 +18523,7 @@
         <v>0.01334722921470315</v>
       </c>
       <c r="AO98" t="n">
-        <v>0.01192469108976007</v>
+        <v>0.01192469108976008</v>
       </c>
       <c r="AP98" t="n">
         <v>0.01351947668345471</v>
@@ -18535,7 +18535,7 @@
         <v>0.01572045098272341</v>
       </c>
       <c r="AS98" t="n">
-        <v>0.009816492287825222</v>
+        <v>0.00981649228782522</v>
       </c>
       <c r="AT98" t="n">
         <v>0.01074690163255151</v>
@@ -18584,7 +18584,7 @@
         <v>0.01404980729007066</v>
       </c>
       <c r="BJ98" t="n">
-        <v>0.09186787815279047</v>
+        <v>0.09186787815279049</v>
       </c>
       <c r="BK98" t="n">
         <v>0.04754535403660589</v>
@@ -19894,10 +19894,10 @@
         <v>0.5777617225338523</v>
       </c>
       <c r="D110" t="n">
-        <v>0.8203879721364681</v>
+        <v>0.820387972136468</v>
       </c>
       <c r="E110" t="n">
-        <v>0.8131049572000668</v>
+        <v>0.8131049572000667</v>
       </c>
       <c r="F110" t="n">
         <v>1.101681046320983</v>
@@ -19909,7 +19909,7 @@
         <v>0.1769037724590967</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1500981025102045</v>
+        <v>0.1500981025102046</v>
       </c>
       <c r="J110" t="n">
         <v>0.1352454314643466</v>
@@ -19921,7 +19921,7 @@
         <v>0.1193313305629441</v>
       </c>
       <c r="M110" t="n">
-        <v>0.1422524532193522</v>
+        <v>0.1422524532193523</v>
       </c>
       <c r="N110" t="n">
         <v>0.165856313408598</v>
@@ -19963,7 +19963,7 @@
         <v>0.4267415427565374</v>
       </c>
       <c r="AA110" t="n">
-        <v>0.335438904753099</v>
+        <v>0.3354389047530989</v>
       </c>
       <c r="AB110" t="n">
         <v>0.1699020072627957</v>
@@ -19987,7 +19987,7 @@
         <v>0.1529226669772445</v>
       </c>
       <c r="AI110" t="n">
-        <v>0.2658360691248403</v>
+        <v>0.2658360691248404</v>
       </c>
       <c r="AJ110" t="n">
         <v>0.2642141253914863</v>
@@ -19999,16 +19999,16 @@
         <v>0.1731459227554564</v>
       </c>
       <c r="AM110" t="n">
-        <v>0.1483122214024858</v>
+        <v>0.1483122214024859</v>
       </c>
       <c r="AN110" t="n">
         <v>0.3077413614061968</v>
       </c>
       <c r="AO110" t="n">
-        <v>0.2754884550663589</v>
+        <v>0.275488455066359</v>
       </c>
       <c r="AP110" t="n">
-        <v>0.2707474481550592</v>
+        <v>0.2707474481550593</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.1588233871561141</v>
@@ -20026,7 +20026,7 @@
         <v>0.3696498472171501</v>
       </c>
       <c r="AV110" t="n">
-        <v>0.3408586798390868</v>
+        <v>0.3408586798390869</v>
       </c>
       <c r="AW110" t="n">
         <v>0.2721771506327155</v>
@@ -20050,7 +20050,7 @@
         <v>1.238081981698215</v>
       </c>
       <c r="BD110" t="n">
-        <v>1.627810069507341</v>
+        <v>1.627810069507342</v>
       </c>
       <c r="BE110" t="n">
         <v>1.083881189007949</v>
@@ -20074,7 +20074,7 @@
         <v>1.607469864471283</v>
       </c>
       <c r="BL110" t="n">
-        <v>0.4927698104548121</v>
+        <v>0.492769810454812</v>
       </c>
       <c r="BM110" t="n">
         <v>0.7269901477363294</v>
@@ -22970,7 +22970,7 @@
         <v>0.06368761987065533</v>
       </c>
       <c r="D135" t="n">
-        <v>0.0886393687445335</v>
+        <v>0.08863936874453349</v>
       </c>
       <c r="E135" t="n">
         <v>0.1129861501681015</v>
@@ -23114,7 +23114,7 @@
         <v>0.1046794069087727</v>
       </c>
       <c r="AZ135" t="n">
-        <v>0.08577680205984688</v>
+        <v>0.08577680205984686</v>
       </c>
       <c r="BA135" t="n">
         <v>0.06997255537417903</v>
@@ -23159,7 +23159,7 @@
         <v>0.03972482034911796</v>
       </c>
       <c r="BO135" t="n">
-        <v>0.08245760281988483</v>
+        <v>0.08245760281988482</v>
       </c>
       <c r="BP135" t="n">
         <v>0.1994972574816646</v>

--- a/data/proteomics/ecGEM_membrane_size_across_compartment.xlsx
+++ b/data/proteomics/ecGEM_membrane_size_across_compartment.xlsx
@@ -828,22 +828,22 @@
         <v>341.9349002733411</v>
       </c>
       <c r="D2" t="n">
-        <v>405.1947170903243</v>
+        <v>405.1947170903246</v>
       </c>
       <c r="E2" t="n">
         <v>363.0797480033033</v>
       </c>
       <c r="F2" t="n">
-        <v>274.5615582077581</v>
+        <v>274.5615582077583</v>
       </c>
       <c r="G2" t="n">
-        <v>172.9248932250705</v>
+        <v>172.9248932250703</v>
       </c>
       <c r="H2" t="n">
-        <v>155.4409650019626</v>
+        <v>155.4409650019624</v>
       </c>
       <c r="I2" t="n">
-        <v>159.9638404648632</v>
+        <v>159.9638404648634</v>
       </c>
       <c r="J2" t="n">
         <v>211.3460219146438</v>
@@ -852,31 +852,31 @@
         <v>221.5226409593047</v>
       </c>
       <c r="L2" t="n">
-        <v>187.9936846122835</v>
+        <v>187.9936846122837</v>
       </c>
       <c r="M2" t="n">
-        <v>120.8896936178489</v>
+        <v>120.8896936178488</v>
       </c>
       <c r="N2" t="n">
         <v>125.5907455487216</v>
       </c>
       <c r="O2" t="n">
-        <v>175.6405888892379</v>
+        <v>175.640588889238</v>
       </c>
       <c r="P2" t="n">
         <v>174.4105961189973</v>
       </c>
       <c r="Q2" t="n">
-        <v>151.1915042685537</v>
+        <v>151.1915042685536</v>
       </c>
       <c r="R2" t="n">
-        <v>152.6438936516335</v>
+        <v>152.6438936516334</v>
       </c>
       <c r="S2" t="n">
         <v>151.0877045263773</v>
       </c>
       <c r="T2" t="n">
-        <v>151.2432138679308</v>
+        <v>151.2432138679309</v>
       </c>
       <c r="U2" t="n">
         <v>156.8027671641793</v>
@@ -885,37 +885,37 @@
         <v>228.5194626076302</v>
       </c>
       <c r="W2" t="n">
-        <v>231.7730421083303</v>
+        <v>231.7730421083306</v>
       </c>
       <c r="X2" t="n">
-        <v>214.1382574620362</v>
+        <v>214.1382574620363</v>
       </c>
       <c r="Y2" t="n">
         <v>261.8597809286516</v>
       </c>
       <c r="Z2" t="n">
-        <v>279.0203552760471</v>
+        <v>279.020355276047</v>
       </c>
       <c r="AA2" t="n">
-        <v>278.354159069203</v>
+        <v>278.3541590692031</v>
       </c>
       <c r="AB2" t="n">
         <v>279.1885986168289</v>
       </c>
       <c r="AC2" t="n">
-        <v>321.811851960721</v>
+        <v>321.8118519607211</v>
       </c>
       <c r="AD2" t="n">
-        <v>330.9064607635642</v>
+        <v>330.9064607635643</v>
       </c>
       <c r="AE2" t="n">
-        <v>304.5224289388145</v>
+        <v>304.5224289388144</v>
       </c>
       <c r="AF2" t="n">
-        <v>193.4648870452864</v>
+        <v>193.4648870452865</v>
       </c>
       <c r="AG2" t="n">
-        <v>242.249692448021</v>
+        <v>242.2496924480211</v>
       </c>
       <c r="AH2" t="n">
         <v>130.8144880329804</v>
@@ -924,43 +924,43 @@
         <v>216.8915738065944</v>
       </c>
       <c r="AJ2" t="n">
-        <v>208.1922107061676</v>
+        <v>208.1922107061677</v>
       </c>
       <c r="AK2" t="n">
         <v>247.8031890058446</v>
       </c>
       <c r="AL2" t="n">
-        <v>306.4636294235856</v>
+        <v>306.4636294235857</v>
       </c>
       <c r="AM2" t="n">
-        <v>260.8792407341285</v>
+        <v>260.8792407341286</v>
       </c>
       <c r="AN2" t="n">
-        <v>239.2254599542548</v>
+        <v>239.2254599542547</v>
       </c>
       <c r="AO2" t="n">
         <v>224.9267901784002</v>
       </c>
       <c r="AP2" t="n">
-        <v>231.1852695671315</v>
+        <v>231.1852695671314</v>
       </c>
       <c r="AQ2" t="n">
-        <v>200.3269817688593</v>
+        <v>200.3269817688594</v>
       </c>
       <c r="AR2" t="n">
-        <v>246.7508226430674</v>
+        <v>246.7508226430676</v>
       </c>
       <c r="AS2" t="n">
         <v>230.1939020535299</v>
       </c>
       <c r="AT2" t="n">
-        <v>310.4983358499036</v>
+        <v>310.4983358499034</v>
       </c>
       <c r="AU2" t="n">
         <v>287.8726795786079</v>
       </c>
       <c r="AV2" t="n">
-        <v>290.1457783095438</v>
+        <v>290.145778309544</v>
       </c>
       <c r="AW2" t="n">
         <v>300.0662134307963</v>
@@ -969,43 +969,43 @@
         <v>267.4974357413823</v>
       </c>
       <c r="AY2" t="n">
-        <v>259.0950691120357</v>
+        <v>259.0950691120359</v>
       </c>
       <c r="AZ2" t="n">
-        <v>349.5896466973705</v>
+        <v>349.5896466973708</v>
       </c>
       <c r="BA2" t="n">
         <v>333.8867481268639</v>
       </c>
       <c r="BB2" t="n">
-        <v>586.6577469290878</v>
+        <v>586.6577469290883</v>
       </c>
       <c r="BC2" t="n">
         <v>329.343784027165</v>
       </c>
       <c r="BD2" t="n">
-        <v>580.1216431772926</v>
+        <v>580.1216431772924</v>
       </c>
       <c r="BE2" t="n">
-        <v>259.3538107294333</v>
+        <v>259.3538107294335</v>
       </c>
       <c r="BF2" t="n">
-        <v>331.4287800826103</v>
+        <v>331.4287800826102</v>
       </c>
       <c r="BG2" t="n">
-        <v>318.8434890755988</v>
+        <v>318.8434890755989</v>
       </c>
       <c r="BH2" t="n">
-        <v>355.8473788560285</v>
+        <v>355.8473788560281</v>
       </c>
       <c r="BI2" t="n">
-        <v>342.1197882023943</v>
+        <v>342.1197882023941</v>
       </c>
       <c r="BJ2" t="n">
-        <v>288.1491550572701</v>
+        <v>288.14915505727</v>
       </c>
       <c r="BK2" t="n">
-        <v>161.827811073294</v>
+        <v>161.8278110732939</v>
       </c>
       <c r="BL2" t="n">
         <v>153.8595194045932</v>
@@ -1017,37 +1017,37 @@
         <v>168.4520436957342</v>
       </c>
       <c r="BO2" t="n">
-        <v>242.6186507355089</v>
+        <v>242.618650735509</v>
       </c>
       <c r="BP2" t="n">
         <v>208.6930947151087</v>
       </c>
       <c r="BQ2" t="n">
-        <v>127.1555314028005</v>
+        <v>127.1555314028006</v>
       </c>
       <c r="BR2" t="n">
         <v>308.2392283694921</v>
       </c>
       <c r="BS2" t="n">
-        <v>326.3861040688067</v>
+        <v>326.3861040688064</v>
       </c>
       <c r="BT2" t="n">
-        <v>337.5075583366238</v>
+        <v>337.5075583366236</v>
       </c>
       <c r="BU2" t="n">
-        <v>359.4194068747439</v>
+        <v>359.4194068747441</v>
       </c>
       <c r="BV2" t="n">
-        <v>257.4587570664362</v>
+        <v>257.458757066436</v>
       </c>
       <c r="BW2" t="n">
-        <v>289.6519867845597</v>
+        <v>289.6519867845598</v>
       </c>
       <c r="BX2" t="n">
-        <v>292.4192857193287</v>
+        <v>292.4192857193289</v>
       </c>
       <c r="BY2" t="n">
-        <v>273.802865642655</v>
+        <v>273.8028656426549</v>
       </c>
       <c r="BZ2" t="n">
         <v>231.1502369602601</v>
@@ -1284,10 +1284,10 @@
         <v>0.08786240744922519</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0977604940289339</v>
+        <v>0.09776049402893387</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09373030712755939</v>
+        <v>0.09373030712755938</v>
       </c>
       <c r="F4" t="n">
         <v>0.2736685339738332</v>
@@ -1344,7 +1344,7 @@
         <v>0.06097944312664596</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05992828074712242</v>
+        <v>0.05992828074712241</v>
       </c>
       <c r="Y4" t="n">
         <v>0.06654170379663973</v>
@@ -1380,13 +1380,13 @@
         <v>0.05482466175825534</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.05196553583678645</v>
+        <v>0.05196553583678644</v>
       </c>
       <c r="AK4" t="n">
         <v>0.05086074976993901</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.05824023616950346</v>
+        <v>0.05824023616950345</v>
       </c>
       <c r="AM4" t="n">
         <v>0.05817918006249573</v>
@@ -1422,13 +1422,13 @@
         <v>0.1082664067649206</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1219220236452313</v>
+        <v>0.1219220236452314</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.1345487008519252</v>
+        <v>0.1345487008519253</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.1149655642176981</v>
+        <v>0.1149655642176982</v>
       </c>
       <c r="BA4" t="n">
         <v>0.126520460682318</v>
@@ -1437,10 +1437,10 @@
         <v>0.4228732170324209</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.4156136549686594</v>
+        <v>0.4156136549686593</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.7451551373727867</v>
+        <v>0.7451551373727868</v>
       </c>
       <c r="BE4" t="n">
         <v>0.3694220892547386</v>
@@ -1488,10 +1488,10 @@
         <v>0.2017787647790989</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.2728290756691354</v>
+        <v>0.2728290756691353</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.2945832900034389</v>
+        <v>0.294583290003439</v>
       </c>
       <c r="BV4" t="n">
         <v>0.2501104416478544</v>
@@ -1757,16 +1757,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>175.4839484593776</v>
+        <v>175.4839484593777</v>
       </c>
       <c r="D6" t="n">
         <v>104.9524906399786</v>
       </c>
       <c r="E6" t="n">
-        <v>92.3689964413791</v>
+        <v>92.36899644137914</v>
       </c>
       <c r="F6" t="n">
-        <v>125.29430404497</v>
+        <v>125.2943040449699</v>
       </c>
       <c r="G6" t="n">
         <v>67.1540926499316</v>
@@ -1775,31 +1775,31 @@
         <v>59.55086416278206</v>
       </c>
       <c r="I6" t="n">
-        <v>63.92916691663604</v>
+        <v>63.92916691663602</v>
       </c>
       <c r="J6" t="n">
-        <v>77.70009605634515</v>
+        <v>77.70009605634512</v>
       </c>
       <c r="K6" t="n">
-        <v>85.76619128918182</v>
+        <v>85.76619128918185</v>
       </c>
       <c r="L6" t="n">
-        <v>68.40745177144233</v>
+        <v>68.40745177144231</v>
       </c>
       <c r="M6" t="n">
         <v>51.76212624651816</v>
       </c>
       <c r="N6" t="n">
-        <v>53.11867279829027</v>
+        <v>53.11867279829029</v>
       </c>
       <c r="O6" t="n">
-        <v>65.66302516626348</v>
+        <v>65.66302516626351</v>
       </c>
       <c r="P6" t="n">
-        <v>72.27950266559915</v>
+        <v>72.2795026655992</v>
       </c>
       <c r="Q6" t="n">
-        <v>64.91522677922794</v>
+        <v>64.91522677922795</v>
       </c>
       <c r="R6" t="n">
         <v>62.77161794016624</v>
@@ -1808,19 +1808,19 @@
         <v>59.76283572635477</v>
       </c>
       <c r="T6" t="n">
-        <v>62.01783985095432</v>
+        <v>62.0178398509543</v>
       </c>
       <c r="U6" t="n">
         <v>64.44286089421347</v>
       </c>
       <c r="V6" t="n">
-        <v>93.10748693845257</v>
+        <v>93.1074869384526</v>
       </c>
       <c r="W6" t="n">
-        <v>93.58365912511361</v>
+        <v>93.5836591251136</v>
       </c>
       <c r="X6" t="n">
-        <v>89.69449523885871</v>
+        <v>89.69449523885872</v>
       </c>
       <c r="Y6" t="n">
         <v>112.6333373179989</v>
@@ -1829,37 +1829,37 @@
         <v>123.3412034750496</v>
       </c>
       <c r="AA6" t="n">
-        <v>112.8590213913089</v>
+        <v>112.8590213913088</v>
       </c>
       <c r="AB6" t="n">
-        <v>99.31938159640281</v>
+        <v>99.31938159640285</v>
       </c>
       <c r="AC6" t="n">
         <v>124.6340634093125</v>
       </c>
       <c r="AD6" t="n">
-        <v>131.5252905827194</v>
+        <v>131.5252905827195</v>
       </c>
       <c r="AE6" t="n">
-        <v>120.6445647834175</v>
+        <v>120.6445647834176</v>
       </c>
       <c r="AF6" t="n">
-        <v>64.376198759697</v>
+        <v>64.37619875969696</v>
       </c>
       <c r="AG6" t="n">
-        <v>83.01749336817693</v>
+        <v>83.01749336817687</v>
       </c>
       <c r="AH6" t="n">
-        <v>47.83625616617233</v>
+        <v>47.83625616617232</v>
       </c>
       <c r="AI6" t="n">
-        <v>81.3396925673957</v>
+        <v>81.33969256739572</v>
       </c>
       <c r="AJ6" t="n">
-        <v>80.33521034376383</v>
+        <v>80.33521034376385</v>
       </c>
       <c r="AK6" t="n">
-        <v>92.55553164731658</v>
+        <v>92.55553164731653</v>
       </c>
       <c r="AL6" t="n">
         <v>118.468423573499</v>
@@ -1868,10 +1868,10 @@
         <v>93.44124449291283</v>
       </c>
       <c r="AN6" t="n">
-        <v>97.55582982877583</v>
+        <v>97.55582982877584</v>
       </c>
       <c r="AO6" t="n">
-        <v>84.13186667825266</v>
+        <v>84.13186667825269</v>
       </c>
       <c r="AP6" t="n">
         <v>84.22489749825198</v>
@@ -1880,16 +1880,16 @@
         <v>65.26362408802045</v>
       </c>
       <c r="AR6" t="n">
-        <v>92.05602153984357</v>
+        <v>92.0560215398436</v>
       </c>
       <c r="AS6" t="n">
-        <v>69.66559203152326</v>
+        <v>69.66559203152327</v>
       </c>
       <c r="AT6" t="n">
         <v>107.2361736484064</v>
       </c>
       <c r="AU6" t="n">
-        <v>103.2412362346523</v>
+        <v>103.2412362346524</v>
       </c>
       <c r="AV6" t="n">
         <v>104.3847403411289</v>
@@ -1898,13 +1898,13 @@
         <v>124.089615540064</v>
       </c>
       <c r="AX6" t="n">
-        <v>72.50375961885449</v>
+        <v>72.5037596188545</v>
       </c>
       <c r="AY6" t="n">
-        <v>63.21708422287573</v>
+        <v>63.21708422287578</v>
       </c>
       <c r="AZ6" t="n">
-        <v>82.19488884521341</v>
+        <v>82.19488884521344</v>
       </c>
       <c r="BA6" t="n">
         <v>72.73883230735767</v>
@@ -1913,10 +1913,10 @@
         <v>174.6498131049931</v>
       </c>
       <c r="BC6" t="n">
-        <v>142.1194502172913</v>
+        <v>142.1194502172914</v>
       </c>
       <c r="BD6" t="n">
-        <v>209.1405143300437</v>
+        <v>209.1405143300436</v>
       </c>
       <c r="BE6" t="n">
         <v>122.3828946934715</v>
@@ -1931,7 +1931,7 @@
         <v>130.2718937998455</v>
       </c>
       <c r="BI6" t="n">
-        <v>127.3227166801646</v>
+        <v>127.3227166801647</v>
       </c>
       <c r="BJ6" t="n">
         <v>127.4098617017515</v>
@@ -1940,28 +1940,28 @@
         <v>66.92972781362373</v>
       </c>
       <c r="BL6" t="n">
-        <v>87.47102830314775</v>
+        <v>87.47102830314779</v>
       </c>
       <c r="BM6" t="n">
-        <v>71.54013841658086</v>
+        <v>71.54013841658083</v>
       </c>
       <c r="BN6" t="n">
-        <v>50.18613880570716</v>
+        <v>50.18613880570715</v>
       </c>
       <c r="BO6" t="n">
-        <v>60.81165837559851</v>
+        <v>60.8116583755985</v>
       </c>
       <c r="BP6" t="n">
-        <v>101.0188662304882</v>
+        <v>101.0188662304881</v>
       </c>
       <c r="BQ6" t="n">
-        <v>58.2169866523052</v>
+        <v>58.21698665230519</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.90347763437536</v>
+        <v>94.90347763437532</v>
       </c>
       <c r="BS6" t="n">
-        <v>96.90866742805292</v>
+        <v>96.90866742805291</v>
       </c>
       <c r="BT6" t="n">
         <v>101.7159524418537</v>
@@ -1970,19 +1970,19 @@
         <v>107.9586264108659</v>
       </c>
       <c r="BV6" t="n">
-        <v>77.04504175968441</v>
+        <v>77.04504175968444</v>
       </c>
       <c r="BW6" t="n">
-        <v>85.38288611857176</v>
+        <v>85.38288611857178</v>
       </c>
       <c r="BX6" t="n">
-        <v>89.7039130477246</v>
+        <v>89.70391304772464</v>
       </c>
       <c r="BY6" t="n">
-        <v>92.10861474080649</v>
+        <v>92.10861474080646</v>
       </c>
       <c r="BZ6" t="n">
-        <v>85.25046617113846</v>
+        <v>85.25046617113848</v>
       </c>
     </row>
     <row r="7">
@@ -1998,16 +1998,16 @@
         <v>393.780289854365</v>
       </c>
       <c r="D7" t="n">
-        <v>353.8297239250331</v>
+        <v>353.8297239250329</v>
       </c>
       <c r="E7" t="n">
-        <v>377.4425983687771</v>
+        <v>377.4425983687769</v>
       </c>
       <c r="F7" t="n">
-        <v>403.1396804407568</v>
+        <v>403.1396804407572</v>
       </c>
       <c r="G7" t="n">
-        <v>145.5494809724669</v>
+        <v>145.5494809724668</v>
       </c>
       <c r="H7" t="n">
         <v>130.9135813885022</v>
@@ -2019,16 +2019,16 @@
         <v>245.1879127668932</v>
       </c>
       <c r="K7" t="n">
-        <v>255.5709307696925</v>
+        <v>255.5709307696926</v>
       </c>
       <c r="L7" t="n">
-        <v>220.3210958773517</v>
+        <v>220.3210958773518</v>
       </c>
       <c r="M7" t="n">
         <v>105.0712846207883</v>
       </c>
       <c r="N7" t="n">
-        <v>111.0730701460938</v>
+        <v>111.0730701460937</v>
       </c>
       <c r="O7" t="n">
         <v>150.4600940928404</v>
@@ -2040,10 +2040,10 @@
         <v>126.3351471257817</v>
       </c>
       <c r="R7" t="n">
-        <v>129.6343786139362</v>
+        <v>129.6343786139361</v>
       </c>
       <c r="S7" t="n">
-        <v>138.6073066025021</v>
+        <v>138.607306602502</v>
       </c>
       <c r="T7" t="n">
         <v>134.93107888812</v>
@@ -2052,7 +2052,7 @@
         <v>136.2893836529861</v>
       </c>
       <c r="V7" t="n">
-        <v>215.1453954863058</v>
+        <v>215.1453954863055</v>
       </c>
       <c r="W7" t="n">
         <v>217.5674339710707</v>
@@ -2061,31 +2061,31 @@
         <v>212.1580742804857</v>
       </c>
       <c r="Y7" t="n">
-        <v>261.1162485178047</v>
+        <v>261.1162485178045</v>
       </c>
       <c r="Z7" t="n">
-        <v>269.0245211137775</v>
+        <v>269.0245211137773</v>
       </c>
       <c r="AA7" t="n">
         <v>273.4404460393056</v>
       </c>
       <c r="AB7" t="n">
-        <v>352.1539869970745</v>
+        <v>352.1539869970749</v>
       </c>
       <c r="AC7" t="n">
-        <v>425.9642767366879</v>
+        <v>425.9642767366882</v>
       </c>
       <c r="AD7" t="n">
-        <v>421.9433531924816</v>
+        <v>421.9433531924815</v>
       </c>
       <c r="AE7" t="n">
-        <v>318.1126415958857</v>
+        <v>318.1126415958858</v>
       </c>
       <c r="AF7" t="n">
-        <v>173.0338740538957</v>
+        <v>173.0338740538959</v>
       </c>
       <c r="AG7" t="n">
-        <v>208.3222249664169</v>
+        <v>208.322224966417</v>
       </c>
       <c r="AH7" t="n">
         <v>100.5966687668571</v>
@@ -2094,19 +2094,19 @@
         <v>174.9488408442104</v>
       </c>
       <c r="AJ7" t="n">
-        <v>175.9573605728364</v>
+        <v>175.9573605728363</v>
       </c>
       <c r="AK7" t="n">
         <v>222.1492721867724</v>
       </c>
       <c r="AL7" t="n">
-        <v>278.1109674714263</v>
+        <v>278.1109674714264</v>
       </c>
       <c r="AM7" t="n">
-        <v>231.7967840619459</v>
+        <v>231.7967840619461</v>
       </c>
       <c r="AN7" t="n">
-        <v>199.6478493085534</v>
+        <v>199.6478493085536</v>
       </c>
       <c r="AO7" t="n">
         <v>177.4639340983667</v>
@@ -2115,82 +2115,82 @@
         <v>190.3193770583186</v>
       </c>
       <c r="AQ7" t="n">
-        <v>187.7926486450443</v>
+        <v>187.7926486450444</v>
       </c>
       <c r="AR7" t="n">
-        <v>262.2362083886539</v>
+        <v>262.2362083886538</v>
       </c>
       <c r="AS7" t="n">
-        <v>202.9162520935215</v>
+        <v>202.9162520935216</v>
       </c>
       <c r="AT7" t="n">
-        <v>262.3901249987253</v>
+        <v>262.3901249987255</v>
       </c>
       <c r="AU7" t="n">
-        <v>234.5226054291994</v>
+        <v>234.5226054291992</v>
       </c>
       <c r="AV7" t="n">
-        <v>233.9243151753151</v>
+        <v>233.9243151753154</v>
       </c>
       <c r="AW7" t="n">
-        <v>278.3197735502646</v>
+        <v>278.3197735502644</v>
       </c>
       <c r="AX7" t="n">
-        <v>360.3273069585054</v>
+        <v>360.3273069585049</v>
       </c>
       <c r="AY7" t="n">
         <v>279.1185715185015</v>
       </c>
       <c r="AZ7" t="n">
-        <v>475.3744339991771</v>
+        <v>475.374433999177</v>
       </c>
       <c r="BA7" t="n">
         <v>401.446391350001</v>
       </c>
       <c r="BB7" t="n">
-        <v>500.2951941358538</v>
+        <v>500.2951941358534</v>
       </c>
       <c r="BC7" t="n">
         <v>343.1854401311076</v>
       </c>
       <c r="BD7" t="n">
-        <v>520.5667864658333</v>
+        <v>520.5667864658332</v>
       </c>
       <c r="BE7" t="n">
         <v>292.112908957438</v>
       </c>
       <c r="BF7" t="n">
-        <v>338.5581515773115</v>
+        <v>338.5581515773117</v>
       </c>
       <c r="BG7" t="n">
-        <v>333.3311871562322</v>
+        <v>333.3311871562324</v>
       </c>
       <c r="BH7" t="n">
-        <v>344.7328947216702</v>
+        <v>344.7328947216703</v>
       </c>
       <c r="BI7" t="n">
-        <v>342.1356160600157</v>
+        <v>342.1356160600159</v>
       </c>
       <c r="BJ7" t="n">
-        <v>336.0826507628212</v>
+        <v>336.0826507628214</v>
       </c>
       <c r="BK7" t="n">
-        <v>152.5296398490327</v>
+        <v>152.5296398490325</v>
       </c>
       <c r="BL7" t="n">
         <v>186.6481188223231</v>
       </c>
       <c r="BM7" t="n">
-        <v>214.4536583219589</v>
+        <v>214.453658321959</v>
       </c>
       <c r="BN7" t="n">
-        <v>154.9903349183698</v>
+        <v>154.9903349183697</v>
       </c>
       <c r="BO7" t="n">
         <v>196.7357390609293</v>
       </c>
       <c r="BP7" t="n">
-        <v>240.9612828350309</v>
+        <v>240.961282835031</v>
       </c>
       <c r="BQ7" t="n">
         <v>145.6101709004396</v>
@@ -2199,25 +2199,25 @@
         <v>244.7642180146869</v>
       </c>
       <c r="BS7" t="n">
-        <v>251.6224931814971</v>
+        <v>251.6224931814972</v>
       </c>
       <c r="BT7" t="n">
-        <v>263.9874116962216</v>
+        <v>263.9874116962217</v>
       </c>
       <c r="BU7" t="n">
-        <v>282.9906179885498</v>
+        <v>282.9906179885497</v>
       </c>
       <c r="BV7" t="n">
         <v>200.7959133700631</v>
       </c>
       <c r="BW7" t="n">
-        <v>227.2885759691805</v>
+        <v>227.2885759691806</v>
       </c>
       <c r="BX7" t="n">
         <v>235.1767751557642</v>
       </c>
       <c r="BY7" t="n">
-        <v>235.7546889003884</v>
+        <v>235.7546889003885</v>
       </c>
       <c r="BZ7" t="n">
         <v>215.9940827949831</v>
@@ -2236,7 +2236,7 @@
         <v>259.6384019303881</v>
       </c>
       <c r="D8" t="n">
-        <v>237.9917917902832</v>
+        <v>237.9917917902831</v>
       </c>
       <c r="E8" t="n">
         <v>193.9100589434975</v>
@@ -2245,16 +2245,16 @@
         <v>203.8738416486983</v>
       </c>
       <c r="G8" t="n">
-        <v>91.20085027116295</v>
+        <v>91.20085027116289</v>
       </c>
       <c r="H8" t="n">
-        <v>77.70618739212735</v>
+        <v>77.7061873921273</v>
       </c>
       <c r="I8" t="n">
-        <v>79.54076642419908</v>
+        <v>79.54076642419913</v>
       </c>
       <c r="J8" t="n">
-        <v>100.1165331364527</v>
+        <v>100.1165331364528</v>
       </c>
       <c r="K8" t="n">
         <v>105.9574565642989</v>
@@ -2272,19 +2272,19 @@
         <v>103.4165822371214</v>
       </c>
       <c r="P8" t="n">
-        <v>95.86266647732133</v>
+        <v>95.86266647732127</v>
       </c>
       <c r="Q8" t="n">
-        <v>83.789437189571</v>
+        <v>83.78943718957105</v>
       </c>
       <c r="R8" t="n">
         <v>80.91084856969363</v>
       </c>
       <c r="S8" t="n">
-        <v>74.14040837319683</v>
+        <v>74.14040837319689</v>
       </c>
       <c r="T8" t="n">
-        <v>77.67187524887824</v>
+        <v>77.67187524887822</v>
       </c>
       <c r="U8" t="n">
         <v>78.75396366684286</v>
@@ -2293,7 +2293,7 @@
         <v>125.7142997109812</v>
       </c>
       <c r="W8" t="n">
-        <v>126.5149532326239</v>
+        <v>126.514953232624</v>
       </c>
       <c r="X8" t="n">
         <v>121.2089115923363</v>
@@ -2305,28 +2305,28 @@
         <v>178.4559386647898</v>
       </c>
       <c r="AA8" t="n">
-        <v>165.7624110590197</v>
+        <v>165.7624110590196</v>
       </c>
       <c r="AB8" t="n">
         <v>128.1453128204851</v>
       </c>
       <c r="AC8" t="n">
-        <v>141.8083848124055</v>
+        <v>141.8083848124056</v>
       </c>
       <c r="AD8" t="n">
-        <v>156.5801394098188</v>
+        <v>156.5801394098187</v>
       </c>
       <c r="AE8" t="n">
-        <v>134.5592569463715</v>
+        <v>134.5592569463714</v>
       </c>
       <c r="AF8" t="n">
-        <v>97.54611162049457</v>
+        <v>97.5461116204946</v>
       </c>
       <c r="AG8" t="n">
         <v>125.4757951859946</v>
       </c>
       <c r="AH8" t="n">
-        <v>70.67714450207893</v>
+        <v>70.67714450207895</v>
       </c>
       <c r="AI8" t="n">
         <v>111.404893570467</v>
@@ -2335,7 +2335,7 @@
         <v>101.8026575009742</v>
       </c>
       <c r="AK8" t="n">
-        <v>99.27375227063077</v>
+        <v>99.27375227063072</v>
       </c>
       <c r="AL8" t="n">
         <v>120.9639896748585</v>
@@ -2350,10 +2350,10 @@
         <v>110.9991004188127</v>
       </c>
       <c r="AP8" t="n">
-        <v>109.6283722821634</v>
+        <v>109.6283722821635</v>
       </c>
       <c r="AQ8" t="n">
-        <v>91.09309068424334</v>
+        <v>91.09309068424342</v>
       </c>
       <c r="AR8" t="n">
         <v>105.1023021247009</v>
@@ -2362,7 +2362,7 @@
         <v>119.6925250784803</v>
       </c>
       <c r="AT8" t="n">
-        <v>178.0275097213576</v>
+        <v>178.0275097213575</v>
       </c>
       <c r="AU8" t="n">
         <v>155.8614180825734</v>
@@ -2374,16 +2374,16 @@
         <v>168.3714959459676</v>
       </c>
       <c r="AX8" t="n">
-        <v>130.1568424724953</v>
+        <v>130.1568424724954</v>
       </c>
       <c r="AY8" t="n">
-        <v>129.4759795993962</v>
+        <v>129.4759795993963</v>
       </c>
       <c r="AZ8" t="n">
-        <v>176.800075837195</v>
+        <v>176.8000758371951</v>
       </c>
       <c r="BA8" t="n">
-        <v>170.1827258067195</v>
+        <v>170.1827258067196</v>
       </c>
       <c r="BB8" t="n">
         <v>319.5444280154531</v>
@@ -2392,10 +2392,10 @@
         <v>219.9931359457752</v>
       </c>
       <c r="BD8" t="n">
-        <v>340.7134403738796</v>
+        <v>340.7134403738793</v>
       </c>
       <c r="BE8" t="n">
-        <v>182.7700552597775</v>
+        <v>182.7700552597774</v>
       </c>
       <c r="BF8" t="n">
         <v>192.5629880154603</v>
@@ -2422,28 +2422,28 @@
         <v>128.5812551175059</v>
       </c>
       <c r="BN8" t="n">
-        <v>92.84927936279969</v>
+        <v>92.84927936279972</v>
       </c>
       <c r="BO8" t="n">
         <v>133.5407599901005</v>
       </c>
       <c r="BP8" t="n">
-        <v>164.5631685377226</v>
+        <v>164.5631685377225</v>
       </c>
       <c r="BQ8" t="n">
-        <v>93.34187316634784</v>
+        <v>93.34187316634785</v>
       </c>
       <c r="BR8" t="n">
-        <v>177.2062987793513</v>
+        <v>177.2062987793514</v>
       </c>
       <c r="BS8" t="n">
-        <v>186.9444492472607</v>
+        <v>186.9444492472606</v>
       </c>
       <c r="BT8" t="n">
         <v>181.0451568225294</v>
       </c>
       <c r="BU8" t="n">
-        <v>184.8144563276101</v>
+        <v>184.8144563276099</v>
       </c>
       <c r="BV8" t="n">
         <v>121.523655542962</v>
@@ -2798,10 +2798,10 @@
         <v>109.1123406764097</v>
       </c>
       <c r="D11" t="n">
-        <v>71.57890644773205</v>
+        <v>71.57890644773207</v>
       </c>
       <c r="E11" t="n">
-        <v>36.10737895848247</v>
+        <v>36.10737895848248</v>
       </c>
       <c r="F11" t="n">
         <v>39.59501038679554</v>
@@ -2816,7 +2816,7 @@
         <v>16.65566243597129</v>
       </c>
       <c r="J11" t="n">
-        <v>18.80615048825731</v>
+        <v>18.80615048825732</v>
       </c>
       <c r="K11" t="n">
         <v>17.98082109436015</v>
@@ -2861,7 +2861,7 @@
         <v>33.20424335815306</v>
       </c>
       <c r="Y11" t="n">
-        <v>44.70782842883759</v>
+        <v>44.70782842883758</v>
       </c>
       <c r="Z11" t="n">
         <v>59.45583977656431</v>
@@ -2879,13 +2879,13 @@
         <v>27.10816099560179</v>
       </c>
       <c r="AE11" t="n">
-        <v>29.89204660793517</v>
+        <v>29.89204660793516</v>
       </c>
       <c r="AF11" t="n">
         <v>26.71956385605761</v>
       </c>
       <c r="AG11" t="n">
-        <v>32.49180909022745</v>
+        <v>32.49180909022746</v>
       </c>
       <c r="AH11" t="n">
         <v>22.3063530075021</v>
@@ -2897,7 +2897,7 @@
         <v>27.55098003582971</v>
       </c>
       <c r="AK11" t="n">
-        <v>19.79291657983976</v>
+        <v>19.79291657983977</v>
       </c>
       <c r="AL11" t="n">
         <v>21.2439005842122</v>
@@ -2921,16 +2921,16 @@
         <v>23.73273144190652</v>
       </c>
       <c r="AS11" t="n">
-        <v>33.11906976771949</v>
+        <v>33.11906976771948</v>
       </c>
       <c r="AT11" t="n">
-        <v>60.76674036159646</v>
+        <v>60.76674036159645</v>
       </c>
       <c r="AU11" t="n">
-        <v>45.41915066391886</v>
+        <v>45.41915066391884</v>
       </c>
       <c r="AV11" t="n">
-        <v>52.17934738613753</v>
+        <v>52.17934738613752</v>
       </c>
       <c r="AW11" t="n">
         <v>49.3562236148133</v>
@@ -2945,7 +2945,7 @@
         <v>9.845059625413011</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.994558773253489</v>
+        <v>8.994558773253488</v>
       </c>
       <c r="BB11" t="n">
         <v>55.27516274225574</v>
@@ -2954,10 +2954,10 @@
         <v>39.64465866347547</v>
       </c>
       <c r="BD11" t="n">
-        <v>62.45167749609767</v>
+        <v>62.45167749609768</v>
       </c>
       <c r="BE11" t="n">
-        <v>31.50811378881529</v>
+        <v>31.5081137888153</v>
       </c>
       <c r="BF11" t="n">
         <v>31.00183039461156</v>
@@ -2966,7 +2966,7 @@
         <v>30.15583617586826</v>
       </c>
       <c r="BH11" t="n">
-        <v>32.60700066214639</v>
+        <v>32.60700066214638</v>
       </c>
       <c r="BI11" t="n">
         <v>31.14348756056181</v>
@@ -2978,13 +2978,13 @@
         <v>6.657703299153503</v>
       </c>
       <c r="BL11" t="n">
-        <v>27.40215148090775</v>
+        <v>27.40215148090774</v>
       </c>
       <c r="BM11" t="n">
-        <v>7.272020155268199</v>
+        <v>7.272020155268198</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.975690048376064</v>
+        <v>3.975690048376065</v>
       </c>
       <c r="BO11" t="n">
         <v>7.837288826132356</v>
@@ -3033,40 +3033,40 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.119726172884627</v>
+        <v>7.119726172884628</v>
       </c>
       <c r="D12" t="n">
-        <v>7.562475616987794</v>
+        <v>7.562475616987798</v>
       </c>
       <c r="E12" t="n">
-        <v>8.265532563734284</v>
+        <v>8.265532563734281</v>
       </c>
       <c r="F12" t="n">
         <v>16.00799889328672</v>
       </c>
       <c r="G12" t="n">
-        <v>6.300152634979604</v>
+        <v>6.300152634979607</v>
       </c>
       <c r="H12" t="n">
-        <v>5.630198045120316</v>
+        <v>5.630198045120318</v>
       </c>
       <c r="I12" t="n">
-        <v>5.887144393701476</v>
+        <v>5.887144393701475</v>
       </c>
       <c r="J12" t="n">
-        <v>7.450227006249111</v>
+        <v>7.450227006249112</v>
       </c>
       <c r="K12" t="n">
-        <v>8.055520527258803</v>
+        <v>8.055520527258805</v>
       </c>
       <c r="L12" t="n">
-        <v>6.713320876612446</v>
+        <v>6.713320876612443</v>
       </c>
       <c r="M12" t="n">
-        <v>4.892222607041884</v>
+        <v>4.892222607041881</v>
       </c>
       <c r="N12" t="n">
-        <v>5.534472728367807</v>
+        <v>5.534472728367811</v>
       </c>
       <c r="O12" t="n">
         <v>5.88987599742088</v>
@@ -3075,19 +3075,19 @@
         <v>8.461873195224177</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.258310988917833</v>
+        <v>7.258310988917832</v>
       </c>
       <c r="R12" t="n">
-        <v>7.331866254835993</v>
+        <v>7.33186625483599</v>
       </c>
       <c r="S12" t="n">
-        <v>8.111145844434258</v>
+        <v>8.11114584443426</v>
       </c>
       <c r="T12" t="n">
         <v>7.43398762287099</v>
       </c>
       <c r="U12" t="n">
-        <v>8.063799081079626</v>
+        <v>8.063799081079624</v>
       </c>
       <c r="V12" t="n">
         <v>9.850610726158132</v>
@@ -3096,13 +3096,13 @@
         <v>10.16200164303329</v>
       </c>
       <c r="X12" t="n">
-        <v>10.03941519897695</v>
+        <v>10.03941519897694</v>
       </c>
       <c r="Y12" t="n">
         <v>10.47011006102952</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.85441070434241</v>
+        <v>10.85441070434242</v>
       </c>
       <c r="AA12" t="n">
         <v>11.38307679018548</v>
@@ -3111,37 +3111,37 @@
         <v>9.468306547395434</v>
       </c>
       <c r="AC12" t="n">
-        <v>12.25831233542274</v>
+        <v>12.25831233542275</v>
       </c>
       <c r="AD12" t="n">
-        <v>10.90954260419334</v>
+        <v>10.90954260419335</v>
       </c>
       <c r="AE12" t="n">
-        <v>9.12766637112588</v>
+        <v>9.127666371125882</v>
       </c>
       <c r="AF12" t="n">
-        <v>5.601882372158085</v>
+        <v>5.601882372158089</v>
       </c>
       <c r="AG12" t="n">
-        <v>6.627505054501247</v>
+        <v>6.627505054501246</v>
       </c>
       <c r="AH12" t="n">
-        <v>5.867923417894614</v>
+        <v>5.867923417894617</v>
       </c>
       <c r="AI12" t="n">
-        <v>9.601721832016622</v>
+        <v>9.601721832016626</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9.636553016470373</v>
+        <v>9.636553016470376</v>
       </c>
       <c r="AK12" t="n">
-        <v>8.514192491464645</v>
+        <v>8.514192491464641</v>
       </c>
       <c r="AL12" t="n">
         <v>8.982038243924654</v>
       </c>
       <c r="AM12" t="n">
-        <v>7.828985586025186</v>
+        <v>7.828985586025188</v>
       </c>
       <c r="AN12" t="n">
         <v>11.22002790629118</v>
@@ -3153,25 +3153,25 @@
         <v>10.98133855129794</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.918029814334999</v>
+        <v>5.918029814335001</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.642043816150816</v>
+        <v>8.642043816150812</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.427689113020836</v>
+        <v>6.427689113020834</v>
       </c>
       <c r="AT12" t="n">
         <v>10.47670249691913</v>
       </c>
       <c r="AU12" t="n">
-        <v>9.918212580541823</v>
+        <v>9.918212580541816</v>
       </c>
       <c r="AV12" t="n">
         <v>10.46723928242286</v>
       </c>
       <c r="AW12" t="n">
-        <v>9.645161436810907</v>
+        <v>9.645161436810911</v>
       </c>
       <c r="AX12" t="n">
         <v>12.45232150727709</v>
@@ -3189,7 +3189,7 @@
         <v>20.13826334412985</v>
       </c>
       <c r="BC12" t="n">
-        <v>18.80404921272088</v>
+        <v>18.80404921272087</v>
       </c>
       <c r="BD12" t="n">
         <v>29.46518008114433</v>
@@ -3201,31 +3201,31 @@
         <v>10.44441464777265</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.934698849405052</v>
+        <v>9.934698849405049</v>
       </c>
       <c r="BH12" t="n">
         <v>11.82642877078547</v>
       </c>
       <c r="BI12" t="n">
-        <v>13.05479532010818</v>
+        <v>13.05479532010817</v>
       </c>
       <c r="BJ12" t="n">
-        <v>25.28616009490269</v>
+        <v>25.28616009490268</v>
       </c>
       <c r="BK12" t="n">
         <v>22.36894723670345</v>
       </c>
       <c r="BL12" t="n">
-        <v>7.418176421548394</v>
+        <v>7.418176421548393</v>
       </c>
       <c r="BM12" t="n">
         <v>10.60120257193019</v>
       </c>
       <c r="BN12" t="n">
-        <v>7.305559463920196</v>
+        <v>7.305559463920195</v>
       </c>
       <c r="BO12" t="n">
-        <v>9.001960857255506</v>
+        <v>9.001960857255499</v>
       </c>
       <c r="BP12" t="n">
         <v>18.91021731681725</v>
@@ -3234,7 +3234,7 @@
         <v>13.93135630752183</v>
       </c>
       <c r="BR12" t="n">
-        <v>9.074348346552322</v>
+        <v>9.074348346552325</v>
       </c>
       <c r="BS12" t="n">
         <v>11.10736995302925</v>
@@ -3255,10 +3255,10 @@
         <v>9.463919591777469</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.750879621111334</v>
+        <v>8.750879621111338</v>
       </c>
       <c r="BZ12" t="n">
-        <v>7.559758207517533</v>
+        <v>7.559758207517532</v>
       </c>
     </row>
     <row r="13">
@@ -3482,13 +3482,13 @@
         <v>2.73724876836601</v>
       </c>
       <c r="D14" t="n">
-        <v>3.704221155906143</v>
+        <v>3.704221155906144</v>
       </c>
       <c r="E14" t="n">
-        <v>5.733964050634744</v>
+        <v>5.733964050634745</v>
       </c>
       <c r="F14" t="n">
-        <v>2.974289202623177</v>
+        <v>2.974289202623176</v>
       </c>
       <c r="G14" t="n">
         <v>2.884630251876803</v>
@@ -3497,10 +3497,10 @@
         <v>2.648520191739398</v>
       </c>
       <c r="I14" t="n">
-        <v>2.693229997986612</v>
+        <v>2.693229997986613</v>
       </c>
       <c r="J14" t="n">
-        <v>4.564044002773525</v>
+        <v>4.564044002773524</v>
       </c>
       <c r="K14" t="n">
         <v>4.589636633851856</v>
@@ -3515,22 +3515,22 @@
         <v>2.077071576155619</v>
       </c>
       <c r="O14" t="n">
-        <v>2.653515436727282</v>
+        <v>2.653515436727281</v>
       </c>
       <c r="P14" t="n">
         <v>3.115059685007847</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.565268812341075</v>
+        <v>2.565268812341076</v>
       </c>
       <c r="R14" t="n">
         <v>2.681845966729323</v>
       </c>
       <c r="S14" t="n">
-        <v>2.882727258011036</v>
+        <v>2.882727258011035</v>
       </c>
       <c r="T14" t="n">
-        <v>2.844422465955986</v>
+        <v>2.844422465955987</v>
       </c>
       <c r="U14" t="n">
         <v>2.872952807615336</v>
@@ -3542,10 +3542,10 @@
         <v>3.78306195369356</v>
       </c>
       <c r="X14" t="n">
-        <v>3.242149192442682</v>
+        <v>3.242149192442681</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.709337859762214</v>
+        <v>3.709337859762215</v>
       </c>
       <c r="Z14" t="n">
         <v>3.501202473720594</v>
@@ -3557,22 +3557,22 @@
         <v>5.002605723416268</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.005097987926042</v>
+        <v>6.005097987926041</v>
       </c>
       <c r="AD14" t="n">
-        <v>5.725753559603689</v>
+        <v>5.725753559603687</v>
       </c>
       <c r="AE14" t="n">
-        <v>4.964500339772381</v>
+        <v>4.964500339772383</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.109585448738489</v>
+        <v>3.109585448738488</v>
       </c>
       <c r="AG14" t="n">
         <v>3.688370817368179</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.210687422774046</v>
+        <v>2.210687422774047</v>
       </c>
       <c r="AI14" t="n">
         <v>3.751449962316109</v>
@@ -3581,16 +3581,16 @@
         <v>3.656342181344686</v>
       </c>
       <c r="AK14" t="n">
-        <v>5.835227707618188</v>
+        <v>5.835227707618187</v>
       </c>
       <c r="AL14" t="n">
-        <v>6.470751522744527</v>
+        <v>6.470751522744526</v>
       </c>
       <c r="AM14" t="n">
-        <v>5.852555910684661</v>
+        <v>5.852555910684662</v>
       </c>
       <c r="AN14" t="n">
-        <v>4.216924019479625</v>
+        <v>4.216924019479624</v>
       </c>
       <c r="AO14" t="n">
         <v>3.926920303068532</v>
@@ -3602,13 +3602,13 @@
         <v>3.278521063401074</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.274742080522755</v>
+        <v>4.274742080522753</v>
       </c>
       <c r="AS14" t="n">
         <v>3.529821224588815</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.55805186391931</v>
+        <v>4.558051863919309</v>
       </c>
       <c r="AU14" t="n">
         <v>4.138163419906759</v>
@@ -3617,13 +3617,13 @@
         <v>3.784626429883467</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.585258363964558</v>
+        <v>9.585258363964559</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.030880232661431</v>
+        <v>4.030880232661429</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.809455031417994</v>
+        <v>4.809455031417992</v>
       </c>
       <c r="AZ14" t="n">
         <v>4.291095192098195</v>
@@ -3641,13 +3641,13 @@
         <v>17.1019590799415</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.205433146633949</v>
+        <v>8.205433146633952</v>
       </c>
       <c r="BF14" t="n">
         <v>7.068399123847304</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.855215211366762</v>
+        <v>6.85521521136676</v>
       </c>
       <c r="BH14" t="n">
         <v>7.97063963125983</v>
@@ -3656,28 +3656,28 @@
         <v>7.86255733759717</v>
       </c>
       <c r="BJ14" t="n">
-        <v>6.247833745439517</v>
+        <v>6.247833745439515</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.407094868010319</v>
+        <v>4.407094868010318</v>
       </c>
       <c r="BL14" t="n">
         <v>4.029274841366272</v>
       </c>
       <c r="BM14" t="n">
-        <v>5.19657193041588</v>
+        <v>5.196571930415881</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.669798646290508</v>
+        <v>4.669798646290509</v>
       </c>
       <c r="BO14" t="n">
-        <v>6.451691336322648</v>
+        <v>6.451691336322647</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.715240122410269</v>
+        <v>4.715240122410268</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.633698415573896</v>
+        <v>3.633698415573897</v>
       </c>
       <c r="BR14" t="n">
         <v>8.505614995591266</v>
@@ -3692,7 +3692,7 @@
         <v>12.40539659886712</v>
       </c>
       <c r="BV14" t="n">
-        <v>8.770307620867031</v>
+        <v>8.770307620867033</v>
       </c>
       <c r="BW14" t="n">
         <v>9.046576423086764</v>
@@ -3744,7 +3744,7 @@
         <v>0.6338891872736576</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5408654221818031</v>
+        <v>0.5408654221818032</v>
       </c>
       <c r="M15" t="n">
         <v>0.2707096328339683</v>
@@ -3789,13 +3789,13 @@
         <v>0.2838597681689801</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.3264662012740702</v>
+        <v>0.3264662012740701</v>
       </c>
       <c r="AB15" t="n">
         <v>0.7523043379194488</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.8840509888624619</v>
+        <v>0.884050988862462</v>
       </c>
       <c r="AD15" t="n">
         <v>0.7814367727596728</v>
@@ -3861,7 +3861,7 @@
         <v>0.4355942448793372</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.4573847186238347</v>
+        <v>0.4573847186238346</v>
       </c>
       <c r="AZ15" t="n">
         <v>0.2610041793806743</v>
@@ -3964,16 +3964,16 @@
         <v>2.43346234594654</v>
       </c>
       <c r="F16" t="n">
-        <v>4.260626849865521</v>
+        <v>4.26062684986552</v>
       </c>
       <c r="G16" t="n">
         <v>0.8124514881825597</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7154757840337828</v>
+        <v>0.7154757840337829</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7139322407803498</v>
+        <v>0.7139322407803499</v>
       </c>
       <c r="J16" t="n">
         <v>1.009737764865348</v>
@@ -4003,7 +4003,7 @@
         <v>1.017886090537425</v>
       </c>
       <c r="S16" t="n">
-        <v>1.198901317211412</v>
+        <v>1.198901317211411</v>
       </c>
       <c r="T16" t="n">
         <v>1.173941069908905</v>
@@ -4024,7 +4024,7 @@
         <v>1.890639599921594</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.937157462730368</v>
+        <v>1.937157462730369</v>
       </c>
       <c r="AA16" t="n">
         <v>1.930519431236428</v>
@@ -4054,7 +4054,7 @@
         <v>1.232726099951339</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.251918500717988</v>
+        <v>1.251918500717989</v>
       </c>
       <c r="AK16" t="n">
         <v>1.166014605838879</v>
@@ -4066,7 +4066,7 @@
         <v>1.264165274572487</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.449179112906695</v>
+        <v>1.449179112906696</v>
       </c>
       <c r="AO16" t="n">
         <v>1.27747482265898</v>
@@ -4084,7 +4084,7 @@
         <v>1.493492289087764</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.219925780238132</v>
+        <v>1.219925780238131</v>
       </c>
       <c r="AU16" t="n">
         <v>1.331219911601964</v>
@@ -4132,7 +4132,7 @@
         <v>3.975392777616582</v>
       </c>
       <c r="BJ16" t="n">
-        <v>4.854055010812435</v>
+        <v>4.854055010812434</v>
       </c>
       <c r="BK16" t="n">
         <v>1.366914610038924</v>
@@ -4141,16 +4141,16 @@
         <v>2.097597127301287</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.713805059357085</v>
+        <v>2.713805059357084</v>
       </c>
       <c r="BN16" t="n">
         <v>2.493284871738283</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.765541627358883</v>
+        <v>1.765541627358884</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.388603069078179</v>
+        <v>3.388603069078178</v>
       </c>
       <c r="BQ16" t="n">
         <v>2.726011635312589</v>
@@ -4214,7 +4214,7 @@
         <v>1.455085761664387</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5791992035854638</v>
+        <v>0.579199203585464</v>
       </c>
       <c r="K17" t="n">
         <v>0.6685532085044581</v>
@@ -4223,7 +4223,7 @@
         <v>0.4697057072433491</v>
       </c>
       <c r="M17" t="n">
-        <v>1.344165002528123</v>
+        <v>1.344165002528124</v>
       </c>
       <c r="N17" t="n">
         <v>1.613132358952614</v>
@@ -4232,7 +4232,7 @@
         <v>1.187095413485738</v>
       </c>
       <c r="P17" t="n">
-        <v>2.33405294963545</v>
+        <v>2.334052949635449</v>
       </c>
       <c r="Q17" t="n">
         <v>1.861746586228385</v>
@@ -4265,7 +4265,7 @@
         <v>1.61976681551037</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.066300982460669</v>
+        <v>2.066300982460668</v>
       </c>
       <c r="AB17" t="n">
         <v>0.8517357928110728</v>
@@ -4274,10 +4274,10 @@
         <v>1.056416984442829</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.9712850494304833</v>
+        <v>0.9712850494304832</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.739308089192848</v>
+        <v>0.7393080891928481</v>
       </c>
       <c r="AF17" t="n">
         <v>0.3959602690686879</v>
@@ -4289,10 +4289,10 @@
         <v>1.567086903802778</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.569738971781009</v>
+        <v>2.569738971781008</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.623080545222473</v>
+        <v>2.623080545222472</v>
       </c>
       <c r="AK17" t="n">
         <v>0.6811707184867224</v>
@@ -4313,13 +4313,13 @@
         <v>3.07269880998091</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.5845843812738988</v>
+        <v>0.5845843812738989</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.9229575246364823</v>
+        <v>0.9229575246364824</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.3963816907185663</v>
+        <v>0.3963816907185662</v>
       </c>
       <c r="AT17" t="n">
         <v>1.442776234657101</v>
@@ -4337,7 +4337,7 @@
         <v>0.2060858071765607</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.1423320266351983</v>
+        <v>0.1423320266351984</v>
       </c>
       <c r="AZ17" t="n">
         <v>0.1981082734354341</v>
@@ -4376,7 +4376,7 @@
         <v>0.08990759903743943</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.104913239465076</v>
+        <v>0.1049132394650761</v>
       </c>
       <c r="BM17" t="n">
         <v>0.1240662684631982</v>
@@ -4388,10 +4388,10 @@
         <v>0.3063629491297378</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.8583838298449807</v>
+        <v>0.8583838298449806</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.4190986298550225</v>
+        <v>0.4190986298550226</v>
       </c>
       <c r="BR17" t="n">
         <v>0.3032374427750849</v>
@@ -4667,16 +4667,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.7735901701984709</v>
+        <v>0.773590170198471</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4653190711638118</v>
+        <v>0.4653190711638117</v>
       </c>
       <c r="E19" t="n">
         <v>0.6354157249715496</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9927081126518774</v>
+        <v>0.9927081126518773</v>
       </c>
       <c r="G19" t="n">
         <v>0.3418049884001831</v>
@@ -4691,7 +4691,7 @@
         <v>0.4748873159214426</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5098564734812681</v>
+        <v>0.5098564734812682</v>
       </c>
       <c r="L19" t="n">
         <v>0.4667664620544784</v>
@@ -4814,10 +4814,10 @@
         <v>0.9918745085507767</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.6108120080821583</v>
+        <v>0.6108120080821582</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.756563576715778</v>
+        <v>0.7565635767157779</v>
       </c>
       <c r="BB19" t="n">
         <v>0.4146632085311309</v>
@@ -4862,7 +4862,7 @@
         <v>0.1554565297458091</v>
       </c>
       <c r="BP19" t="n">
-        <v>1.614962049962967</v>
+        <v>1.614962049962966</v>
       </c>
       <c r="BQ19" t="n">
         <v>1.320641510840016</v>
@@ -4889,7 +4889,7 @@
         <v>0.404813652145684</v>
       </c>
       <c r="BY19" t="n">
-        <v>0.4292371850066529</v>
+        <v>0.4292371850066528</v>
       </c>
       <c r="BZ19" t="n">
         <v>0.3961282539063952</v>
@@ -4917,7 +4917,7 @@
         <v>8.628859541400345</v>
       </c>
       <c r="G20" t="n">
-        <v>3.014440162275169</v>
+        <v>3.01444016227517</v>
       </c>
       <c r="H20" t="n">
         <v>2.575352704987752</v>
@@ -4929,7 +4929,7 @@
         <v>4.569866195256066</v>
       </c>
       <c r="K20" t="n">
-        <v>4.556597900427715</v>
+        <v>4.556597900427714</v>
       </c>
       <c r="L20" t="n">
         <v>3.806525871489071</v>
@@ -4944,7 +4944,7 @@
         <v>3.592748794035064</v>
       </c>
       <c r="P20" t="n">
-        <v>3.76797152001436</v>
+        <v>3.767971520014359</v>
       </c>
       <c r="Q20" t="n">
         <v>3.228757101193537</v>
@@ -4965,7 +4965,7 @@
         <v>7.79719706618496</v>
       </c>
       <c r="W20" t="n">
-        <v>7.616062654817821</v>
+        <v>7.616062654817822</v>
       </c>
       <c r="X20" t="n">
         <v>7.504611354894319</v>
@@ -4977,7 +4977,7 @@
         <v>7.723196175775692</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.51510512489957</v>
+        <v>9.515105124899572</v>
       </c>
       <c r="AB20" t="n">
         <v>6.170929639670693</v>
@@ -5016,7 +5016,7 @@
         <v>3.597234933670768</v>
       </c>
       <c r="AN20" t="n">
-        <v>4.386258042226513</v>
+        <v>4.386258042226514</v>
       </c>
       <c r="AO20" t="n">
         <v>3.605185078575199</v>
@@ -5034,13 +5034,13 @@
         <v>4.03022663822675</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.957934772927239</v>
+        <v>5.95793477292724</v>
       </c>
       <c r="AU20" t="n">
-        <v>5.726468636419575</v>
+        <v>5.726468636419576</v>
       </c>
       <c r="AV20" t="n">
-        <v>6.582639319704821</v>
+        <v>6.58263931970482</v>
       </c>
       <c r="AW20" t="n">
         <v>2.580612427823259</v>
@@ -5462,10 +5462,10 @@
         <v>111.9651332624607</v>
       </c>
       <c r="D23" t="n">
-        <v>74.46818141774904</v>
+        <v>74.46818141774902</v>
       </c>
       <c r="E23" t="n">
-        <v>39.3458420393398</v>
+        <v>39.34584203933981</v>
       </c>
       <c r="F23" t="n">
         <v>41.95366035123351</v>
@@ -5474,7 +5474,7 @@
         <v>26.87321717524441</v>
       </c>
       <c r="H23" t="n">
-        <v>21.41389844644233</v>
+        <v>21.41389844644234</v>
       </c>
       <c r="I23" t="n">
         <v>18.47414650033026</v>
@@ -5483,7 +5483,7 @@
         <v>21.43980283870801</v>
       </c>
       <c r="K23" t="n">
-        <v>20.57881981755401</v>
+        <v>20.578819817554</v>
       </c>
       <c r="L23" t="n">
         <v>19.68671415745135</v>
@@ -5498,19 +5498,19 @@
         <v>38.19854184731548</v>
       </c>
       <c r="P23" t="n">
-        <v>29.09293322891899</v>
+        <v>29.09293322891898</v>
       </c>
       <c r="Q23" t="n">
-        <v>24.42270259705824</v>
+        <v>24.42270259705823</v>
       </c>
       <c r="R23" t="n">
         <v>23.00401462267708</v>
       </c>
       <c r="S23" t="n">
-        <v>19.72058261024681</v>
+        <v>19.72058261024682</v>
       </c>
       <c r="T23" t="n">
-        <v>21.99508738517612</v>
+        <v>21.99508738517611</v>
       </c>
       <c r="U23" t="n">
         <v>19.35975687148134</v>
@@ -5519,16 +5519,16 @@
         <v>36.73156940755083</v>
       </c>
       <c r="W23" t="n">
-        <v>38.13961512036101</v>
+        <v>38.13961512036103</v>
       </c>
       <c r="X23" t="n">
-        <v>36.01378592008253</v>
+        <v>36.01378592008252</v>
       </c>
       <c r="Y23" t="n">
-        <v>47.95407109056902</v>
+        <v>47.954071090569</v>
       </c>
       <c r="Z23" t="n">
-        <v>62.47586000875877</v>
+        <v>62.47586000875876</v>
       </c>
       <c r="AA23" t="n">
         <v>51.40054702504174</v>
@@ -5537,49 +5537,49 @@
         <v>18.69342771522822</v>
       </c>
       <c r="AC23" t="n">
-        <v>24.89015482015797</v>
+        <v>24.89015482015798</v>
       </c>
       <c r="AD23" t="n">
         <v>29.7944279067285</v>
       </c>
       <c r="AE23" t="n">
-        <v>32.02601838215921</v>
+        <v>32.02601838215919</v>
       </c>
       <c r="AF23" t="n">
-        <v>28.80526633110571</v>
+        <v>28.8052663311057</v>
       </c>
       <c r="AG23" t="n">
-        <v>34.54786208788661</v>
+        <v>34.5478620878866</v>
       </c>
       <c r="AH23" t="n">
         <v>24.74845956415302</v>
       </c>
       <c r="AI23" t="n">
-        <v>37.25685060014577</v>
+        <v>37.25685060014578</v>
       </c>
       <c r="AJ23" t="n">
         <v>30.39395369418602</v>
       </c>
       <c r="AK23" t="n">
-        <v>23.04313486797042</v>
+        <v>23.04313486797041</v>
       </c>
       <c r="AL23" t="n">
-        <v>24.46194013129455</v>
+        <v>24.46194013129454</v>
       </c>
       <c r="AM23" t="n">
-        <v>22.95735330478274</v>
+        <v>22.95735330478273</v>
       </c>
       <c r="AN23" t="n">
-        <v>32.6931322774023</v>
+        <v>32.69313227740229</v>
       </c>
       <c r="AO23" t="n">
         <v>33.83385132245898</v>
       </c>
       <c r="AP23" t="n">
-        <v>34.76916181143743</v>
+        <v>34.76916181143744</v>
       </c>
       <c r="AQ23" t="n">
-        <v>23.02030589020389</v>
+        <v>23.02030589020388</v>
       </c>
       <c r="AR23" t="n">
         <v>26.22333568261248</v>
@@ -5588,16 +5588,16 @@
         <v>35.83072811848898</v>
       </c>
       <c r="AT23" t="n">
-        <v>64.84761631768939</v>
+        <v>64.8476163176894</v>
       </c>
       <c r="AU23" t="n">
-        <v>48.8737101695546</v>
+        <v>48.87371016955461</v>
       </c>
       <c r="AV23" t="n">
-        <v>55.39613793815887</v>
+        <v>55.39613793815888</v>
       </c>
       <c r="AW23" t="n">
-        <v>59.21691419238613</v>
+        <v>59.21691419238612</v>
       </c>
       <c r="AX23" t="n">
         <v>8.228715909647898</v>
@@ -5615,10 +5615,10 @@
         <v>69.84836341056911</v>
       </c>
       <c r="BC23" t="n">
-        <v>50.77743693856383</v>
+        <v>50.77743693856382</v>
       </c>
       <c r="BD23" t="n">
-        <v>81.0366459704161</v>
+        <v>81.03664597041612</v>
       </c>
       <c r="BE23" t="n">
         <v>40.71822344716205</v>
@@ -5648,16 +5648,16 @@
         <v>13.54686600387851</v>
       </c>
       <c r="BN23" t="n">
-        <v>9.777613208107235</v>
+        <v>9.777613208107237</v>
       </c>
       <c r="BO23" t="n">
-        <v>14.73438081215211</v>
+        <v>14.73438081215212</v>
       </c>
       <c r="BP23" t="n">
-        <v>34.35521399945725</v>
+        <v>34.35521399945724</v>
       </c>
       <c r="BQ23" t="n">
-        <v>21.40225801811749</v>
+        <v>21.4022580181175</v>
       </c>
       <c r="BR23" t="n">
         <v>40.19329232127688</v>
@@ -5968,7 +5968,7 @@
         <v>0.0397353698936833</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0.07996147621114071</v>
+        <v>0.07996147621114072</v>
       </c>
       <c r="BK25" t="n">
         <v>0.004029802339128698</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02496779118561094</v>
+        <v>0.02496779118561095</v>
       </c>
       <c r="D28" t="n">
         <v>0.03279589746970663</v>
@@ -6566,7 +6566,7 @@
         <v>0.02285706842787808</v>
       </c>
       <c r="X28" t="n">
-        <v>0.02278373244598076</v>
+        <v>0.02278373244598077</v>
       </c>
       <c r="Y28" t="n">
         <v>0.02596708370429958</v>
@@ -6581,7 +6581,7 @@
         <v>0.03039634057311421</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.03909412180269181</v>
+        <v>0.0390941218026918</v>
       </c>
       <c r="AD28" t="n">
         <v>0.03866445418033427</v>
@@ -6680,7 +6680,7 @@
         <v>0.01777739244926321</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0.226126684935963</v>
+        <v>0.2261266849359631</v>
       </c>
       <c r="BK28" t="n">
         <v>0.08151875088265326</v>
@@ -6732,10 +6732,10 @@
         <v>13.72903318516088</v>
       </c>
       <c r="D29" t="n">
-        <v>55.92610833039318</v>
+        <v>55.92610833039319</v>
       </c>
       <c r="E29" t="n">
-        <v>30.87886282575769</v>
+        <v>30.87886282575768</v>
       </c>
       <c r="F29" t="n">
         <v>8.325835261231592</v>
@@ -6744,43 +6744,43 @@
         <v>7.376694375621585</v>
       </c>
       <c r="H29" t="n">
-        <v>7.052943728629352</v>
+        <v>7.052943728629351</v>
       </c>
       <c r="I29" t="n">
-        <v>6.873757950931459</v>
+        <v>6.873757950931458</v>
       </c>
       <c r="J29" t="n">
-        <v>6.04708063078375</v>
+        <v>6.047080630783751</v>
       </c>
       <c r="K29" t="n">
-        <v>6.15025717676014</v>
+        <v>6.150257176760141</v>
       </c>
       <c r="L29" t="n">
-        <v>5.67249020019941</v>
+        <v>5.672490200199409</v>
       </c>
       <c r="M29" t="n">
-        <v>6.377406071975502</v>
+        <v>6.377406071975503</v>
       </c>
       <c r="N29" t="n">
-        <v>7.535407480987431</v>
+        <v>7.535407480987432</v>
       </c>
       <c r="O29" t="n">
-        <v>5.382090518941815</v>
+        <v>5.382090518941812</v>
       </c>
       <c r="P29" t="n">
-        <v>7.117313832367344</v>
+        <v>7.117313832367342</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.273954458848543</v>
+        <v>6.273954458848541</v>
       </c>
       <c r="R29" t="n">
-        <v>7.28965684215603</v>
+        <v>7.289656842156029</v>
       </c>
       <c r="S29" t="n">
         <v>7.635971385794096</v>
       </c>
       <c r="T29" t="n">
-        <v>7.188252160831983</v>
+        <v>7.18825216083198</v>
       </c>
       <c r="U29" t="n">
         <v>7.629187385918093</v>
@@ -6789,7 +6789,7 @@
         <v>9.796761601627827</v>
       </c>
       <c r="W29" t="n">
-        <v>10.1001400869777</v>
+        <v>10.10014008697769</v>
       </c>
       <c r="X29" t="n">
         <v>10.02052308521086</v>
@@ -6798,7 +6798,7 @@
         <v>10.75954557297328</v>
       </c>
       <c r="Z29" t="n">
-        <v>9.078892014128515</v>
+        <v>9.078892014128513</v>
       </c>
       <c r="AA29" t="n">
         <v>11.31577428483735</v>
@@ -6810,28 +6810,28 @@
         <v>12.61594045050826</v>
       </c>
       <c r="AD29" t="n">
-        <v>12.01465177299594</v>
+        <v>12.01465177299595</v>
       </c>
       <c r="AE29" t="n">
-        <v>6.67549139471893</v>
+        <v>6.675491394718928</v>
       </c>
       <c r="AF29" t="n">
         <v>3.984893458974788</v>
       </c>
       <c r="AG29" t="n">
-        <v>4.585712940422375</v>
+        <v>4.585712940422376</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.65765646351508</v>
+        <v>3.657656463515079</v>
       </c>
       <c r="AI29" t="n">
-        <v>6.549377205804147</v>
+        <v>6.549377205804145</v>
       </c>
       <c r="AJ29" t="n">
         <v>7.181181049163306</v>
       </c>
       <c r="AK29" t="n">
-        <v>7.835168699620398</v>
+        <v>7.835168699620396</v>
       </c>
       <c r="AL29" t="n">
         <v>9.065252650103218</v>
@@ -6840,16 +6840,16 @@
         <v>8.608972756430434</v>
       </c>
       <c r="AN29" t="n">
-        <v>9.96489627954675</v>
+        <v>9.964896279546753</v>
       </c>
       <c r="AO29" t="n">
         <v>8.941477713491276</v>
       </c>
       <c r="AP29" t="n">
-        <v>9.222773514044897</v>
+        <v>9.222773514044894</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.485246139310101</v>
+        <v>4.485246139310102</v>
       </c>
       <c r="AR29" t="n">
         <v>6.119578602800318</v>
@@ -6864,13 +6864,13 @@
         <v>9.842537146621359</v>
       </c>
       <c r="AV29" t="n">
-        <v>9.671444603464764</v>
+        <v>9.671444603464765</v>
       </c>
       <c r="AW29" t="n">
         <v>8.025790058533612</v>
       </c>
       <c r="AX29" t="n">
-        <v>8.704266239912197</v>
+        <v>8.704266239912203</v>
       </c>
       <c r="AY29" t="n">
         <v>8.469150264784103</v>
@@ -6879,19 +6879,19 @@
         <v>10.39551234444018</v>
       </c>
       <c r="BA29" t="n">
-        <v>8.123095935853968</v>
+        <v>8.123095935853966</v>
       </c>
       <c r="BB29" t="n">
-        <v>10.3775485876845</v>
+        <v>10.37754858768451</v>
       </c>
       <c r="BC29" t="n">
-        <v>6.248727779797543</v>
+        <v>6.248727779797544</v>
       </c>
       <c r="BD29" t="n">
         <v>11.33463064424723</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.073161151188097</v>
+        <v>5.073161151188096</v>
       </c>
       <c r="BF29" t="n">
         <v>10.35438068201418</v>
@@ -6903,19 +6903,19 @@
         <v>10.03404578998275</v>
       </c>
       <c r="BI29" t="n">
-        <v>11.77198090801089</v>
+        <v>11.77198090801088</v>
       </c>
       <c r="BJ29" t="n">
-        <v>13.16254681169557</v>
+        <v>13.16254681169556</v>
       </c>
       <c r="BK29" t="n">
-        <v>4.644438582975665</v>
+        <v>4.644438582975664</v>
       </c>
       <c r="BL29" t="n">
-        <v>5.465601750023418</v>
+        <v>5.465601750023419</v>
       </c>
       <c r="BM29" t="n">
-        <v>3.050223389716582</v>
+        <v>3.050223389716579</v>
       </c>
       <c r="BN29" t="n">
         <v>2.493341680164959</v>
@@ -6927,13 +6927,13 @@
         <v>12.23926758331609</v>
       </c>
       <c r="BQ29" t="n">
-        <v>8.553671156333396</v>
+        <v>8.553671156333397</v>
       </c>
       <c r="BR29" t="n">
         <v>4.637609346564038</v>
       </c>
       <c r="BS29" t="n">
-        <v>4.728767456709005</v>
+        <v>4.728767456709004</v>
       </c>
       <c r="BT29" t="n">
         <v>5.478260625805139</v>
@@ -6951,10 +6951,10 @@
         <v>5.657043774645458</v>
       </c>
       <c r="BY29" t="n">
-        <v>5.542175727669365</v>
+        <v>5.542175727669364</v>
       </c>
       <c r="BZ29" t="n">
-        <v>5.087747021317211</v>
+        <v>5.087747021317212</v>
       </c>
     </row>
     <row r="30">
@@ -7151,13 +7151,13 @@
         <v>23.63133560734495</v>
       </c>
       <c r="G32" t="n">
-        <v>8.468343413740572</v>
+        <v>8.468343413740573</v>
       </c>
       <c r="H32" t="n">
-        <v>7.778266700311579</v>
+        <v>7.778266700311581</v>
       </c>
       <c r="I32" t="n">
-        <v>9.015659182562823</v>
+        <v>9.015659182562825</v>
       </c>
       <c r="J32" t="n">
         <v>14.86539938074984</v>
@@ -7172,25 +7172,25 @@
         <v>7.491877414826924</v>
       </c>
       <c r="N32" t="n">
-        <v>8.338512298542017</v>
+        <v>8.338512298542019</v>
       </c>
       <c r="O32" t="n">
-        <v>9.780281058583842</v>
+        <v>9.780281058583844</v>
       </c>
       <c r="P32" t="n">
-        <v>10.16893999904383</v>
+        <v>10.16893999904382</v>
       </c>
       <c r="Q32" t="n">
         <v>8.761073891162685</v>
       </c>
       <c r="R32" t="n">
-        <v>8.853203063371748</v>
+        <v>8.853203063371744</v>
       </c>
       <c r="S32" t="n">
-        <v>9.815987296287968</v>
+        <v>9.815987296287966</v>
       </c>
       <c r="T32" t="n">
-        <v>10.08502083889389</v>
+        <v>10.08502083889388</v>
       </c>
       <c r="U32" t="n">
         <v>10.12366002106877</v>
@@ -7205,25 +7205,25 @@
         <v>15.70415447255984</v>
       </c>
       <c r="Y32" t="n">
-        <v>19.54203183642951</v>
+        <v>19.54203183642952</v>
       </c>
       <c r="Z32" t="n">
-        <v>22.35185919439449</v>
+        <v>22.35185919439448</v>
       </c>
       <c r="AA32" t="n">
         <v>20.04563192463346</v>
       </c>
       <c r="AB32" t="n">
-        <v>30.53812362074749</v>
+        <v>30.5381236207475</v>
       </c>
       <c r="AC32" t="n">
-        <v>36.63610255390932</v>
+        <v>36.63610255390931</v>
       </c>
       <c r="AD32" t="n">
-        <v>39.52941046999605</v>
+        <v>39.52941046999604</v>
       </c>
       <c r="AE32" t="n">
-        <v>23.59368008502962</v>
+        <v>23.59368008502963</v>
       </c>
       <c r="AF32" t="n">
         <v>10.78000777276084</v>
@@ -7232,7 +7232,7 @@
         <v>13.65938585663139</v>
       </c>
       <c r="AH32" t="n">
-        <v>7.379183642088871</v>
+        <v>7.379183642088869</v>
       </c>
       <c r="AI32" t="n">
         <v>13.23397876323568</v>
@@ -7247,7 +7247,7 @@
         <v>21.49719265766768</v>
       </c>
       <c r="AM32" t="n">
-        <v>16.62143866567809</v>
+        <v>16.6214386656781</v>
       </c>
       <c r="AN32" t="n">
         <v>17.17541846560081</v>
@@ -7259,7 +7259,7 @@
         <v>15.82061863516728</v>
       </c>
       <c r="AQ32" t="n">
-        <v>12.05897923208789</v>
+        <v>12.0589792320879</v>
       </c>
       <c r="AR32" t="n">
         <v>17.45861987245021</v>
@@ -7268,16 +7268,16 @@
         <v>11.1323187459061</v>
       </c>
       <c r="AT32" t="n">
-        <v>17.94911619783907</v>
+        <v>17.94911619783908</v>
       </c>
       <c r="AU32" t="n">
-        <v>17.03160236807579</v>
+        <v>17.0316023680758</v>
       </c>
       <c r="AV32" t="n">
         <v>16.18446120001957</v>
       </c>
       <c r="AW32" t="n">
-        <v>26.07706979016037</v>
+        <v>26.07706979016038</v>
       </c>
       <c r="AX32" t="n">
         <v>15.0825737116319</v>
@@ -7286,13 +7286,13 @@
         <v>11.99128794894395</v>
       </c>
       <c r="AZ32" t="n">
-        <v>15.51679829542291</v>
+        <v>15.5167982954229</v>
       </c>
       <c r="BA32" t="n">
         <v>12.81017119802214</v>
       </c>
       <c r="BB32" t="n">
-        <v>35.63568241775639</v>
+        <v>35.6356824177564</v>
       </c>
       <c r="BC32" t="n">
         <v>27.65919886443865</v>
@@ -7313,10 +7313,10 @@
         <v>34.12382462167717</v>
       </c>
       <c r="BI32" t="n">
-        <v>33.51396658970302</v>
+        <v>33.51396658970301</v>
       </c>
       <c r="BJ32" t="n">
-        <v>27.36239635416111</v>
+        <v>27.3623963541611</v>
       </c>
       <c r="BK32" t="n">
         <v>13.5362767448521</v>
@@ -7340,7 +7340,7 @@
         <v>10.93948151061718</v>
       </c>
       <c r="BR32" t="n">
-        <v>13.38224545073876</v>
+        <v>13.38224545073877</v>
       </c>
       <c r="BS32" t="n">
         <v>14.53882443966239</v>
@@ -7395,19 +7395,19 @@
         <v>16.62459518857714</v>
       </c>
       <c r="I33" t="n">
-        <v>20.68582129326669</v>
+        <v>20.6858212932667</v>
       </c>
       <c r="J33" t="n">
-        <v>27.81541999240339</v>
+        <v>27.81541999240338</v>
       </c>
       <c r="K33" t="n">
-        <v>32.40427873225658</v>
+        <v>32.40427873225659</v>
       </c>
       <c r="L33" t="n">
         <v>20.78049940610539</v>
       </c>
       <c r="M33" t="n">
-        <v>17.06456014852472</v>
+        <v>17.06456014852471</v>
       </c>
       <c r="N33" t="n">
         <v>17.22293701558039</v>
@@ -7422,10 +7422,10 @@
         <v>20.54730891969151</v>
       </c>
       <c r="R33" t="n">
-        <v>18.84790844797517</v>
+        <v>18.84790844797516</v>
       </c>
       <c r="S33" t="n">
-        <v>16.0483363353001</v>
+        <v>16.04833633530009</v>
       </c>
       <c r="T33" t="n">
         <v>16.96927614894433</v>
@@ -7434,13 +7434,13 @@
         <v>20.30827904260996</v>
       </c>
       <c r="V33" t="n">
-        <v>26.61806908782123</v>
+        <v>26.61806908782124</v>
       </c>
       <c r="W33" t="n">
-        <v>27.54012582156907</v>
+        <v>27.54012582156906</v>
       </c>
       <c r="X33" t="n">
-        <v>23.66599454387799</v>
+        <v>23.66599454387798</v>
       </c>
       <c r="Y33" t="n">
         <v>27.34674135034101</v>
@@ -7449,13 +7449,13 @@
         <v>26.28631115580657</v>
       </c>
       <c r="AA33" t="n">
-        <v>26.96252760163028</v>
+        <v>26.96252760163027</v>
       </c>
       <c r="AB33" t="n">
         <v>47.08102830840533</v>
       </c>
       <c r="AC33" t="n">
-        <v>54.20790264344377</v>
+        <v>54.20790264344375</v>
       </c>
       <c r="AD33" t="n">
         <v>56.26689771271553</v>
@@ -7488,19 +7488,19 @@
         <v>27.28928792846015</v>
       </c>
       <c r="AN33" t="n">
-        <v>32.52081133348101</v>
+        <v>32.520811333481</v>
       </c>
       <c r="AO33" t="n">
         <v>25.28867464149842</v>
       </c>
       <c r="AP33" t="n">
-        <v>22.70437107929175</v>
+        <v>22.70437107929176</v>
       </c>
       <c r="AQ33" t="n">
         <v>18.60012177257393</v>
       </c>
       <c r="AR33" t="n">
-        <v>25.05172342581661</v>
+        <v>25.0517234258166</v>
       </c>
       <c r="AS33" t="n">
         <v>19.48863874070645</v>
@@ -7518,7 +7518,7 @@
         <v>11.38817062033185</v>
       </c>
       <c r="AX33" t="n">
-        <v>25.90545990051211</v>
+        <v>25.90545990051212</v>
       </c>
       <c r="AY33" t="n">
         <v>24.9459259571915</v>
@@ -7527,16 +7527,16 @@
         <v>32.23437670272448</v>
       </c>
       <c r="BA33" t="n">
-        <v>31.93431115043354</v>
+        <v>31.93431115043353</v>
       </c>
       <c r="BB33" t="n">
         <v>37.94093105896926</v>
       </c>
       <c r="BC33" t="n">
-        <v>24.73851131124484</v>
+        <v>24.73851131124483</v>
       </c>
       <c r="BD33" t="n">
-        <v>39.19409304135491</v>
+        <v>39.19409304135492</v>
       </c>
       <c r="BE33" t="n">
         <v>20.43734217357522</v>
@@ -7545,7 +7545,7 @@
         <v>21.0659635069765</v>
       </c>
       <c r="BG33" t="n">
-        <v>20.44187505908531</v>
+        <v>20.44187505908532</v>
       </c>
       <c r="BH33" t="n">
         <v>22.9996660247162</v>
@@ -7554,16 +7554,16 @@
         <v>21.23324450615404</v>
       </c>
       <c r="BJ33" t="n">
-        <v>15.98166079660192</v>
+        <v>15.98166079660193</v>
       </c>
       <c r="BK33" t="n">
-        <v>12.11192239030468</v>
+        <v>12.11192239030467</v>
       </c>
       <c r="BL33" t="n">
         <v>12.85279650904235</v>
       </c>
       <c r="BM33" t="n">
-        <v>17.23979083478965</v>
+        <v>17.23979083478964</v>
       </c>
       <c r="BN33" t="n">
         <v>13.12365616336768</v>
@@ -7575,13 +7575,13 @@
         <v>8.89629985487003</v>
       </c>
       <c r="BQ33" t="n">
-        <v>5.453850994072488</v>
+        <v>5.453850994072486</v>
       </c>
       <c r="BR33" t="n">
-        <v>22.88183991063863</v>
+        <v>22.88183991063864</v>
       </c>
       <c r="BS33" t="n">
-        <v>24.25543127433969</v>
+        <v>24.25543127433968</v>
       </c>
       <c r="BT33" t="n">
         <v>22.2203741441984</v>
@@ -7599,7 +7599,7 @@
         <v>18.90718180762351</v>
       </c>
       <c r="BY33" t="n">
-        <v>18.40947068550695</v>
+        <v>18.40947068550694</v>
       </c>
       <c r="BZ33" t="n">
         <v>15.48910336950341</v>
@@ -7986,16 +7986,16 @@
         <v>0.03339947361909435</v>
       </c>
       <c r="H36" t="n">
-        <v>0.02804357781065375</v>
+        <v>0.02804357781065376</v>
       </c>
       <c r="I36" t="n">
-        <v>0.03716788393750816</v>
+        <v>0.03716788393750817</v>
       </c>
       <c r="J36" t="n">
         <v>0.04881198937555416</v>
       </c>
       <c r="K36" t="n">
-        <v>0.06167469426318805</v>
+        <v>0.06167469426318804</v>
       </c>
       <c r="L36" t="n">
         <v>0.04827098855217372</v>
@@ -8004,16 +8004,16 @@
         <v>0.03215153528514963</v>
       </c>
       <c r="N36" t="n">
-        <v>0.03123826328716182</v>
+        <v>0.03123826328716183</v>
       </c>
       <c r="O36" t="n">
-        <v>0.03592466725668749</v>
+        <v>0.03592466725668748</v>
       </c>
       <c r="P36" t="n">
         <v>0.04668140243717957</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.04212779181433191</v>
+        <v>0.04212779181433192</v>
       </c>
       <c r="R36" t="n">
         <v>0.03998859929626113</v>
@@ -8025,7 +8025,7 @@
         <v>0.04595159671944588</v>
       </c>
       <c r="U36" t="n">
-        <v>0.04890567960926719</v>
+        <v>0.04890567960926718</v>
       </c>
       <c r="V36" t="n">
         <v>0.0658383630526731</v>
@@ -8037,7 +8037,7 @@
         <v>0.0722106250650871</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.07342383231365855</v>
+        <v>0.07342383231365857</v>
       </c>
       <c r="Z36" t="n">
         <v>0.08846332587273012</v>
@@ -8061,10 +8061,10 @@
         <v>0.04330160187968778</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.05168449570205724</v>
+        <v>0.05168449570205725</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.02928898384114541</v>
+        <v>0.02928898384114542</v>
       </c>
       <c r="AI36" t="n">
         <v>0.05190389708626374</v>
@@ -8091,7 +8091,7 @@
         <v>0.06289351099044631</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.04658959975009144</v>
+        <v>0.04658959975009145</v>
       </c>
       <c r="AR36" t="n">
         <v>0.0727067486427742</v>
@@ -8121,7 +8121,7 @@
         <v>0.4701650753921289</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.4649226306047457</v>
+        <v>0.4649226306047456</v>
       </c>
       <c r="BB36" t="n">
         <v>0.4590133129941308</v>
@@ -8148,19 +8148,19 @@
         <v>0.7422902816484519</v>
       </c>
       <c r="BJ36" t="n">
-        <v>1.37495760423143</v>
+        <v>1.374957604231431</v>
       </c>
       <c r="BK36" t="n">
         <v>1.267201947986528</v>
       </c>
       <c r="BL36" t="n">
-        <v>0.3068915044294452</v>
+        <v>0.3068915044294451</v>
       </c>
       <c r="BM36" t="n">
         <v>0.4048809084560938</v>
       </c>
       <c r="BN36" t="n">
-        <v>0.2755960746579551</v>
+        <v>0.2755960746579552</v>
       </c>
       <c r="BO36" t="n">
         <v>0.2483924917734967</v>
@@ -8169,7 +8169,7 @@
         <v>0.9112755889146799</v>
       </c>
       <c r="BQ36" t="n">
-        <v>0.7724071405214495</v>
+        <v>0.7724071405214494</v>
       </c>
       <c r="BR36" t="n">
         <v>0.2160405486904482</v>
@@ -8209,7 +8209,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>9.236681106254375</v>
+        <v>9.236681106254377</v>
       </c>
       <c r="D37" t="n">
         <v>13.83001405596348</v>
@@ -8218,10 +8218,10 @@
         <v>23.07311216312834</v>
       </c>
       <c r="F37" t="n">
-        <v>8.21440487226819</v>
+        <v>8.214404872268188</v>
       </c>
       <c r="G37" t="n">
-        <v>6.591021022239651</v>
+        <v>6.591021022239652</v>
       </c>
       <c r="H37" t="n">
         <v>5.377812061686631</v>
@@ -8236,10 +8236,10 @@
         <v>12.13466082506201</v>
       </c>
       <c r="L37" t="n">
-        <v>9.573732828637862</v>
+        <v>9.57373282863786</v>
       </c>
       <c r="M37" t="n">
-        <v>4.860692542322349</v>
+        <v>4.860692542322351</v>
       </c>
       <c r="N37" t="n">
         <v>5.122287941395714</v>
@@ -8266,7 +8266,7 @@
         <v>7.828551501770106</v>
       </c>
       <c r="V37" t="n">
-        <v>10.05863872993807</v>
+        <v>10.05863872993806</v>
       </c>
       <c r="W37" t="n">
         <v>10.60331267863964</v>
@@ -8278,7 +8278,7 @@
         <v>10.58159554193468</v>
       </c>
       <c r="Z37" t="n">
-        <v>9.545759445174127</v>
+        <v>9.545759445174129</v>
       </c>
       <c r="AA37" t="n">
         <v>11.24438007331585</v>
@@ -8296,13 +8296,13 @@
         <v>12.86261943016644</v>
       </c>
       <c r="AF37" t="n">
-        <v>7.021138259949989</v>
+        <v>7.021138259949991</v>
       </c>
       <c r="AG37" t="n">
         <v>8.518893433083626</v>
       </c>
       <c r="AH37" t="n">
-        <v>6.565116527656256</v>
+        <v>6.565116527656255</v>
       </c>
       <c r="AI37" t="n">
         <v>10.29140937174527</v>
@@ -8314,7 +8314,7 @@
         <v>14.29406490731991</v>
       </c>
       <c r="AL37" t="n">
-        <v>17.20846273805516</v>
+        <v>17.20846273805517</v>
       </c>
       <c r="AM37" t="n">
         <v>15.27742456485975</v>
@@ -8329,7 +8329,7 @@
         <v>10.98580411046728</v>
       </c>
       <c r="AQ37" t="n">
-        <v>7.954700156171888</v>
+        <v>7.954700156171885</v>
       </c>
       <c r="AR37" t="n">
         <v>10.94822002738547</v>
@@ -8359,7 +8359,7 @@
         <v>11.05715001145059</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.072633397442192</v>
+        <v>5.072633397442193</v>
       </c>
       <c r="BB37" t="n">
         <v>29.999571473569</v>
@@ -8389,13 +8389,13 @@
         <v>13.19566903535406</v>
       </c>
       <c r="BK37" t="n">
-        <v>6.8045080440168</v>
+        <v>6.804508044016801</v>
       </c>
       <c r="BL37" t="n">
-        <v>5.288796939907737</v>
+        <v>5.288796939907736</v>
       </c>
       <c r="BM37" t="n">
-        <v>9.089603919206453</v>
+        <v>9.089603919206452</v>
       </c>
       <c r="BN37" t="n">
         <v>15.92722249833599</v>
@@ -8404,16 +8404,16 @@
         <v>17.64654073589238</v>
       </c>
       <c r="BP37" t="n">
-        <v>8.496328403568475</v>
+        <v>8.496328403568477</v>
       </c>
       <c r="BQ37" t="n">
-        <v>5.152965835855252</v>
+        <v>5.152965835855254</v>
       </c>
       <c r="BR37" t="n">
-        <v>14.72111163831099</v>
+        <v>14.721111638311</v>
       </c>
       <c r="BS37" t="n">
-        <v>16.6333150346013</v>
+        <v>16.63331503460129</v>
       </c>
       <c r="BT37" t="n">
         <v>21.2943844867156</v>
@@ -8422,7 +8422,7 @@
         <v>24.92132946153939</v>
       </c>
       <c r="BV37" t="n">
-        <v>20.59889969679988</v>
+        <v>20.59889969679989</v>
       </c>
       <c r="BW37" t="n">
         <v>25.36193491932729</v>
@@ -8434,7 +8434,7 @@
         <v>28.42097757845574</v>
       </c>
       <c r="BZ37" t="n">
-        <v>21.95760191428738</v>
+        <v>21.95760191428739</v>
       </c>
     </row>
     <row r="38">
@@ -8947,10 +8947,10 @@
         <v>0.2864966655776944</v>
       </c>
       <c r="G43" t="n">
-        <v>0.08775110047001004</v>
+        <v>0.08775110047001003</v>
       </c>
       <c r="H43" t="n">
-        <v>0.08207111685074069</v>
+        <v>0.0820711168507407</v>
       </c>
       <c r="I43" t="n">
         <v>0.08415929333605361</v>
@@ -8959,7 +8959,7 @@
         <v>0.2191954449388508</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2258468722453944</v>
+        <v>0.2258468722453943</v>
       </c>
       <c r="L43" t="n">
         <v>0.2181694254459223</v>
@@ -8977,10 +8977,10 @@
         <v>0.1176094817437705</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.09584056828964703</v>
+        <v>0.09584056828964702</v>
       </c>
       <c r="R43" t="n">
-        <v>0.1070846964101654</v>
+        <v>0.1070846964101655</v>
       </c>
       <c r="S43" t="n">
         <v>0.107201241042783</v>
@@ -9001,7 +9001,7 @@
         <v>0.1221753922190812</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.1441483534626473</v>
+        <v>0.1441483534626474</v>
       </c>
       <c r="Z43" t="n">
         <v>0.1308295030927066</v>
@@ -9031,7 +9031,7 @@
         <v>0.06769110948257599</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.1225463994838213</v>
+        <v>0.1225463994838212</v>
       </c>
       <c r="AJ43" t="n">
         <v>0.131767594036505</v>
@@ -9043,7 +9043,7 @@
         <v>0.1850913164579692</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.1734347026183222</v>
+        <v>0.1734347026183223</v>
       </c>
       <c r="AN43" t="n">
         <v>0.1574826552831692</v>
@@ -9067,7 +9067,7 @@
         <v>0.1492397689402625</v>
       </c>
       <c r="AU43" t="n">
-        <v>0.1943294841460757</v>
+        <v>0.1943294841460756</v>
       </c>
       <c r="AV43" t="n">
         <v>0.1536841561137615</v>
@@ -9076,7 +9076,7 @@
         <v>0.3537110713230627</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.2123219129312912</v>
+        <v>0.2123219129312913</v>
       </c>
       <c r="AY43" t="n">
         <v>0.2143790702298435</v>
@@ -9094,13 +9094,13 @@
         <v>0.4388652259986646</v>
       </c>
       <c r="BD43" t="n">
-        <v>0.6882475573203</v>
+        <v>0.6882475573203001</v>
       </c>
       <c r="BE43" t="n">
         <v>0.3704434303883064</v>
       </c>
       <c r="BF43" t="n">
-        <v>0.2948365740511934</v>
+        <v>0.2948365740511933</v>
       </c>
       <c r="BG43" t="n">
         <v>0.2856403457134515</v>
@@ -9182,16 +9182,16 @@
         <v>0.2250182242963864</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7624504149167778</v>
+        <v>0.7624504149167779</v>
       </c>
       <c r="G44" t="n">
-        <v>0.08774566591444311</v>
+        <v>0.08774566591444309</v>
       </c>
       <c r="H44" t="n">
         <v>0.08036184650083542</v>
       </c>
       <c r="I44" t="n">
-        <v>0.07724716661173285</v>
+        <v>0.07724716661173286</v>
       </c>
       <c r="J44" t="n">
         <v>0.1101830025614886</v>
@@ -9218,7 +9218,7 @@
         <v>0.0925458294467181</v>
       </c>
       <c r="R44" t="n">
-        <v>0.09698951305406624</v>
+        <v>0.09698951305406628</v>
       </c>
       <c r="S44" t="n">
         <v>0.1143782596740054</v>
@@ -9227,10 +9227,10 @@
         <v>0.1058435544479691</v>
       </c>
       <c r="U44" t="n">
-        <v>0.1100274223193427</v>
+        <v>0.1100274223193428</v>
       </c>
       <c r="V44" t="n">
-        <v>0.1568286092115539</v>
+        <v>0.1568286092115538</v>
       </c>
       <c r="W44" t="n">
         <v>0.1641985893442817</v>
@@ -9239,7 +9239,7 @@
         <v>0.1658330182048349</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.1882168586785155</v>
+        <v>0.1882168586785154</v>
       </c>
       <c r="Z44" t="n">
         <v>0.1900076316229404</v>
@@ -9251,19 +9251,19 @@
         <v>0.191785710139686</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.2373119428431414</v>
+        <v>0.2373119428431413</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.2381503223367589</v>
+        <v>0.238150322336759</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.1803611259188315</v>
+        <v>0.1803611259188314</v>
       </c>
       <c r="AF44" t="n">
         <v>0.1016195009878331</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.1126710562381137</v>
+        <v>0.1126710562381136</v>
       </c>
       <c r="AH44" t="n">
         <v>0.06816232161193234</v>
@@ -9308,22 +9308,22 @@
         <v>0.1624638001787902</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.145732170267155</v>
+        <v>0.1457321702671549</v>
       </c>
       <c r="AW44" t="n">
         <v>0.08816303235530486</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.3770277623326744</v>
+        <v>0.3770277623326745</v>
       </c>
       <c r="AY44" t="n">
         <v>0.4270783408076336</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.4184677809772496</v>
+        <v>0.4184677809772497</v>
       </c>
       <c r="BA44" t="n">
-        <v>0.4812785878329095</v>
+        <v>0.4812785878329096</v>
       </c>
       <c r="BB44" t="n">
         <v>0.2961664459131726</v>
@@ -9332,10 +9332,10 @@
         <v>0.4199216592495831</v>
       </c>
       <c r="BD44" t="n">
-        <v>0.5369640631346538</v>
+        <v>0.5369640631346539</v>
       </c>
       <c r="BE44" t="n">
-        <v>0.3173756942732027</v>
+        <v>0.3173756942732028</v>
       </c>
       <c r="BF44" t="n">
         <v>0.2018199098890827</v>
@@ -9365,13 +9365,13 @@
         <v>0.2085130323800725</v>
       </c>
       <c r="BO44" t="n">
-        <v>0.2193492146756422</v>
+        <v>0.2193492146756423</v>
       </c>
       <c r="BP44" t="n">
-        <v>1.45697222835643</v>
+        <v>1.456972228356431</v>
       </c>
       <c r="BQ44" t="n">
-        <v>1.363615921638566</v>
+        <v>1.363615921638565</v>
       </c>
       <c r="BR44" t="n">
         <v>0.1590719067104512</v>
@@ -9398,7 +9398,7 @@
         <v>0.2067117906321942</v>
       </c>
       <c r="BZ44" t="n">
-        <v>0.1965945769088317</v>
+        <v>0.1965945769088316</v>
       </c>
     </row>
     <row r="45">
@@ -9822,10 +9822,10 @@
         <v>1.065429315869947</v>
       </c>
       <c r="L48" t="n">
-        <v>0.9657065733674696</v>
+        <v>0.9657065733674695</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1115771841482974</v>
+        <v>0.1115771841482973</v>
       </c>
       <c r="N48" t="n">
         <v>0.113233317520678</v>
@@ -9870,13 +9870,13 @@
         <v>0.1493784155364853</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.9651593666854725</v>
+        <v>0.9651593666854726</v>
       </c>
       <c r="AC48" t="n">
         <v>1.058895750861178</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.9830918431165466</v>
+        <v>0.9830918431165465</v>
       </c>
       <c r="AE48" t="n">
         <v>0.3645636672803193</v>
@@ -9918,7 +9918,7 @@
         <v>0.2613420016626071</v>
       </c>
       <c r="AR48" t="n">
-        <v>0.4487727701532031</v>
+        <v>0.4487727701532032</v>
       </c>
       <c r="AS48" t="n">
         <v>0.2946395421476545</v>
@@ -9933,7 +9933,7 @@
         <v>0.1882880450394185</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.5399310015245957</v>
+        <v>0.5399310015245959</v>
       </c>
       <c r="AX48" t="n">
         <v>0.2862403753286038</v>
@@ -9990,7 +9990,7 @@
         <v>0.06900117258326856</v>
       </c>
       <c r="BP48" t="n">
-        <v>0.7542639896671279</v>
+        <v>0.7542639896671278</v>
       </c>
       <c r="BQ48" t="n">
         <v>0.5140796070046958</v>
@@ -10585,13 +10585,13 @@
         <v>70.67034498512589</v>
       </c>
       <c r="E54" t="n">
-        <v>45.63002593684</v>
+        <v>45.63002593684001</v>
       </c>
       <c r="F54" t="n">
         <v>60.01895002236657</v>
       </c>
       <c r="G54" t="n">
-        <v>18.97454872322374</v>
+        <v>18.97454872322375</v>
       </c>
       <c r="H54" t="n">
         <v>17.29429587879103</v>
@@ -10603,10 +10603,10 @@
         <v>28.42480898603429</v>
       </c>
       <c r="K54" t="n">
-        <v>28.07555072519659</v>
+        <v>28.0755507251966</v>
       </c>
       <c r="L54" t="n">
-        <v>23.95046814589336</v>
+        <v>23.95046814589337</v>
       </c>
       <c r="M54" t="n">
         <v>10.97912727596544</v>
@@ -10627,16 +10627,16 @@
         <v>11.8813956859162</v>
       </c>
       <c r="S54" t="n">
-        <v>11.31709676877051</v>
+        <v>11.3170967687705</v>
       </c>
       <c r="T54" t="n">
-        <v>11.374531567085</v>
+        <v>11.37453156708499</v>
       </c>
       <c r="U54" t="n">
         <v>11.72879361200085</v>
       </c>
       <c r="V54" t="n">
-        <v>23.040752478151</v>
+        <v>23.04075247815099</v>
       </c>
       <c r="W54" t="n">
         <v>22.19398020957372</v>
@@ -10654,25 +10654,25 @@
         <v>34.4595697349563</v>
       </c>
       <c r="AB54" t="n">
-        <v>40.79073190754479</v>
+        <v>40.79073190754478</v>
       </c>
       <c r="AC54" t="n">
-        <v>38.38609938031143</v>
+        <v>38.38609938031144</v>
       </c>
       <c r="AD54" t="n">
-        <v>36.56103446528616</v>
+        <v>36.56103446528615</v>
       </c>
       <c r="AE54" t="n">
-        <v>30.90723162760485</v>
+        <v>30.90723162760484</v>
       </c>
       <c r="AF54" t="n">
-        <v>23.45644036162583</v>
+        <v>23.45644036162582</v>
       </c>
       <c r="AG54" t="n">
-        <v>31.11451135005029</v>
+        <v>31.11451135005028</v>
       </c>
       <c r="AH54" t="n">
-        <v>9.670676931053688</v>
+        <v>9.67067693105369</v>
       </c>
       <c r="AI54" t="n">
         <v>15.87100855164787</v>
@@ -10681,7 +10681,7 @@
         <v>15.58412659767417</v>
       </c>
       <c r="AK54" t="n">
-        <v>13.47911074905618</v>
+        <v>13.47911074905617</v>
       </c>
       <c r="AL54" t="n">
         <v>16.08860138826397</v>
@@ -10732,7 +10732,7 @@
         <v>43.34507620709159</v>
       </c>
       <c r="BB54" t="n">
-        <v>64.77923411740964</v>
+        <v>64.77923411740963</v>
       </c>
       <c r="BC54" t="n">
         <v>47.32190548940223</v>
@@ -10744,19 +10744,19 @@
         <v>37.50862219599895</v>
       </c>
       <c r="BF54" t="n">
-        <v>37.27760518836685</v>
+        <v>37.27760518836683</v>
       </c>
       <c r="BG54" t="n">
         <v>37.07979525293703</v>
       </c>
       <c r="BH54" t="n">
-        <v>36.37676097937889</v>
+        <v>36.37676097937888</v>
       </c>
       <c r="BI54" t="n">
-        <v>36.94491590486591</v>
+        <v>36.9449159048659</v>
       </c>
       <c r="BJ54" t="n">
-        <v>40.66718207039255</v>
+        <v>40.66718207039254</v>
       </c>
       <c r="BK54" t="n">
         <v>13.14370625450515</v>
@@ -10768,7 +10768,7 @@
         <v>21.70957628659496</v>
       </c>
       <c r="BN54" t="n">
-        <v>10.81201343552676</v>
+        <v>10.81201343552675</v>
       </c>
       <c r="BO54" t="n">
         <v>18.01149224696858</v>
@@ -10798,10 +10798,10 @@
         <v>16.0278424114532</v>
       </c>
       <c r="BX54" t="n">
-        <v>17.44268804643087</v>
+        <v>17.44268804643088</v>
       </c>
       <c r="BY54" t="n">
-        <v>19.24150662009026</v>
+        <v>19.24150662009027</v>
       </c>
       <c r="BZ54" t="n">
         <v>18.9395036590646</v>
@@ -10823,7 +10823,7 @@
         <v>2.322935742790195</v>
       </c>
       <c r="E55" t="n">
-        <v>2.748244523003454</v>
+        <v>2.748244523003455</v>
       </c>
       <c r="F55" t="n">
         <v>3.02764839475289</v>
@@ -10841,7 +10841,7 @@
         <v>1.541114418535989</v>
       </c>
       <c r="K55" t="n">
-        <v>1.623878656285505</v>
+        <v>1.623878656285506</v>
       </c>
       <c r="L55" t="n">
         <v>1.440937134627114</v>
@@ -10859,13 +10859,13 @@
         <v>1.535193873726075</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.338747948198056</v>
+        <v>1.338747948198057</v>
       </c>
       <c r="R55" t="n">
-        <v>1.340809037990955</v>
+        <v>1.340809037990956</v>
       </c>
       <c r="S55" t="n">
-        <v>1.27350202942629</v>
+        <v>1.273502029426289</v>
       </c>
       <c r="T55" t="n">
         <v>1.307124651072876</v>
@@ -10874,7 +10874,7 @@
         <v>1.301894949442884</v>
       </c>
       <c r="V55" t="n">
-        <v>1.590394643038574</v>
+        <v>1.590394643038575</v>
       </c>
       <c r="W55" t="n">
         <v>1.561154124035071</v>
@@ -10898,7 +10898,7 @@
         <v>2.010687887233364</v>
       </c>
       <c r="AD55" t="n">
-        <v>2.16710572034282</v>
+        <v>2.167105720342821</v>
       </c>
       <c r="AE55" t="n">
         <v>2.131438198863493</v>
@@ -10913,10 +10913,10 @@
         <v>1.02180566739888</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.656850075061417</v>
+        <v>1.656850075061418</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.719519346616017</v>
+        <v>1.719519346616018</v>
       </c>
       <c r="AK55" t="n">
         <v>1.647555951520457</v>
@@ -10961,7 +10961,7 @@
         <v>3.759793588119867</v>
       </c>
       <c r="AY55" t="n">
-        <v>4.576309627153179</v>
+        <v>4.57630962715318</v>
       </c>
       <c r="AZ55" t="n">
         <v>3.663727660542295</v>
@@ -10997,7 +10997,7 @@
         <v>7.819995638000586</v>
       </c>
       <c r="BK55" t="n">
-        <v>4.237511392000477</v>
+        <v>4.237511392000478</v>
       </c>
       <c r="BL55" t="n">
         <v>2.009007713833513</v>
@@ -11015,7 +11015,7 @@
         <v>4.425915192831257</v>
       </c>
       <c r="BQ55" t="n">
-        <v>3.594382167600898</v>
+        <v>3.594382167600897</v>
       </c>
       <c r="BR55" t="n">
         <v>4.897913517669521</v>
@@ -11024,7 +11024,7 @@
         <v>5.165891083251555</v>
       </c>
       <c r="BT55" t="n">
-        <v>4.716103535293787</v>
+        <v>4.716103535293788</v>
       </c>
       <c r="BU55" t="n">
         <v>4.55789676818944</v>
@@ -11033,7 +11033,7 @@
         <v>3.117661154966156</v>
       </c>
       <c r="BW55" t="n">
-        <v>3.222936405445294</v>
+        <v>3.222936405445295</v>
       </c>
       <c r="BX55" t="n">
         <v>3.540361117230148</v>
@@ -11061,22 +11061,22 @@
         <v>16.67632669855201</v>
       </c>
       <c r="E56" t="n">
-        <v>24.8469393031319</v>
+        <v>24.84693930313189</v>
       </c>
       <c r="F56" t="n">
-        <v>5.878100175664291</v>
+        <v>5.878100175664292</v>
       </c>
       <c r="G56" t="n">
         <v>11.14428981943255</v>
       </c>
       <c r="H56" t="n">
-        <v>9.871486922020692</v>
+        <v>9.871486922020694</v>
       </c>
       <c r="I56" t="n">
-        <v>10.31798840219446</v>
+        <v>10.31798840219445</v>
       </c>
       <c r="J56" t="n">
-        <v>15.70931832437396</v>
+        <v>15.70931832437395</v>
       </c>
       <c r="K56" t="n">
         <v>15.67593561120263</v>
@@ -11100,16 +11100,16 @@
         <v>14.81393133983271</v>
       </c>
       <c r="R56" t="n">
-        <v>15.88234552166685</v>
+        <v>15.88234552166686</v>
       </c>
       <c r="S56" t="n">
-        <v>17.72249587580757</v>
+        <v>17.72249587580758</v>
       </c>
       <c r="T56" t="n">
-        <v>16.94237959412322</v>
+        <v>16.94237959412323</v>
       </c>
       <c r="U56" t="n">
-        <v>18.19059222171002</v>
+        <v>18.19059222171001</v>
       </c>
       <c r="V56" t="n">
         <v>23.46365132181275</v>
@@ -11121,7 +11121,7 @@
         <v>20.14176725211009</v>
       </c>
       <c r="Y56" t="n">
-        <v>21.08948437655292</v>
+        <v>21.08948437655291</v>
       </c>
       <c r="Z56" t="n">
         <v>23.94610342829396</v>
@@ -11130,13 +11130,13 @@
         <v>26.08438318489998</v>
       </c>
       <c r="AB56" t="n">
-        <v>23.64087899768518</v>
+        <v>23.64087899768519</v>
       </c>
       <c r="AC56" t="n">
-        <v>26.34453627059335</v>
+        <v>26.34453627059336</v>
       </c>
       <c r="AD56" t="n">
-        <v>27.38236752196276</v>
+        <v>27.38236752196275</v>
       </c>
       <c r="AE56" t="n">
         <v>27.59552356706648</v>
@@ -11160,10 +11160,10 @@
         <v>22.45690642660067</v>
       </c>
       <c r="AL56" t="n">
-        <v>27.97243818936642</v>
+        <v>27.97243818936643</v>
       </c>
       <c r="AM56" t="n">
-        <v>24.36361552070706</v>
+        <v>24.36361552070705</v>
       </c>
       <c r="AN56" t="n">
         <v>24.66001940036943</v>
@@ -11178,19 +11178,19 @@
         <v>18.91977316428192</v>
       </c>
       <c r="AR56" t="n">
-        <v>22.91544567916656</v>
+        <v>22.91544567916658</v>
       </c>
       <c r="AS56" t="n">
-        <v>16.31491634802738</v>
+        <v>16.31491634802739</v>
       </c>
       <c r="AT56" t="n">
         <v>23.39557921547557</v>
       </c>
       <c r="AU56" t="n">
-        <v>25.96428754222718</v>
+        <v>25.96428754222719</v>
       </c>
       <c r="AV56" t="n">
-        <v>23.16174859097403</v>
+        <v>23.16174859097402</v>
       </c>
       <c r="AW56" t="n">
         <v>6.657757709754605</v>
@@ -11214,7 +11214,7 @@
         <v>1.152149058719085</v>
       </c>
       <c r="BD56" t="n">
-        <v>1.724558811823649</v>
+        <v>1.724558811823648</v>
       </c>
       <c r="BE56" t="n">
         <v>1.106000628905154</v>
@@ -11223,16 +11223,16 @@
         <v>1.84055859135515</v>
       </c>
       <c r="BG56" t="n">
-        <v>1.768968592826203</v>
+        <v>1.768968592826204</v>
       </c>
       <c r="BH56" t="n">
-        <v>2.346229562976341</v>
+        <v>2.346229562976342</v>
       </c>
       <c r="BI56" t="n">
         <v>1.732131645594523</v>
       </c>
       <c r="BJ56" t="n">
-        <v>2.604827632131044</v>
+        <v>2.604827632131043</v>
       </c>
       <c r="BK56" t="n">
         <v>1.12329918889286</v>
@@ -11244,13 +11244,13 @@
         <v>1.961622231577266</v>
       </c>
       <c r="BN56" t="n">
-        <v>3.634098628643369</v>
+        <v>3.63409862864337</v>
       </c>
       <c r="BO56" t="n">
-        <v>4.21931918668251</v>
+        <v>4.219319186682511</v>
       </c>
       <c r="BP56" t="n">
-        <v>2.383784758376181</v>
+        <v>2.383784758376182</v>
       </c>
       <c r="BQ56" t="n">
         <v>1.736955733759818</v>
@@ -11259,7 +11259,7 @@
         <v>3.528776806954189</v>
       </c>
       <c r="BS56" t="n">
-        <v>4.540565058249707</v>
+        <v>4.540565058249708</v>
       </c>
       <c r="BT56" t="n">
         <v>6.459092403238426</v>
@@ -11268,7 +11268,7 @@
         <v>7.447208336314008</v>
       </c>
       <c r="BV56" t="n">
-        <v>5.81281229699224</v>
+        <v>5.812812296992241</v>
       </c>
       <c r="BW56" t="n">
         <v>6.722167702843915</v>
@@ -11277,7 +11277,7 @@
         <v>7.386269850184358</v>
       </c>
       <c r="BY56" t="n">
-        <v>6.663676250112323</v>
+        <v>6.663676250112321</v>
       </c>
       <c r="BZ56" t="n">
         <v>5.617653995683447</v>
@@ -11590,7 +11590,7 @@
         <v>0.02276320675267867</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.03049616292395551</v>
+        <v>0.03049616292395552</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.01943631658519676</v>
@@ -11605,7 +11605,7 @@
         <v>0.02603842562028252</v>
       </c>
       <c r="AU59" t="n">
-        <v>0.02828784272618075</v>
+        <v>0.02828784272618076</v>
       </c>
       <c r="AV59" t="n">
         <v>0.02585958513147249</v>
@@ -11620,7 +11620,7 @@
         <v>0.4564406077736735</v>
       </c>
       <c r="AZ59" t="n">
-        <v>0.3001417553672671</v>
+        <v>0.300141755367267</v>
       </c>
       <c r="BA59" t="n">
         <v>0.4416445783861374</v>
@@ -11650,7 +11650,7 @@
         <v>0.3059201218442392</v>
       </c>
       <c r="BJ59" t="n">
-        <v>2.675367980651073</v>
+        <v>2.675367980651074</v>
       </c>
       <c r="BK59" t="n">
         <v>3.744436323619934</v>
@@ -11723,7 +11723,7 @@
         <v>12.88019145559012</v>
       </c>
       <c r="G60" t="n">
-        <v>5.069772271738575</v>
+        <v>5.069772271738576</v>
       </c>
       <c r="H60" t="n">
         <v>4.376163401460544</v>
@@ -11732,7 +11732,7 @@
         <v>5.043449815346333</v>
       </c>
       <c r="J60" t="n">
-        <v>4.274311413818575</v>
+        <v>4.274311413818576</v>
       </c>
       <c r="K60" t="n">
         <v>4.69446809009763</v>
@@ -11753,13 +11753,13 @@
         <v>8.360776556891929</v>
       </c>
       <c r="Q60" t="n">
-        <v>7.376157410853418</v>
+        <v>7.376157410853416</v>
       </c>
       <c r="R60" t="n">
-        <v>7.362273830986727</v>
+        <v>7.362273830986726</v>
       </c>
       <c r="S60" t="n">
-        <v>7.59696390046717</v>
+        <v>7.596963900467171</v>
       </c>
       <c r="T60" t="n">
         <v>7.292699371132184</v>
@@ -11774,7 +11774,7 @@
         <v>9.230752329228446</v>
       </c>
       <c r="X60" t="n">
-        <v>9.824392419347955</v>
+        <v>9.824392419347953</v>
       </c>
       <c r="Y60" t="n">
         <v>10.99865033335314</v>
@@ -11786,7 +11786,7 @@
         <v>11.7694578419839</v>
       </c>
       <c r="AB60" t="n">
-        <v>5.95729133747726</v>
+        <v>5.957291337477261</v>
       </c>
       <c r="AC60" t="n">
         <v>7.933874213963636</v>
@@ -11801,19 +11801,19 @@
         <v>5.730530428679295</v>
       </c>
       <c r="AG60" t="n">
-        <v>6.417887733144274</v>
+        <v>6.417887733144273</v>
       </c>
       <c r="AH60" t="n">
         <v>5.199258660763308</v>
       </c>
       <c r="AI60" t="n">
-        <v>8.295863017702468</v>
+        <v>8.295863017702466</v>
       </c>
       <c r="AJ60" t="n">
-        <v>7.719821757094704</v>
+        <v>7.719821757094703</v>
       </c>
       <c r="AK60" t="n">
-        <v>4.419897438745169</v>
+        <v>4.41989743874517</v>
       </c>
       <c r="AL60" t="n">
         <v>5.989451600693563</v>
@@ -11831,10 +11831,10 @@
         <v>9.097334582420569</v>
       </c>
       <c r="AQ60" t="n">
-        <v>5.854200638534349</v>
+        <v>5.854200638534348</v>
       </c>
       <c r="AR60" t="n">
-        <v>7.059336453621986</v>
+        <v>7.059336453621985</v>
       </c>
       <c r="AS60" t="n">
         <v>6.693544568435808</v>
@@ -11843,7 +11843,7 @@
         <v>11.08560544832138</v>
       </c>
       <c r="AU60" t="n">
-        <v>10.7478852804862</v>
+        <v>10.74788528048621</v>
       </c>
       <c r="AV60" t="n">
         <v>11.30043174355873</v>
@@ -11852,7 +11852,7 @@
         <v>4.193357514419293</v>
       </c>
       <c r="AX60" t="n">
-        <v>6.847158056909884</v>
+        <v>6.847158056909885</v>
       </c>
       <c r="AY60" t="n">
         <v>6.661168252559383</v>
@@ -11861,7 +11861,7 @@
         <v>8.500788868670959</v>
       </c>
       <c r="BA60" t="n">
-        <v>8.199288015592822</v>
+        <v>8.199288015592824</v>
       </c>
       <c r="BB60" t="n">
         <v>3.553114160968207</v>
@@ -11891,13 +11891,13 @@
         <v>27.84021114365188</v>
       </c>
       <c r="BK60" t="n">
-        <v>39.22633925121375</v>
+        <v>39.22633925121374</v>
       </c>
       <c r="BL60" t="n">
-        <v>5.918676742838743</v>
+        <v>5.918676742838742</v>
       </c>
       <c r="BM60" t="n">
-        <v>4.128081617489364</v>
+        <v>4.128081617489363</v>
       </c>
       <c r="BN60" t="n">
         <v>2.581538718304228</v>
@@ -11909,7 +11909,7 @@
         <v>6.85678837608662</v>
       </c>
       <c r="BQ60" t="n">
-        <v>3.696800246266607</v>
+        <v>3.696800246266608</v>
       </c>
       <c r="BR60" t="n">
         <v>5.550791624562271</v>
@@ -11933,10 +11933,10 @@
         <v>6.660480537241252</v>
       </c>
       <c r="BY60" t="n">
-        <v>8.243324276720969</v>
+        <v>8.243324276720971</v>
       </c>
       <c r="BZ60" t="n">
-        <v>7.811798335466432</v>
+        <v>7.811798335466431</v>
       </c>
     </row>
     <row r="61">
@@ -12272,7 +12272,7 @@
         <v>2.79991348130604</v>
       </c>
       <c r="D63" t="n">
-        <v>4.264365852458415</v>
+        <v>4.264365852458414</v>
       </c>
       <c r="E63" t="n">
         <v>7.470328686616686</v>
@@ -12287,7 +12287,7 @@
         <v>4.288145295229945</v>
       </c>
       <c r="I63" t="n">
-        <v>4.843132563597555</v>
+        <v>4.843132563597556</v>
       </c>
       <c r="J63" t="n">
         <v>2.410297747032073</v>
@@ -12299,16 +12299,16 @@
         <v>1.876829976907474</v>
       </c>
       <c r="M63" t="n">
-        <v>3.555555813284483</v>
+        <v>3.555555813284482</v>
       </c>
       <c r="N63" t="n">
-        <v>4.314127092758112</v>
+        <v>4.314127092758113</v>
       </c>
       <c r="O63" t="n">
         <v>5.731111266270409</v>
       </c>
       <c r="P63" t="n">
-        <v>4.968133204627756</v>
+        <v>4.968133204627757</v>
       </c>
       <c r="Q63" t="n">
         <v>4.792632014635735</v>
@@ -12347,7 +12347,7 @@
         <v>2.790128806359558</v>
       </c>
       <c r="AC63" t="n">
-        <v>3.690613647707701</v>
+        <v>3.6906136477077</v>
       </c>
       <c r="AD63" t="n">
         <v>3.765981401910957</v>
@@ -12359,10 +12359,10 @@
         <v>4.254420751103686</v>
       </c>
       <c r="AG63" t="n">
-        <v>5.943506769653193</v>
+        <v>5.943506769653192</v>
       </c>
       <c r="AH63" t="n">
-        <v>3.935020703838506</v>
+        <v>3.935020703838507</v>
       </c>
       <c r="AI63" t="n">
         <v>6.878479241372824</v>
@@ -12389,10 +12389,10 @@
         <v>5.962659898238021</v>
       </c>
       <c r="AQ63" t="n">
-        <v>4.564040765283085</v>
+        <v>4.564040765283086</v>
       </c>
       <c r="AR63" t="n">
-        <v>7.856242291902202</v>
+        <v>7.856242291902201</v>
       </c>
       <c r="AS63" t="n">
         <v>2.630387961497413</v>
@@ -12431,7 +12431,7 @@
         <v>6.242262368505729</v>
       </c>
       <c r="BE63" t="n">
-        <v>2.740342993393775</v>
+        <v>2.740342993393774</v>
       </c>
       <c r="BF63" t="n">
         <v>1.736801380602102</v>
@@ -12446,19 +12446,19 @@
         <v>1.686071747697091</v>
       </c>
       <c r="BJ63" t="n">
-        <v>5.346409142291315</v>
+        <v>5.346409142291316</v>
       </c>
       <c r="BK63" t="n">
-        <v>5.554425239233173</v>
+        <v>5.554425239233175</v>
       </c>
       <c r="BL63" t="n">
-        <v>0.6592710097238205</v>
+        <v>0.6592710097238207</v>
       </c>
       <c r="BM63" t="n">
         <v>1.024311770859487</v>
       </c>
       <c r="BN63" t="n">
-        <v>0.9137574707421922</v>
+        <v>0.9137574707421919</v>
       </c>
       <c r="BO63" t="n">
         <v>2.10552615856498</v>
@@ -12717,7 +12717,7 @@
         <v>16.42498548726356</v>
       </c>
       <c r="E65" t="n">
-        <v>33.24811853724505</v>
+        <v>33.24811853724506</v>
       </c>
       <c r="F65" t="n">
         <v>15.74623534675436</v>
@@ -12741,13 +12741,13 @@
         <v>17.21687066573466</v>
       </c>
       <c r="M65" t="n">
-        <v>7.126870113289404</v>
+        <v>7.126870113289405</v>
       </c>
       <c r="N65" t="n">
-        <v>7.761856330566276</v>
+        <v>7.761856330566278</v>
       </c>
       <c r="O65" t="n">
-        <v>12.25137494843027</v>
+        <v>12.25137494843028</v>
       </c>
       <c r="P65" t="n">
         <v>10.90932992734961</v>
@@ -12759,7 +12759,7 @@
         <v>9.906998316432437</v>
       </c>
       <c r="S65" t="n">
-        <v>10.77025783340516</v>
+        <v>10.77025783340515</v>
       </c>
       <c r="T65" t="n">
         <v>10.22798048229222</v>
@@ -12777,10 +12777,10 @@
         <v>12.46640276955226</v>
       </c>
       <c r="Y65" t="n">
-        <v>15.06376639168586</v>
+        <v>15.06376639168587</v>
       </c>
       <c r="Z65" t="n">
-        <v>13.62806684929938</v>
+        <v>13.62806684929937</v>
       </c>
       <c r="AA65" t="n">
         <v>15.52134896413366</v>
@@ -12792,7 +12792,7 @@
         <v>33.81245803558935</v>
       </c>
       <c r="AD65" t="n">
-        <v>33.14556033531046</v>
+        <v>33.14556033531047</v>
       </c>
       <c r="AE65" t="n">
         <v>34.00074542254205</v>
@@ -12804,7 +12804,7 @@
         <v>25.27823514257086</v>
       </c>
       <c r="AH65" t="n">
-        <v>11.901373938882</v>
+        <v>11.90137393888201</v>
       </c>
       <c r="AI65" t="n">
         <v>18.92319705586949</v>
@@ -12813,13 +12813,13 @@
         <v>18.32616809440302</v>
       </c>
       <c r="AK65" t="n">
-        <v>37.96654535202737</v>
+        <v>37.96654535202738</v>
       </c>
       <c r="AL65" t="n">
-        <v>47.03640480753075</v>
+        <v>47.03640480753074</v>
       </c>
       <c r="AM65" t="n">
-        <v>40.46877384043077</v>
+        <v>40.46877384043079</v>
       </c>
       <c r="AN65" t="n">
         <v>18.66182662774581</v>
@@ -12831,7 +12831,7 @@
         <v>20.67227238832454</v>
       </c>
       <c r="AQ65" t="n">
-        <v>21.92514054121094</v>
+        <v>21.92514054121093</v>
       </c>
       <c r="AR65" t="n">
         <v>28.04451099155321</v>
@@ -12840,7 +12840,7 @@
         <v>22.98303201422998</v>
       </c>
       <c r="AT65" t="n">
-        <v>24.69564912547802</v>
+        <v>24.69564912547803</v>
       </c>
       <c r="AU65" t="n">
         <v>21.48838106030491</v>
@@ -12849,7 +12849,7 @@
         <v>20.9292249993142</v>
       </c>
       <c r="AW65" t="n">
-        <v>50.62993113228756</v>
+        <v>50.62993113228757</v>
       </c>
       <c r="AX65" t="n">
         <v>16.98280122066726</v>
@@ -12858,7 +12858,7 @@
         <v>13.24787508334976</v>
       </c>
       <c r="AZ65" t="n">
-        <v>12.80554533730192</v>
+        <v>12.80554533730191</v>
       </c>
       <c r="BA65" t="n">
         <v>8.879944946040105</v>
@@ -12867,7 +12867,7 @@
         <v>119.8002698580501</v>
       </c>
       <c r="BC65" t="n">
-        <v>37.44458601377007</v>
+        <v>37.44458601377006</v>
       </c>
       <c r="BD65" t="n">
         <v>108.6770826107377</v>
@@ -12879,10 +12879,10 @@
         <v>46.39445459823104</v>
       </c>
       <c r="BG65" t="n">
-        <v>43.68080411303128</v>
+        <v>43.68080411303129</v>
       </c>
       <c r="BH65" t="n">
-        <v>53.64444630655385</v>
+        <v>53.64444630655386</v>
       </c>
       <c r="BI65" t="n">
         <v>48.78719727270538</v>
@@ -12900,7 +12900,7 @@
         <v>13.86407509000137</v>
       </c>
       <c r="BN65" t="n">
-        <v>22.00150208953174</v>
+        <v>22.00150208953173</v>
       </c>
       <c r="BO65" t="n">
         <v>42.36421446028131</v>
@@ -12909,19 +12909,19 @@
         <v>13.84789079187592</v>
       </c>
       <c r="BQ65" t="n">
-        <v>6.480403998485294</v>
+        <v>6.480403998485293</v>
       </c>
       <c r="BR65" t="n">
-        <v>51.25479446067623</v>
+        <v>51.25479446067622</v>
       </c>
       <c r="BS65" t="n">
-        <v>54.17977204347731</v>
+        <v>54.17977204347732</v>
       </c>
       <c r="BT65" t="n">
-        <v>62.20335410112788</v>
+        <v>62.20335410112787</v>
       </c>
       <c r="BU65" t="n">
-        <v>68.14268615438363</v>
+        <v>68.14268615438361</v>
       </c>
       <c r="BV65" t="n">
         <v>52.71957356756503</v>
@@ -12930,7 +12930,7 @@
         <v>60.84473982549751</v>
       </c>
       <c r="BX65" t="n">
-        <v>51.63637233794018</v>
+        <v>51.63637233794019</v>
       </c>
       <c r="BY65" t="n">
         <v>42.04694426947935</v>
@@ -13054,19 +13054,19 @@
         <v>0.04375162598701705</v>
       </c>
       <c r="AL66" t="n">
-        <v>0.05320357180351024</v>
+        <v>0.05320357180351023</v>
       </c>
       <c r="AM66" t="n">
         <v>0.04303010740970132</v>
       </c>
       <c r="AN66" t="n">
-        <v>0.05248462079232705</v>
+        <v>0.05248462079232706</v>
       </c>
       <c r="AO66" t="n">
-        <v>0.04858791120577843</v>
+        <v>0.04858791120577845</v>
       </c>
       <c r="AP66" t="n">
-        <v>0.04741481553032647</v>
+        <v>0.04741481553032648</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.04309042992899655</v>
@@ -13081,7 +13081,7 @@
         <v>0.05326429879185376</v>
       </c>
       <c r="AU66" t="n">
-        <v>0.0553188567571552</v>
+        <v>0.05531885675715519</v>
       </c>
       <c r="AV66" t="n">
         <v>0.05794698938143877</v>
@@ -13944,13 +13944,13 @@
         <v>2.16251417569332</v>
       </c>
       <c r="J72" t="n">
-        <v>3.696545577161217</v>
+        <v>3.696545577161218</v>
       </c>
       <c r="K72" t="n">
         <v>3.723678963865669</v>
       </c>
       <c r="L72" t="n">
-        <v>3.376236524914878</v>
+        <v>3.376236524914879</v>
       </c>
       <c r="M72" t="n">
         <v>1.824694485232099</v>
@@ -13977,7 +13977,7 @@
         <v>2.494216693973865</v>
       </c>
       <c r="U72" t="n">
-        <v>2.469482476289568</v>
+        <v>2.469482476289567</v>
       </c>
       <c r="V72" t="n">
         <v>4.502241046758979</v>
@@ -13998,13 +13998,13 @@
         <v>5.703350163585783</v>
       </c>
       <c r="AB72" t="n">
-        <v>5.260023923165285</v>
+        <v>5.260023923165286</v>
       </c>
       <c r="AC72" t="n">
-        <v>6.435725873210994</v>
+        <v>6.435725873210993</v>
       </c>
       <c r="AD72" t="n">
-        <v>5.796831160735115</v>
+        <v>5.796831160735116</v>
       </c>
       <c r="AE72" t="n">
         <v>4.68456746099486</v>
@@ -14016,13 +14016,13 @@
         <v>3.067425498640364</v>
       </c>
       <c r="AH72" t="n">
-        <v>2.051616018490941</v>
+        <v>2.05161601849094</v>
       </c>
       <c r="AI72" t="n">
         <v>3.400235439589585</v>
       </c>
       <c r="AJ72" t="n">
-        <v>3.481823544341123</v>
+        <v>3.481823544341124</v>
       </c>
       <c r="AK72" t="n">
         <v>7.221576171288306</v>
@@ -14031,7 +14031,7 @@
         <v>8.349184623310784</v>
       </c>
       <c r="AM72" t="n">
-        <v>7.849176400410666</v>
+        <v>7.849176400410665</v>
       </c>
       <c r="AN72" t="n">
         <v>3.585172859688571</v>
@@ -14049,7 +14049,7 @@
         <v>3.981549624493045</v>
       </c>
       <c r="AS72" t="n">
-        <v>2.891653492855655</v>
+        <v>2.891653492855654</v>
       </c>
       <c r="AT72" t="n">
         <v>3.885330261839941</v>
@@ -14073,10 +14073,10 @@
         <v>4.964921553099321</v>
       </c>
       <c r="BA72" t="n">
-        <v>6.369045869594877</v>
+        <v>6.369045869594876</v>
       </c>
       <c r="BB72" t="n">
-        <v>5.980367212418304</v>
+        <v>5.980367212418303</v>
       </c>
       <c r="BC72" t="n">
         <v>4.184193667851291</v>
@@ -14088,19 +14088,19 @@
         <v>3.108082498877033</v>
       </c>
       <c r="BF72" t="n">
-        <v>6.783585499297509</v>
+        <v>6.78358549929751</v>
       </c>
       <c r="BG72" t="n">
-        <v>6.62246096615758</v>
+        <v>6.622460966157581</v>
       </c>
       <c r="BH72" t="n">
-        <v>7.233715446633333</v>
+        <v>7.233715446633335</v>
       </c>
       <c r="BI72" t="n">
-        <v>7.174542695164829</v>
+        <v>7.174542695164828</v>
       </c>
       <c r="BJ72" t="n">
-        <v>6.129596863548791</v>
+        <v>6.129596863548792</v>
       </c>
       <c r="BK72" t="n">
         <v>2.622431313624594</v>
@@ -14109,7 +14109,7 @@
         <v>3.011095429887524</v>
       </c>
       <c r="BM72" t="n">
-        <v>2.723729141919337</v>
+        <v>2.723729141919338</v>
       </c>
       <c r="BN72" t="n">
         <v>6.530158205965199</v>
@@ -14121,7 +14121,7 @@
         <v>4.563277354348036</v>
       </c>
       <c r="BQ72" t="n">
-        <v>3.544396043475585</v>
+        <v>3.544396043475586</v>
       </c>
       <c r="BR72" t="n">
         <v>3.281308475141461</v>
@@ -14139,7 +14139,7 @@
         <v>5.515505292294513</v>
       </c>
       <c r="BW72" t="n">
-        <v>6.874943329720743</v>
+        <v>6.874943329720742</v>
       </c>
       <c r="BX72" t="n">
         <v>7.805514014212128</v>
@@ -14170,16 +14170,16 @@
         <v>15.5146489806167</v>
       </c>
       <c r="F73" t="n">
-        <v>1.820169612964183</v>
+        <v>1.820169612964184</v>
       </c>
       <c r="G73" t="n">
         <v>1.028490795999998</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9493904499797007</v>
+        <v>0.9493904499797006</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9487346819976641</v>
+        <v>0.9487346819976642</v>
       </c>
       <c r="J73" t="n">
         <v>1.362561186275795</v>
@@ -14191,10 +14191,10 @@
         <v>1.30272740281549</v>
       </c>
       <c r="M73" t="n">
-        <v>0.8082319760276143</v>
+        <v>0.8082319760276144</v>
       </c>
       <c r="N73" t="n">
-        <v>0.8357971352868575</v>
+        <v>0.8357971352868574</v>
       </c>
       <c r="O73" t="n">
         <v>1.194777470261088</v>
@@ -14203,7 +14203,7 @@
         <v>1.303399130528253</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.048955214928992</v>
+        <v>1.048955214928991</v>
       </c>
       <c r="R73" t="n">
         <v>1.149112359220171</v>
@@ -14242,7 +14242,7 @@
         <v>1.861598259642847</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.966615622851112</v>
+        <v>1.966615622851113</v>
       </c>
       <c r="AE73" t="n">
         <v>1.795221408375513</v>
@@ -14254,7 +14254,7 @@
         <v>1.534777801365066</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.070358596505768</v>
+        <v>1.070358596505767</v>
       </c>
       <c r="AI73" t="n">
         <v>1.621844396761394</v>
@@ -14293,19 +14293,19 @@
         <v>2.295443370046029</v>
       </c>
       <c r="AU73" t="n">
-        <v>1.908305928406145</v>
+        <v>1.908305928406144</v>
       </c>
       <c r="AV73" t="n">
-        <v>1.95565141987464</v>
+        <v>1.955651419874639</v>
       </c>
       <c r="AW73" t="n">
         <v>12.07663263325047</v>
       </c>
       <c r="AX73" t="n">
-        <v>3.177982204474137</v>
+        <v>3.177982204474138</v>
       </c>
       <c r="AY73" t="n">
-        <v>3.381460116391875</v>
+        <v>3.381460116391876</v>
       </c>
       <c r="AZ73" t="n">
         <v>3.036298674380602</v>
@@ -14320,10 +14320,10 @@
         <v>5.872990642625203</v>
       </c>
       <c r="BD73" t="n">
-        <v>10.86933707554019</v>
+        <v>10.86933707554018</v>
       </c>
       <c r="BE73" t="n">
-        <v>4.637054203267976</v>
+        <v>4.637054203267975</v>
       </c>
       <c r="BF73" t="n">
         <v>4.570989971262401</v>
@@ -14332,61 +14332,61 @@
         <v>4.385094804811652</v>
       </c>
       <c r="BH73" t="n">
-        <v>5.126668671270251</v>
+        <v>5.12666867127025</v>
       </c>
       <c r="BI73" t="n">
-        <v>4.747363221458894</v>
+        <v>4.747363221458895</v>
       </c>
       <c r="BJ73" t="n">
-        <v>2.708342057066829</v>
+        <v>2.708342057066828</v>
       </c>
       <c r="BK73" t="n">
         <v>1.012906987647647</v>
       </c>
       <c r="BL73" t="n">
-        <v>2.421855639381421</v>
+        <v>2.421855639381422</v>
       </c>
       <c r="BM73" t="n">
-        <v>2.335674122696744</v>
+        <v>2.335674122696745</v>
       </c>
       <c r="BN73" t="n">
-        <v>2.559154677979145</v>
+        <v>2.559154677979146</v>
       </c>
       <c r="BO73" t="n">
-        <v>8.043749703183584</v>
+        <v>8.043749703183586</v>
       </c>
       <c r="BP73" t="n">
-        <v>3.082443734005836</v>
+        <v>3.082443734005835</v>
       </c>
       <c r="BQ73" t="n">
-        <v>2.22921359781061</v>
+        <v>2.229213597810609</v>
       </c>
       <c r="BR73" t="n">
-        <v>7.895809724770188</v>
+        <v>7.895809724770189</v>
       </c>
       <c r="BS73" t="n">
-        <v>8.186106646799896</v>
+        <v>8.186106646799894</v>
       </c>
       <c r="BT73" t="n">
-        <v>7.899780427942614</v>
+        <v>7.899780427942613</v>
       </c>
       <c r="BU73" t="n">
         <v>7.858886627952236</v>
       </c>
       <c r="BV73" t="n">
-        <v>5.469799948955499</v>
+        <v>5.469799948955498</v>
       </c>
       <c r="BW73" t="n">
         <v>5.668449225217168</v>
       </c>
       <c r="BX73" t="n">
-        <v>5.382796217445994</v>
+        <v>5.382796217445995</v>
       </c>
       <c r="BY73" t="n">
-        <v>3.890382327953748</v>
+        <v>3.890382327953749</v>
       </c>
       <c r="BZ73" t="n">
-        <v>2.837411505347575</v>
+        <v>2.837411505347576</v>
       </c>
     </row>
     <row r="74">
@@ -14405,7 +14405,7 @@
         <v>0.6200917579748507</v>
       </c>
       <c r="E74" t="n">
-        <v>0.6366800106273985</v>
+        <v>0.6366800106273984</v>
       </c>
       <c r="F74" t="n">
         <v>0.3640652003090395</v>
@@ -14501,7 +14501,7 @@
         <v>0.2706264854165202</v>
       </c>
       <c r="AK74" t="n">
-        <v>0.3600787651038707</v>
+        <v>0.3600787651038706</v>
       </c>
       <c r="AL74" t="n">
         <v>0.3747685100697778</v>
@@ -14510,13 +14510,13 @@
         <v>0.397060448327709</v>
       </c>
       <c r="AN74" t="n">
-        <v>0.3232928862631578</v>
+        <v>0.3232928862631577</v>
       </c>
       <c r="AO74" t="n">
         <v>0.287523056599517</v>
       </c>
       <c r="AP74" t="n">
-        <v>0.3174969969322279</v>
+        <v>0.3174969969322278</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.2444197551329816</v>
@@ -14528,7 +14528,7 @@
         <v>0.2799500228643972</v>
       </c>
       <c r="AT74" t="n">
-        <v>0.3510307047023835</v>
+        <v>0.3510307047023836</v>
       </c>
       <c r="AU74" t="n">
         <v>0.3540692955967938</v>
@@ -14738,7 +14738,7 @@
         <v>0.1013686115783968</v>
       </c>
       <c r="H76" t="n">
-        <v>0.09302697201854229</v>
+        <v>0.09302697201854231</v>
       </c>
       <c r="I76" t="n">
         <v>0.09164851608456254</v>
@@ -14747,7 +14747,7 @@
         <v>0.129697685750499</v>
       </c>
       <c r="K76" t="n">
-        <v>0.1412973210877279</v>
+        <v>0.1412973210877278</v>
       </c>
       <c r="L76" t="n">
         <v>0.1226446614012856</v>
@@ -14852,7 +14852,7 @@
         <v>0.133622850750763</v>
       </c>
       <c r="AT76" t="n">
-        <v>0.1489429426829874</v>
+        <v>0.1489429426829875</v>
       </c>
       <c r="AU76" t="n">
         <v>0.167119106066005</v>
@@ -14906,16 +14906,16 @@
         <v>1.405626126578456</v>
       </c>
       <c r="BL76" t="n">
-        <v>0.3354456477973418</v>
+        <v>0.3354456477973419</v>
       </c>
       <c r="BM76" t="n">
-        <v>0.381176663090538</v>
+        <v>0.3811766630905379</v>
       </c>
       <c r="BN76" t="n">
         <v>0.2579853382344927</v>
       </c>
       <c r="BO76" t="n">
-        <v>0.2920967849790298</v>
+        <v>0.2920967849790299</v>
       </c>
       <c r="BP76" t="n">
         <v>0.4954334773867137</v>
@@ -14945,7 +14945,7 @@
         <v>0.212666678560062</v>
       </c>
       <c r="BY76" t="n">
-        <v>0.1977148527146103</v>
+        <v>0.1977148527146104</v>
       </c>
       <c r="BZ76" t="n">
         <v>0.181891459264547</v>
@@ -15664,7 +15664,7 @@
         <v>1.853032700079784</v>
       </c>
       <c r="H83" t="n">
-        <v>1.689037137221685</v>
+        <v>1.689037137221684</v>
       </c>
       <c r="I83" t="n">
         <v>1.678543119192666</v>
@@ -15676,7 +15676,7 @@
         <v>2.17608127755277</v>
       </c>
       <c r="L83" t="n">
-        <v>1.716703293374512</v>
+        <v>1.716703293374513</v>
       </c>
       <c r="M83" t="n">
         <v>1.809582992479477</v>
@@ -15691,7 +15691,7 @@
         <v>3.27551587872165</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.791513193613764</v>
+        <v>2.791513193613765</v>
       </c>
       <c r="R83" t="n">
         <v>2.802569049117495</v>
@@ -15703,13 +15703,13 @@
         <v>3.364980266620962</v>
       </c>
       <c r="U83" t="n">
-        <v>3.14215686504065</v>
+        <v>3.142156865040651</v>
       </c>
       <c r="V83" t="n">
         <v>5.200489072612822</v>
       </c>
       <c r="W83" t="n">
-        <v>5.563510791661921</v>
+        <v>5.56351079166192</v>
       </c>
       <c r="X83" t="n">
         <v>4.749164277747942</v>
@@ -15721,7 +15721,7 @@
         <v>5.976482231812954</v>
       </c>
       <c r="AA83" t="n">
-        <v>6.015567008960661</v>
+        <v>6.015567008960662</v>
       </c>
       <c r="AB83" t="n">
         <v>2.546377297557834</v>
@@ -15799,13 +15799,13 @@
         <v>7.802645733807812</v>
       </c>
       <c r="BA83" t="n">
-        <v>8.064374965772698</v>
+        <v>8.0643749657727</v>
       </c>
       <c r="BB83" t="n">
         <v>7.619175188219162</v>
       </c>
       <c r="BC83" t="n">
-        <v>9.341850916800182</v>
+        <v>9.34185091680018</v>
       </c>
       <c r="BD83" t="n">
         <v>11.13132543339599</v>
@@ -15814,16 +15814,16 @@
         <v>8.281263014930225</v>
       </c>
       <c r="BF83" t="n">
-        <v>6.867701433205149</v>
+        <v>6.867701433205148</v>
       </c>
       <c r="BG83" t="n">
-        <v>6.885711274535898</v>
+        <v>6.885711274535897</v>
       </c>
       <c r="BH83" t="n">
         <v>6.663061076369354</v>
       </c>
       <c r="BI83" t="n">
-        <v>6.836618643319919</v>
+        <v>6.83661864331992</v>
       </c>
       <c r="BJ83" t="n">
         <v>10.59384681221351</v>
@@ -15832,7 +15832,7 @@
         <v>9.75394240668777</v>
       </c>
       <c r="BL83" t="n">
-        <v>6.093971219116221</v>
+        <v>6.093971219116222</v>
       </c>
       <c r="BM83" t="n">
         <v>6.17421842073531</v>
@@ -15841,10 +15841,10 @@
         <v>4.044737082403086</v>
       </c>
       <c r="BO83" t="n">
-        <v>4.353968230626616</v>
+        <v>4.353968230626615</v>
       </c>
       <c r="BP83" t="n">
-        <v>5.093105766481382</v>
+        <v>5.093105766481381</v>
       </c>
       <c r="BQ83" t="n">
         <v>4.077457267217009</v>
@@ -15856,10 +15856,10 @@
         <v>3.562794894653635</v>
       </c>
       <c r="BT83" t="n">
-        <v>4.451530148742519</v>
+        <v>4.451530148742518</v>
       </c>
       <c r="BU83" t="n">
-        <v>5.106325163568669</v>
+        <v>5.106325163568668</v>
       </c>
       <c r="BV83" t="n">
         <v>3.959930523306012</v>
@@ -15874,7 +15874,7 @@
         <v>5.295652822652454</v>
       </c>
       <c r="BZ83" t="n">
-        <v>5.079524485052684</v>
+        <v>5.079524485052683</v>
       </c>
     </row>
     <row r="84">
@@ -15914,7 +15914,7 @@
         <v>0.5281159754846262</v>
       </c>
       <c r="L84" t="n">
-        <v>0.3347298202711429</v>
+        <v>0.3347298202711428</v>
       </c>
       <c r="M84" t="n">
         <v>0.2894938583441362</v>
@@ -15929,7 +15929,7 @@
         <v>0.5472088160063479</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.4955660905181579</v>
+        <v>0.4955660905181578</v>
       </c>
       <c r="R84" t="n">
         <v>0.4632022778723619</v>
@@ -15971,7 +15971,7 @@
         <v>0.6347507605601701</v>
       </c>
       <c r="AE84" t="n">
-        <v>0.5156335680652689</v>
+        <v>0.5156335680652688</v>
       </c>
       <c r="AF84" t="n">
         <v>0.3245911069487588</v>
@@ -15995,7 +15995,7 @@
         <v>0.6091610825465367</v>
       </c>
       <c r="AM84" t="n">
-        <v>0.5142984173989418</v>
+        <v>0.5142984173989417</v>
       </c>
       <c r="AN84" t="n">
         <v>0.7547549066144904</v>
@@ -16013,7 +16013,7 @@
         <v>0.4910319049975715</v>
       </c>
       <c r="AS84" t="n">
-        <v>0.4025937841676209</v>
+        <v>0.4025937841676208</v>
       </c>
       <c r="AT84" t="n">
         <v>0.8215457704046119</v>
@@ -16022,7 +16022,7 @@
         <v>0.7226371687391281</v>
       </c>
       <c r="AV84" t="n">
-        <v>0.6522650802928907</v>
+        <v>0.6522650802928905</v>
       </c>
       <c r="AW84" t="n">
         <v>2.016113643332917</v>
@@ -16085,7 +16085,7 @@
         <v>1.079486591520434</v>
       </c>
       <c r="BQ84" t="n">
-        <v>0.9119414321488793</v>
+        <v>0.9119414321488795</v>
       </c>
       <c r="BR84" t="n">
         <v>0.9265148345070381</v>
@@ -16272,7 +16272,7 @@
         <v>3.484933315759847</v>
       </c>
       <c r="AZ85" t="n">
-        <v>0.7000798493063447</v>
+        <v>0.7000798493063446</v>
       </c>
       <c r="BA85" t="n">
         <v>1.491699902482934</v>
@@ -16934,10 +16934,10 @@
         <v>0.005128169598211417</v>
       </c>
       <c r="H91" t="n">
-        <v>0.004934281538811341</v>
+        <v>0.004934281538811342</v>
       </c>
       <c r="I91" t="n">
-        <v>0.004615980839953355</v>
+        <v>0.004615980839953356</v>
       </c>
       <c r="J91" t="n">
         <v>0.01109048634528731</v>
@@ -16949,7 +16949,7 @@
         <v>0.01126820629511671</v>
       </c>
       <c r="M91" t="n">
-        <v>0.003906739311408113</v>
+        <v>0.003906739311408112</v>
       </c>
       <c r="N91" t="n">
         <v>0.004864564605790016</v>
@@ -16961,10 +16961,10 @@
         <v>0.005104429648843259</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.004896702041713663</v>
+        <v>0.004896702041713662</v>
       </c>
       <c r="R91" t="n">
-        <v>0.004768375472542639</v>
+        <v>0.004768375472542638</v>
       </c>
       <c r="S91" t="n">
         <v>0.005908791673296735</v>
@@ -16973,7 +16973,7 @@
         <v>0.005519313224901472</v>
       </c>
       <c r="U91" t="n">
-        <v>0.006851309254681137</v>
+        <v>0.006851309254681135</v>
       </c>
       <c r="V91" t="n">
         <v>0.007206040986604118</v>
@@ -17006,7 +17006,7 @@
         <v>0.01246406530884596</v>
       </c>
       <c r="AF91" t="n">
-        <v>0.00601433156309228</v>
+        <v>0.006014331563092281</v>
       </c>
       <c r="AG91" t="n">
         <v>0.007042742835416198</v>
@@ -17018,7 +17018,7 @@
         <v>0.005607381837918363</v>
       </c>
       <c r="AJ91" t="n">
-        <v>0.008032353973488738</v>
+        <v>0.00803235397348874</v>
       </c>
       <c r="AK91" t="n">
         <v>0.01081533219513197</v>
@@ -17030,7 +17030,7 @@
         <v>0.01199015835028661</v>
       </c>
       <c r="AN91" t="n">
-        <v>0.007872694791481139</v>
+        <v>0.007872694791481137</v>
       </c>
       <c r="AO91" t="n">
         <v>0.00667227226010189</v>
@@ -17054,7 +17054,7 @@
         <v>0.008216830248491184</v>
       </c>
       <c r="AV91" t="n">
-        <v>0.004977381452137083</v>
+        <v>0.004977381452137084</v>
       </c>
       <c r="AW91" t="n">
         <v>0.004512193878169039</v>
@@ -17094,7 +17094,7 @@
         <v>0.002841010898929838</v>
       </c>
       <c r="BJ91" t="n">
-        <v>0.04542470413985877</v>
+        <v>0.04542470413985878</v>
       </c>
       <c r="BK91" t="n">
         <v>0.03067681324272945</v>
@@ -17699,7 +17699,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.9205367100830055</v>
+        <v>0.9205367100830056</v>
       </c>
       <c r="D95" t="n">
         <v>3.817158416189333</v>
@@ -17720,22 +17720,22 @@
         <v>0.6504951537366944</v>
       </c>
       <c r="J95" t="n">
-        <v>0.9448599909104214</v>
+        <v>0.9448599909104215</v>
       </c>
       <c r="K95" t="n">
-        <v>0.9908342363656869</v>
+        <v>0.990834236365687</v>
       </c>
       <c r="L95" t="n">
         <v>0.8895983021433984</v>
       </c>
       <c r="M95" t="n">
-        <v>0.4709756111027243</v>
+        <v>0.4709756111027242</v>
       </c>
       <c r="N95" t="n">
-        <v>0.5237196468145875</v>
+        <v>0.5237196468145876</v>
       </c>
       <c r="O95" t="n">
-        <v>0.6346243735533651</v>
+        <v>0.634624373553365</v>
       </c>
       <c r="P95" t="n">
         <v>0.6525376073775273</v>
@@ -17744,13 +17744,13 @@
         <v>0.5653124899561633</v>
       </c>
       <c r="R95" t="n">
-        <v>0.5955357682203425</v>
+        <v>0.5955357682203426</v>
       </c>
       <c r="S95" t="n">
         <v>0.5942980842216132</v>
       </c>
       <c r="T95" t="n">
-        <v>0.5636608634038375</v>
+        <v>0.5636608634038376</v>
       </c>
       <c r="U95" t="n">
         <v>0.5874637315655226</v>
@@ -17759,7 +17759,7 @@
         <v>0.6067138677858945</v>
       </c>
       <c r="W95" t="n">
-        <v>0.6834500199763762</v>
+        <v>0.6834500199763761</v>
       </c>
       <c r="X95" t="n">
         <v>0.5350082131784626</v>
@@ -17789,10 +17789,10 @@
         <v>0.6508834817073622</v>
       </c>
       <c r="AG95" t="n">
-        <v>0.8698486323271666</v>
+        <v>0.8698486323271667</v>
       </c>
       <c r="AH95" t="n">
-        <v>0.646725714632963</v>
+        <v>0.6467257146329631</v>
       </c>
       <c r="AI95" t="n">
         <v>1.015167633333392</v>
@@ -17807,7 +17807,7 @@
         <v>1.734196256928511</v>
       </c>
       <c r="AM95" t="n">
-        <v>1.666402834449118</v>
+        <v>1.666402834449119</v>
       </c>
       <c r="AN95" t="n">
         <v>1.158605979632494</v>
@@ -17819,19 +17819,19 @@
         <v>0.9691201029765193</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.6929628585263676</v>
+        <v>0.6929628585263677</v>
       </c>
       <c r="AR95" t="n">
         <v>0.8860935253256026</v>
       </c>
       <c r="AS95" t="n">
-        <v>0.6805582539506633</v>
+        <v>0.6805582539506634</v>
       </c>
       <c r="AT95" t="n">
         <v>1.16229019781048</v>
       </c>
       <c r="AU95" t="n">
-        <v>0.9888115691206724</v>
+        <v>0.9888115691206723</v>
       </c>
       <c r="AV95" t="n">
         <v>0.9478997630041396</v>
@@ -17840,10 +17840,10 @@
         <v>7.11754504703621</v>
       </c>
       <c r="AX95" t="n">
-        <v>1.063159875858528</v>
+        <v>1.063159875858529</v>
       </c>
       <c r="AY95" t="n">
-        <v>1.412663303859853</v>
+        <v>1.412663303859854</v>
       </c>
       <c r="AZ95" t="n">
         <v>0.7060250030013899</v>
@@ -17882,10 +17882,10 @@
         <v>0.3089988076164391</v>
       </c>
       <c r="BL95" t="n">
-        <v>0.5540376372208826</v>
+        <v>0.5540376372208825</v>
       </c>
       <c r="BM95" t="n">
-        <v>0.7038337688711354</v>
+        <v>0.7038337688711355</v>
       </c>
       <c r="BN95" t="n">
         <v>1.240643910900456</v>
@@ -17894,7 +17894,7 @@
         <v>4.319589039343176</v>
       </c>
       <c r="BP95" t="n">
-        <v>0.8337878450540918</v>
+        <v>0.8337878450540919</v>
       </c>
       <c r="BQ95" t="n">
         <v>0.6758106367871616</v>
@@ -17903,10 +17903,10 @@
         <v>4.608146826834149</v>
       </c>
       <c r="BS95" t="n">
-        <v>4.670304156912012</v>
+        <v>4.670304156912013</v>
       </c>
       <c r="BT95" t="n">
-        <v>4.336233295896637</v>
+        <v>4.336233295896636</v>
       </c>
       <c r="BU95" t="n">
         <v>4.279072152430222</v>
@@ -17921,7 +17921,7 @@
         <v>3.144868686394676</v>
       </c>
       <c r="BY95" t="n">
-        <v>1.809684838964271</v>
+        <v>1.80968483896427</v>
       </c>
       <c r="BZ95" t="n">
         <v>1.120261138227176</v>
@@ -19894,7 +19894,7 @@
         <v>0.5777617225338523</v>
       </c>
       <c r="D110" t="n">
-        <v>0.820387972136468</v>
+        <v>0.8203879721364682</v>
       </c>
       <c r="E110" t="n">
         <v>0.8131049572000667</v>
@@ -19987,31 +19987,31 @@
         <v>0.1529226669772445</v>
       </c>
       <c r="AI110" t="n">
-        <v>0.2658360691248404</v>
+        <v>0.2658360691248403</v>
       </c>
       <c r="AJ110" t="n">
-        <v>0.2642141253914863</v>
+        <v>0.2642141253914862</v>
       </c>
       <c r="AK110" t="n">
-        <v>0.1494917703141486</v>
+        <v>0.1494917703141487</v>
       </c>
       <c r="AL110" t="n">
         <v>0.1731459227554564</v>
       </c>
       <c r="AM110" t="n">
-        <v>0.1483122214024859</v>
+        <v>0.1483122214024858</v>
       </c>
       <c r="AN110" t="n">
         <v>0.3077413614061968</v>
       </c>
       <c r="AO110" t="n">
-        <v>0.275488455066359</v>
+        <v>0.2754884550663589</v>
       </c>
       <c r="AP110" t="n">
         <v>0.2707474481550593</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.1588233871561141</v>
+        <v>0.1588233871561142</v>
       </c>
       <c r="AR110" t="n">
         <v>0.1938578656505644</v>
@@ -20026,7 +20026,7 @@
         <v>0.3696498472171501</v>
       </c>
       <c r="AV110" t="n">
-        <v>0.3408586798390869</v>
+        <v>0.3408586798390868</v>
       </c>
       <c r="AW110" t="n">
         <v>0.2721771506327155</v>
@@ -20050,7 +20050,7 @@
         <v>1.238081981698215</v>
       </c>
       <c r="BD110" t="n">
-        <v>1.627810069507342</v>
+        <v>1.627810069507341</v>
       </c>
       <c r="BE110" t="n">
         <v>1.083881189007949</v>
@@ -20074,7 +20074,7 @@
         <v>1.607469864471283</v>
       </c>
       <c r="BL110" t="n">
-        <v>0.492769810454812</v>
+        <v>0.4927698104548121</v>
       </c>
       <c r="BM110" t="n">
         <v>0.7269901477363294</v>
@@ -21264,7 +21264,7 @@
         <v>2.215706141711796</v>
       </c>
       <c r="BH119" t="n">
-        <v>2.103221510026734</v>
+        <v>2.103221510026733</v>
       </c>
       <c r="BI119" t="n">
         <v>2.08975789030447</v>
@@ -21282,7 +21282,7 @@
         <v>0.4778668365235835</v>
       </c>
       <c r="BN119" t="n">
-        <v>1.360640262695524</v>
+        <v>1.360640262695523</v>
       </c>
       <c r="BO119" t="n">
         <v>1.402656401382943</v>
@@ -22982,13 +22982,13 @@
         <v>0.0416426549335638</v>
       </c>
       <c r="H135" t="n">
-        <v>0.03968903398926332</v>
+        <v>0.03968903398926331</v>
       </c>
       <c r="I135" t="n">
         <v>0.03761243515136396</v>
       </c>
       <c r="J135" t="n">
-        <v>0.0681192320149801</v>
+        <v>0.06811923201498009</v>
       </c>
       <c r="K135" t="n">
         <v>0.06133558091468464</v>
@@ -23003,7 +23003,7 @@
         <v>0.02437832744505029</v>
       </c>
       <c r="O135" t="n">
-        <v>0.02210217485458716</v>
+        <v>0.02210217485458717</v>
       </c>
       <c r="P135" t="n">
         <v>0.02965350396032431</v>
@@ -23018,19 +23018,19 @@
         <v>0.03236408202761017</v>
       </c>
       <c r="T135" t="n">
-        <v>0.03463037880248247</v>
+        <v>0.03463037880248246</v>
       </c>
       <c r="U135" t="n">
         <v>0.03348668416488885</v>
       </c>
       <c r="V135" t="n">
-        <v>0.04964323510241056</v>
+        <v>0.04964323510241057</v>
       </c>
       <c r="W135" t="n">
         <v>0.05473689256019157</v>
       </c>
       <c r="X135" t="n">
-        <v>0.05455347266775543</v>
+        <v>0.05455347266775544</v>
       </c>
       <c r="Y135" t="n">
         <v>0.06384940821029893</v>
@@ -23066,7 +23066,7 @@
         <v>0.04619262175391208</v>
       </c>
       <c r="AJ135" t="n">
-        <v>0.04915241807401021</v>
+        <v>0.0491524180740102</v>
       </c>
       <c r="AK135" t="n">
         <v>0.165461569364945</v>
@@ -23078,7 +23078,7 @@
         <v>0.1794157381411084</v>
       </c>
       <c r="AN135" t="n">
-        <v>0.0526653818738668</v>
+        <v>0.05266538187386681</v>
       </c>
       <c r="AO135" t="n">
         <v>0.05434938931192165</v>
@@ -23087,7 +23087,7 @@
         <v>0.06078590848008313</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.06007248378643163</v>
+        <v>0.06007248378643162</v>
       </c>
       <c r="AR135" t="n">
         <v>0.06675040764156259</v>
@@ -23114,7 +23114,7 @@
         <v>0.1046794069087727</v>
       </c>
       <c r="AZ135" t="n">
-        <v>0.08577680205984686</v>
+        <v>0.08577680205984688</v>
       </c>
       <c r="BA135" t="n">
         <v>0.06997255537417903</v>
@@ -23159,7 +23159,7 @@
         <v>0.03972482034911796</v>
       </c>
       <c r="BO135" t="n">
-        <v>0.08245760281988482</v>
+        <v>0.08245760281988483</v>
       </c>
       <c r="BP135" t="n">
         <v>0.1994972574816646</v>
